--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -863,7 +863,7 @@
       <c r="E5" s="33" t="n"/>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 52</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 54</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>Установка гребёнки ХВС Ду 32 на 7 выходов с шаровыми кранами</t>
+          <t>Установка гребёнки ХВС Ду 32 на 8 выходов с шаровыми кранами</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 37,9, Т3 7,9 м + 10 %</t>
+          <t>по модели В1 41,8, Т3 7,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 39, 40, 41</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 41, 42, 43</t>
         </is>
       </c>
       <c r="G16" s="35" t="inlineStr">
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>24 + 30 + 15 + 4 = 73</t>
+          <t>24 + 30 + 17 + 4 = 75</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 42, 43, 44, 45</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 44, 45, 46, 47</t>
         </is>
       </c>
       <c r="G17" s="35" t="inlineStr">
@@ -1362,7 +1362,7 @@
       <c r="E18" s="33" t="n"/>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 46</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 48</t>
         </is>
       </c>
       <c r="G18" s="35" t="inlineStr">
@@ -1394,16 +1394,16 @@
         </is>
       </c>
       <c r="D19" s="32" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E19" s="33" t="inlineStr">
         <is>
-          <t>36 + 28 + 12 + 1 = 77</t>
+          <t>36 + 28 + 13 + 1 = 78</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 47, 48, 49, 50</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 49, 50, 51, 52</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -1440,7 +1440,7 @@
       <c r="E20" s="33" t="n"/>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 51</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 53</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I20" s="36" t="n"/>
     </row>
-    <row r="21" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="21" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A21" s="30" t="inlineStr">
         <is>
           <t>16</t>
@@ -1472,16 +1472,16 @@
         </is>
       </c>
       <c r="D21" s="32" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E21" s="33" t="inlineStr">
         <is>
-          <t>37 + 19 = 56</t>
+          <t>39 + 19 = 58</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 93, 94</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 101, 102</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="D22" s="32" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="E22" s="33" t="inlineStr">
         <is>
-          <t>76 + 133 + 35 + 21 = 265</t>
+          <t>76 + 133 + 43 + 21 = 273</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 100, 101, 102, 103</t>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 108, 109, 110, 111</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H22" s="30" t="inlineStr">
         <is>
-          <t>5 7 14 18</t>
+          <t>5 7 14 19</t>
         </is>
       </c>
       <c r="I22" s="36" t="inlineStr">
@@ -1563,7 +1563,7 @@
       <c r="E23" s="33" t="n"/>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 107</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 115</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 64, 65</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 69, 70</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="E26" s="33" t="n"/>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 66</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 71</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -1693,7 +1693,7 @@
       <c r="E27" s="33" t="n"/>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 67</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 75</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1734,7 +1734,7 @@
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 68</t>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 76</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1771,7 +1771,7 @@
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 69</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 77</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="I29" s="36" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1" thickBot="1">
+    <row r="30" ht="45" customHeight="1" thickBot="1">
       <c r="A30" s="30" t="inlineStr">
         <is>
           <t>24</t>
@@ -1794,94 +1794,94 @@
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
+          <t>Подводка автополива КХ-8: установка обратного клапана, спускного крана и заглушки на конце трубы</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t>1 + 1 + 1 = 3</t>
+        </is>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 72, 73, 74</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H30" s="30" t="inlineStr">
+        <is>
+          <t>4 7 14 17</t>
+        </is>
+      </c>
+      <c r="I30" s="36" t="inlineStr">
+        <is>
+          <t>далее — по ландшафтному проекту</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
           <t>Установка кранов шаровых угловых для гибких подводок приборов</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D30" s="32" t="n">
+      <c r="D31" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="E30" s="33" t="n"/>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 70</t>
-        </is>
-      </c>
-      <c r="G30" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H30" s="30" t="inlineStr">
-        <is>
-          <t>3 4 5 8 17</t>
-        </is>
-      </c>
-      <c r="I30" s="36" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="E31" s="33" t="n"/>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 78</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H31" s="30" t="inlineStr">
+        <is>
+          <t>3 4 5 8 18</t>
+        </is>
+      </c>
+      <c r="I31" s="36" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Оборудование горячего водоснабжения</t>
         </is>
       </c>
-      <c r="B31" s="28" t="n"/>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="28" t="n"/>
-      <c r="E31" s="28" t="n"/>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="28" t="n"/>
-      <c r="H31" s="28" t="n"/>
-      <c r="I31" s="29" t="n"/>
-    </row>
-    <row r="32" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="inlineStr">
-        <is>
-          <t>Установка насосов циркуляционных ГВС Н8, Н9 с подключением</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D32" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="33" t="inlineStr">
-        <is>
-          <t>1 + 1 = 2</t>
-        </is>
-      </c>
-      <c r="F32" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 1, 2</t>
-        </is>
-      </c>
-      <c r="G32" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H32" s="30" t="inlineStr">
-        <is>
-          <t>7 8 10 11 15</t>
-        </is>
-      </c>
-      <c r="I32" s="36" t="inlineStr">
-        <is>
-          <t>подключение к сети — ЭОМ</t>
-        </is>
-      </c>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="29" t="n"/>
     </row>
     <row r="33" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A33" s="30" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>Установка бака мембранного для ГВС 12 л</t>
+          <t>Установка насосов циркуляционных ГВС Н8, Н9 с подключением</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -1900,12 +1900,16 @@
         </is>
       </c>
       <c r="D33" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="33" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
+        <is>
+          <t>1 + 1 = 2</t>
+        </is>
+      </c>
       <c r="F33" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 8, 11; И05.09.26-ВК.СО, поз. 3</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 1, 2</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -1915,10 +1919,14 @@
       </c>
       <c r="H33" s="30" t="inlineStr">
         <is>
-          <t>8 11 15</t>
-        </is>
-      </c>
-      <c r="I33" s="36" t="n"/>
+          <t>7 8 10 11 15</t>
+        </is>
+      </c>
+      <c r="I33" s="36" t="inlineStr">
+        <is>
+          <t>подключение к сети — ЭОМ</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A34" s="30" t="inlineStr">
@@ -1928,7 +1936,7 @@
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>Установка группы безопасности бойлера Б2</t>
+          <t>Установка бака мембранного для ГВС 12 л</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -1942,141 +1950,141 @@
       <c r="E34" s="33" t="n"/>
       <c r="F34" s="34" t="inlineStr">
         <is>
+          <t>И05.09.26-ВК, см. листы 8, 11; И05.09.26-ВК.СО, поз. 3</t>
+        </is>
+      </c>
+      <c r="G34" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H34" s="30" t="inlineStr">
+        <is>
+          <t>8 11 15</t>
+        </is>
+      </c>
+      <c r="I34" s="36" t="n"/>
+    </row>
+    <row r="35" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>Установка группы безопасности бойлера Б2</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="33" t="n"/>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
           <t>И05.09.26-ВК, см. листы 8, 11; И05.09.26-ВК.СО, поз. 4</t>
         </is>
       </c>
-      <c r="G34" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H34" s="30" t="inlineStr">
+      <c r="G35" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H35" s="30" t="inlineStr">
         <is>
           <t>8 11 15</t>
         </is>
       </c>
-      <c r="I34" s="36" t="n"/>
-    </row>
-    <row r="35" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B35" s="31" t="inlineStr">
+      <c r="I35" s="36" t="n"/>
+    </row>
+    <row r="36" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>Установка полотенцесушителей водяных на Т4 с комплектами запорных клапанов</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C36" s="32" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D35" s="32" t="n">
+      <c r="D36" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="E35" s="33" t="inlineStr">
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>1 + 1 + 2 + 1 = 5</t>
         </is>
       </c>
-      <c r="F35" s="34" t="inlineStr">
+      <c r="F36" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 5, 6, 7, 8</t>
         </is>
       </c>
-      <c r="G35" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H35" s="30" t="inlineStr">
+      <c r="G36" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>5 8 10 11 15</t>
         </is>
       </c>
-      <c r="I35" s="36" t="inlineStr">
+      <c r="I36" s="36" t="inlineStr">
         <is>
           <t>5 шт.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A36" s="27" t="inlineStr">
+    <row r="37" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>Система бытовой канализации К1</t>
         </is>
       </c>
-      <c r="B36" s="28" t="n"/>
-      <c r="C36" s="28" t="n"/>
-      <c r="D36" s="28" t="n"/>
-      <c r="E36" s="28" t="n"/>
-      <c r="F36" s="28" t="n"/>
-      <c r="G36" s="28" t="n"/>
-      <c r="H36" s="28" t="n"/>
-      <c r="I36" s="29" t="n"/>
-    </row>
-    <row r="37" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка трубопроводов из ПП канализационных труб Ø110 внутри здания (стояки, под потолком гаража, вытяжные части) с фасонными частями</t>
-        </is>
-      </c>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="B37" s="28" t="n"/>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="28" t="n"/>
+      <c r="H37" s="28" t="n"/>
+      <c r="I37" s="29" t="n"/>
+    </row>
+    <row r="38" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø110 (стояк Ст.К1-1 с вытяжной частью, сборный под потолком гаража) с фасонными частями</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D37" s="32" t="n">
-        <v>28</v>
-      </c>
-      <c r="E37" s="33" t="n"/>
-      <c r="F37" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 33, 53</t>
-        </is>
-      </c>
-      <c r="G37" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H37" s="30" t="inlineStr">
-        <is>
-          <t>5 6 9 12 16 17</t>
-        </is>
-      </c>
-      <c r="I37" s="36" t="n"/>
-    </row>
-    <row r="38" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A38" s="30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B38" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 внутри здания с фасонными частями</t>
-        </is>
-      </c>
-      <c r="C38" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
       <c r="D38" s="32" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E38" s="33" t="n"/>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 34, 54</t>
+          <t>И05.09.26-ВК, см. листы 5, 12; И05.09.26-ВК.СО, поз. 33, 55</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -2086,12 +2094,12 @@
       </c>
       <c r="H38" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 12 16 17</t>
+          <t>5 12 16 17</t>
         </is>
       </c>
       <c r="I38" s="36" t="n"/>
     </row>
-    <row r="39" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="39" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A39" s="30" t="inlineStr">
         <is>
           <t>31</t>
@@ -2099,7 +2107,7 @@
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП канализационных труб Ø32 (конденсат) с фасонными частями</t>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø50 (отводы от приборов 2 этажа) с фасонными частями</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -2108,12 +2116,12 @@
         </is>
       </c>
       <c r="D39" s="32" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E39" s="33" t="n"/>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 12; И05.09.26-ВК.СО, поз. 36</t>
+          <t>И05.09.26-ВК, см. листы 5, 12; И05.09.26-ВК.СО, поз. 34, 56</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -2123,7 +2131,7 @@
       </c>
       <c r="H39" s="30" t="inlineStr">
         <is>
-          <t>5 12 16</t>
+          <t>5 12 16 17</t>
         </is>
       </c>
       <c r="I39" s="36" t="n"/>
@@ -2136,7 +2144,7 @@
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 в грунте под плитой на песчаном основании</t>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø32 (конденсат на 2 этаже) с фасонными частями</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -2145,12 +2153,12 @@
         </is>
       </c>
       <c r="D40" s="32" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 35</t>
+          <t>И05.09.26-ВК, см. листы 5, 12; И05.09.26-ВК.СО, поз. 35, 57</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2160,16 +2168,12 @@
       </c>
       <c r="H40" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 14 16</t>
-        </is>
-      </c>
-      <c r="I40" s="36" t="inlineStr">
-        <is>
-          <t>вариант А (п. 18.38 — решение Заказчика)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>5 12 16 17</t>
+        </is>
+      </c>
+      <c r="I40" s="36" t="n"/>
+    </row>
+    <row r="41" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="30" t="inlineStr">
         <is>
           <t>33</t>
@@ -2177,7 +2181,7 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП наружных труб Ø110 SN8 в грунте под плитой на песчаном основании с фасонными частями</t>
+          <t>Прокладка трубопроводов из ПП канализационных труб Ø110 внутри здания (баня: стояк с вытяжной частью; подъёмы к приборам 1 этажа) с фасонными частями</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -2186,12 +2190,12 @@
         </is>
       </c>
       <c r="D41" s="32" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 37</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12; И05.09.26-ВК.СО, поз. 36, 61</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -2201,14 +2205,10 @@
       </c>
       <c r="H41" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 14 16</t>
-        </is>
-      </c>
-      <c r="I41" s="36" t="inlineStr">
-        <is>
-          <t>в т. ч. выпуски до границы с НВК</t>
-        </is>
-      </c>
+          <t>6 9 12 16 17</t>
+        </is>
+      </c>
+      <c r="I41" s="36" t="n"/>
     </row>
     <row r="42" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A42" s="30" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>Устройство песчаного основания 100 мм и обсыпки 300 мм над верхом трубы с ручным уплотнением</t>
+          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 внутри здания с фасонными частями</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -2227,16 +2227,12 @@
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>61</v>
-      </c>
-      <c r="E42" s="33" t="inlineStr">
-        <is>
-          <t>24 + 37 = 61</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 35, 37</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 37, 62</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -2246,16 +2242,12 @@
       </c>
       <c r="H42" s="30" t="inlineStr">
         <is>
-          <t>14 16</t>
-        </is>
-      </c>
-      <c r="I42" s="36" t="inlineStr">
-        <is>
-          <t>до бетонирования плиты</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>5 6 9 12 16 17</t>
+        </is>
+      </c>
+      <c r="I42" s="36" t="n"/>
+    </row>
+    <row r="43" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A43" s="30" t="inlineStr">
         <is>
           <t>35</t>
@@ -2263,21 +2255,21 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>Установка футляров Ø160 SN8 на выпусках под краем плиты</t>
+          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 в грунте под плитой на песчаном основании</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E43" s="33" t="n"/>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 38</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 38</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -2287,94 +2279,102 @@
       </c>
       <c r="H43" s="30" t="inlineStr">
         <is>
+          <t>6 9 12 14 16</t>
+        </is>
+      </c>
+      <c r="I43" s="36" t="inlineStr">
+        <is>
+          <t>под плитой — решение Заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка трубопроводов из ПП наружных труб Ø110 SN8 в грунте под плитой на песчаном основании с фасонными частями</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="n">
+        <v>37</v>
+      </c>
+      <c r="E44" s="33" t="n"/>
+      <c r="F44" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 39</t>
+        </is>
+      </c>
+      <c r="G44" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H44" s="30" t="inlineStr">
+        <is>
+          <t>6 9 12 14 16</t>
+        </is>
+      </c>
+      <c r="I44" s="36" t="inlineStr">
+        <is>
+          <t>в т. ч. выпуски до границы с НВК</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A45" s="30" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>Устройство песчаного основания 100 мм и обсыпки 300 мм над верхом трубы с ручным уплотнением</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="n">
+        <v>61</v>
+      </c>
+      <c r="E45" s="33" t="inlineStr">
+        <is>
+          <t>24 + 37 = 61</t>
+        </is>
+      </c>
+      <c r="F45" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 38, 39</t>
+        </is>
+      </c>
+      <c r="G45" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H45" s="30" t="inlineStr">
+        <is>
           <t>14 16</t>
         </is>
       </c>
-      <c r="I43" s="36" t="inlineStr">
-        <is>
-          <t>узел 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="inlineStr">
-        <is>
-          <t>Установка тройников косых ПП</t>
-        </is>
-      </c>
-      <c r="C44" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D44" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="E44" s="33" t="inlineStr">
-        <is>
-          <t>5 + 6 + 1 + 1 + 2 = 15</t>
-        </is>
-      </c>
-      <c r="F44" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12; И05.09.26-ВК.СО, поз. 56, 57, 58, 59, 60</t>
-        </is>
-      </c>
-      <c r="G44" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H44" s="30" t="inlineStr">
-        <is>
-          <t>6 9 12 17</t>
-        </is>
-      </c>
-      <c r="I44" s="36" t="n"/>
-    </row>
-    <row r="45" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A45" s="30" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>Установка ревизий ПП Ø110</t>
-        </is>
-      </c>
-      <c r="C45" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D45" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="33" t="n"/>
-      <c r="F45" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 61</t>
-        </is>
-      </c>
-      <c r="G45" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H45" s="30" t="inlineStr">
-        <is>
-          <t>5 6 12 17</t>
-        </is>
-      </c>
-      <c r="I45" s="36" t="n"/>
-    </row>
-    <row r="46" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="I45" s="36" t="inlineStr">
+        <is>
+          <t>до бетонирования плиты</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A46" s="30" t="inlineStr">
         <is>
           <t>38</t>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>Устройство прочисток в грунте с выводом к люку в полу (тройник, отвод, стояк, заглушка, гильза, люк)</t>
+          <t>Установка футляров Ø160 SN8 на выпусках под краем плиты</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       <c r="E46" s="33" t="n"/>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 84</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 40</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="H46" s="30" t="inlineStr">
         <is>
-          <t>6 9 14 18</t>
+          <t>14 16</t>
         </is>
       </c>
       <c r="I46" s="36" t="inlineStr">
         <is>
-          <t>узел 5 листа 14</t>
+          <t>узел 2</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>Установка трапов с сухим затвором</t>
+          <t>Установка тройников косых канализационных</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -2432,16 +2432,16 @@
         </is>
       </c>
       <c r="D47" s="32" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E47" s="33" t="inlineStr">
         <is>
-          <t>2 + 1 + 1 = 4</t>
+          <t>3 + 1 + 2 + 2 + 6 + 1 = 15</t>
         </is>
       </c>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 77, 78, 79</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 58, 59, 60, 63, 64, 65</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H47" s="30" t="inlineStr">
         <is>
-          <t>4 6 9 18</t>
+          <t>5 6 9 12 17</t>
         </is>
       </c>
       <c r="I47" s="36" t="n"/>
     </row>
-    <row r="48" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="48" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A48" s="30" t="inlineStr">
         <is>
           <t>40</t>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>Установка сифонов конденсата, сифона стиральной машины и воронки с разрывом струи</t>
+          <t>Установка ревизий Ø110</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -2473,16 +2473,12 @@
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E48" s="33" t="inlineStr">
-        <is>
-          <t>3 + 1 + 1 = 5</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E48" s="33" t="n"/>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 80, 81, 82</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 66</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -2492,14 +2488,10 @@
       </c>
       <c r="H48" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 14 18</t>
-        </is>
-      </c>
-      <c r="I48" s="36" t="inlineStr">
-        <is>
-          <t>узел 7 листа 14</t>
-        </is>
-      </c>
+          <t>5 6 12 17</t>
+        </is>
+      </c>
+      <c r="I48" s="36" t="n"/>
     </row>
     <row r="49" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A49" s="30" t="inlineStr">
@@ -2509,7 +2501,7 @@
       </c>
       <c r="B49" s="31" t="inlineStr">
         <is>
-          <t>Установка проходных кровельных элементов для вытяжных частей стояков Ø110</t>
+          <t>Устройство прочисток в грунте с выводом к люку в полу (тройник, отвод, стояк, заглушка, гильза, люк)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -2523,7 +2515,7 @@
       <c r="E49" s="33" t="n"/>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 83</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 92</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2533,12 +2525,12 @@
       </c>
       <c r="H49" s="30" t="inlineStr">
         <is>
-          <t>12 14 18</t>
+          <t>6 9 14 18</t>
         </is>
       </c>
       <c r="I49" s="36" t="inlineStr">
         <is>
-          <t>узел 6 листа 14</t>
+          <t>узел 5 листа 14</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2542,7 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>Крепление трубопроводов К1 хомутами с резиновым вкладышем</t>
+          <t>Установка трапов с сухим затвором</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -2559,16 +2551,16 @@
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="E50" s="33" t="inlineStr">
         <is>
-          <t>23 + 2 + 32 = 57</t>
+          <t>2 + 1 + 1 = 4</t>
         </is>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 104, 105, 106</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 85, 86, 87</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2578,49 +2570,79 @@
       </c>
       <c r="H50" s="30" t="inlineStr">
         <is>
-          <t>5 14 18 19</t>
+          <t>4 6 9 18</t>
         </is>
       </c>
       <c r="I50" s="36" t="n"/>
     </row>
-    <row r="51" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A51" s="27" t="inlineStr">
-        <is>
-          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
-        </is>
-      </c>
-      <c r="B51" s="28" t="n"/>
-      <c r="C51" s="28" t="n"/>
-      <c r="D51" s="28" t="n"/>
-      <c r="E51" s="28" t="n"/>
-      <c r="F51" s="28" t="n"/>
-      <c r="G51" s="28" t="n"/>
-      <c r="H51" s="28" t="n"/>
-      <c r="I51" s="29" t="n"/>
-    </row>
-    <row r="52" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="51" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>Установка сифонов конденсата, сифона стиральной машины и воронки с разрывом струи</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" s="33" t="inlineStr">
+        <is>
+          <t>3 + 1 + 1 = 5</t>
+        </is>
+      </c>
+      <c r="F51" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 88, 89, 90</t>
+        </is>
+      </c>
+      <c r="G51" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H51" s="30" t="inlineStr">
+        <is>
+          <t>5 6 9 14 18</t>
+        </is>
+      </c>
+      <c r="I51" s="36" t="inlineStr">
+        <is>
+          <t>узел 7 листа 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A52" s="30" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B52" s="31" t="inlineStr">
         <is>
-          <t>Установка унитазов подвесных с инсталляциями</t>
+          <t>Установка проходных кровельных элементов для вытяжных частей стояков Ø110</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D52" s="32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" s="33" t="n"/>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 71</t>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 91</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2630,34 +2652,42 @@
       </c>
       <c r="H52" s="30" t="inlineStr">
         <is>
-          <t>3 5 6 8 9 17</t>
-        </is>
-      </c>
-      <c r="I52" s="36" t="n"/>
-    </row>
-    <row r="53" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>12 14 18</t>
+        </is>
+      </c>
+      <c r="I52" s="36" t="inlineStr">
+        <is>
+          <t>узел 6 листа 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="30" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B53" s="31" t="inlineStr">
         <is>
-          <t>Установка умывальников со смесителями и сифонами</t>
+          <t>Крепление трубопроводов К1 хомутами с резиновым вкладышем</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D53" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" s="33" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="E53" s="33" t="inlineStr">
+        <is>
+          <t>23 + 2 + 32 = 57</t>
+        </is>
+      </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 72</t>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 112, 113, 114</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -2667,47 +2697,25 @@
       </c>
       <c r="H53" s="30" t="inlineStr">
         <is>
-          <t>3 5 8 17</t>
+          <t>5 14 19</t>
         </is>
       </c>
       <c r="I53" s="36" t="n"/>
     </row>
-    <row r="54" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A54" s="30" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B54" s="31" t="inlineStr">
-        <is>
-          <t>Установка ванн со смесителями и сифонами</t>
-        </is>
-      </c>
-      <c r="C54" s="32" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="D54" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E54" s="33" t="n"/>
-      <c r="F54" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 73</t>
-        </is>
-      </c>
-      <c r="G54" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H54" s="30" t="inlineStr">
-        <is>
-          <t>5 8 17</t>
-        </is>
-      </c>
-      <c r="I54" s="36" t="n"/>
+    <row r="54" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
+        </is>
+      </c>
+      <c r="B54" s="28" t="n"/>
+      <c r="C54" s="28" t="n"/>
+      <c r="D54" s="28" t="n"/>
+      <c r="E54" s="28" t="n"/>
+      <c r="F54" s="28" t="n"/>
+      <c r="G54" s="28" t="n"/>
+      <c r="H54" s="28" t="n"/>
+      <c r="I54" s="29" t="n"/>
     </row>
     <row r="55" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A55" s="30" t="inlineStr">
@@ -2717,7 +2725,7 @@
       </c>
       <c r="B55" s="31" t="inlineStr">
         <is>
-          <t>Установка душевых систем, кабины, подключение трапов</t>
+          <t>Установка унитазов подвесных с инсталляциями</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -2726,12 +2734,12 @@
         </is>
       </c>
       <c r="D55" s="32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55" s="33" t="n"/>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 74</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 79</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -2741,7 +2749,7 @@
       </c>
       <c r="H55" s="30" t="inlineStr">
         <is>
-          <t>4 5 8 17</t>
+          <t>3 5 6 8 9 18</t>
         </is>
       </c>
       <c r="I55" s="36" t="n"/>
@@ -2754,7 +2762,7 @@
       </c>
       <c r="B56" s="31" t="inlineStr">
         <is>
-          <t>Установка моек кухонных со смесителями и сифонами</t>
+          <t>Установка умывальников со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -2763,12 +2771,12 @@
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56" s="33" t="n"/>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 75</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 80</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -2778,7 +2786,7 @@
       </c>
       <c r="H56" s="30" t="inlineStr">
         <is>
-          <t>3 8 17</t>
+          <t>3 5 8 18</t>
         </is>
       </c>
       <c r="I56" s="36" t="n"/>
@@ -2791,21 +2799,21 @@
       </c>
       <c r="B57" s="31" t="inlineStr">
         <is>
-          <t>Установка смесителя для наполнения СПА</t>
+          <t>Установка ванн со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D57" s="32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" s="33" t="n"/>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 76</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 81</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -2815,224 +2823,242 @@
       </c>
       <c r="H57" s="30" t="inlineStr">
         <is>
-          <t>8 17</t>
+          <t>5 8 18</t>
         </is>
       </c>
       <c r="I57" s="36" t="n"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A58" s="27" t="inlineStr">
+    <row r="58" ht="30" customHeight="1" thickBot="1">
+      <c r="A58" s="30" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>Установка душевых систем, кабины, подключение трапов</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="33" t="n"/>
+      <c r="F58" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 82</t>
+        </is>
+      </c>
+      <c r="G58" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H58" s="30" t="inlineStr">
+        <is>
+          <t>4 5 8 18</t>
+        </is>
+      </c>
+      <c r="I58" s="36" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B59" s="31" t="inlineStr">
+        <is>
+          <t>Установка моек кухонных со смесителями и сифонами</t>
+        </is>
+      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="33" t="n"/>
+      <c r="F59" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 83</t>
+        </is>
+      </c>
+      <c r="G59" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H59" s="30" t="inlineStr">
+        <is>
+          <t>3 8 18</t>
+        </is>
+      </c>
+      <c r="I59" s="36" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
+          <t>Установка смесителя для наполнения СПА</t>
+        </is>
+      </c>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="33" t="n"/>
+      <c r="F60" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 84</t>
+        </is>
+      </c>
+      <c r="G60" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H60" s="30" t="inlineStr">
+        <is>
+          <t>8 18</t>
+        </is>
+      </c>
+      <c r="I60" s="36" t="n"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>Тепловая изоляция</t>
         </is>
       </c>
-      <c r="B58" s="28" t="n"/>
-      <c r="C58" s="28" t="n"/>
-      <c r="D58" s="28" t="n"/>
-      <c r="E58" s="28" t="n"/>
-      <c r="F58" s="28" t="n"/>
-      <c r="G58" s="28" t="n"/>
-      <c r="H58" s="28" t="n"/>
-      <c r="I58" s="29" t="n"/>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="30" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B59" s="31" t="inlineStr">
+      <c r="B61" s="28" t="n"/>
+      <c r="C61" s="28" t="n"/>
+      <c r="D61" s="28" t="n"/>
+      <c r="E61" s="28" t="n"/>
+      <c r="F61" s="28" t="n"/>
+      <c r="G61" s="28" t="n"/>
+      <c r="H61" s="28" t="n"/>
+      <c r="I61" s="29" t="n"/>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
         <is>
           <t>Изоляция трубопроводов Т3, Т4 трубками из вспененного полиэтилена толщиной 13 мм</t>
         </is>
       </c>
-      <c r="C59" s="32" t="inlineStr">
+      <c r="C62" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D59" s="32" t="n">
+      <c r="D62" s="32" t="n">
         <v>159</v>
       </c>
-      <c r="E59" s="33" t="inlineStr">
+      <c r="E62" s="33" t="inlineStr">
         <is>
           <t>65 + 85 + 9 = 159</t>
         </is>
       </c>
-      <c r="F59" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 85, 86, 87</t>
-        </is>
-      </c>
-      <c r="G59" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H59" s="30" t="inlineStr">
+      <c r="F62" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 93, 94, 95</t>
+        </is>
+      </c>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H62" s="30" t="inlineStr">
         <is>
           <t>3 5 8 10 11 18</t>
         </is>
       </c>
-      <c r="I59" s="36" t="n"/>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="inlineStr">
+      <c r="I62" s="36" t="n"/>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B63" s="31" t="inlineStr">
         <is>
           <t>Изоляция трубопроводов В1 трубками из вспененного полиэтилена толщиной 9 мм</t>
         </is>
       </c>
-      <c r="C60" s="32" t="inlineStr">
+      <c r="C63" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D60" s="32" t="n">
-        <v>197</v>
-      </c>
-      <c r="E60" s="33" t="inlineStr">
-        <is>
-          <t>91 + 53 + 42 + 11 = 197</t>
-        </is>
-      </c>
-      <c r="F60" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 88, 89, 90, 91</t>
-        </is>
-      </c>
-      <c r="G60" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H60" s="30" t="inlineStr">
+      <c r="D63" s="32" t="n">
+        <v>202</v>
+      </c>
+      <c r="E63" s="33" t="inlineStr">
+        <is>
+          <t>91 + 53 + 47 + 11 = 202</t>
+        </is>
+      </c>
+      <c r="F63" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 96, 97, 98, 99</t>
+        </is>
+      </c>
+      <c r="G63" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H63" s="30" t="inlineStr">
         <is>
           <t>3 5 8 10 11 18</t>
         </is>
       </c>
-      <c r="I60" s="36" t="n"/>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="30" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B61" s="31" t="inlineStr">
-        <is>
-          <t>Изоляция ввода ПЭ 32 в проёме фундамента</t>
-        </is>
-      </c>
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D61" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" s="33" t="n"/>
-      <c r="F61" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 92</t>
-        </is>
-      </c>
-      <c r="G61" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H61" s="30" t="inlineStr">
-        <is>
-          <t>14 18</t>
-        </is>
-      </c>
-      <c r="I61" s="36" t="n"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
-        <is>
-          <t>Проходы через строительные конструкции</t>
-        </is>
-      </c>
-      <c r="B62" s="28" t="n"/>
-      <c r="C62" s="28" t="n"/>
-      <c r="D62" s="28" t="n"/>
-      <c r="E62" s="28" t="n"/>
-      <c r="F62" s="28" t="n"/>
-      <c r="G62" s="28" t="n"/>
-      <c r="H62" s="28" t="n"/>
-      <c r="I62" s="29" t="n"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="30" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B63" s="31" t="inlineStr">
-        <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
-        </is>
-      </c>
-      <c r="C63" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="E63" s="33" t="n"/>
-      <c r="F63" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 95</t>
-        </is>
-      </c>
-      <c r="G63" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H63" s="30" t="inlineStr">
-        <is>
-          <t>14 18</t>
-        </is>
-      </c>
-      <c r="I63" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
+      <c r="I63" s="36" t="n"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B64" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
+          <t>Изоляция ввода ПЭ 32 в проёме фундамента</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D64" s="32" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E64" s="33" t="n"/>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 95</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 100</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -3045,52 +3071,22 @@
           <t>14 18</t>
         </is>
       </c>
-      <c r="I64" s="36" t="inlineStr">
-        <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="30" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B65" s="31" t="inlineStr">
-        <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
-        </is>
-      </c>
-      <c r="C65" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D65" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="E65" s="33" t="n"/>
-      <c r="F65" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 96</t>
-        </is>
-      </c>
-      <c r="G65" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H65" s="30" t="inlineStr">
-        <is>
-          <t>14 18</t>
-        </is>
-      </c>
-      <c r="I65" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
+      <c r="I64" s="36" t="n"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>Проходы через строительные конструкции</t>
+        </is>
+      </c>
+      <c r="B65" s="28" t="n"/>
+      <c r="C65" s="28" t="n"/>
+      <c r="D65" s="28" t="n"/>
+      <c r="E65" s="28" t="n"/>
+      <c r="F65" s="28" t="n"/>
+      <c r="G65" s="28" t="n"/>
+      <c r="H65" s="28" t="n"/>
+      <c r="I65" s="29" t="n"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="30" t="inlineStr">
@@ -3100,7 +3096,7 @@
       </c>
       <c r="B66" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -3109,12 +3105,12 @@
         </is>
       </c>
       <c r="D66" s="32" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 96</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 103</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3129,7 +3125,7 @@
       </c>
       <c r="I66" s="36" t="inlineStr">
         <is>
-          <t>п. 11.5</t>
+          <t>по толщине конструкции</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3137,7 @@
       </c>
       <c r="B67" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
+          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -3150,12 +3146,12 @@
         </is>
       </c>
       <c r="D67" s="32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E67" s="33" t="n"/>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 97</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 103</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -3170,7 +3166,7 @@
       </c>
       <c r="I67" s="36" t="inlineStr">
         <is>
-          <t>по толщине конструкции</t>
+          <t>п. 11.5</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3178,7 @@
       </c>
       <c r="B68" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -3191,12 +3187,12 @@
         </is>
       </c>
       <c r="D68" s="32" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E68" s="33" t="n"/>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 97</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 104</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3211,11 +3207,11 @@
       </c>
       <c r="I68" s="36" t="inlineStr">
         <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="45" customHeight="1">
+          <t>по толщине конструкции</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
       <c r="A69" s="30" t="inlineStr">
         <is>
           <t>58</t>
@@ -3223,21 +3219,21 @@
       </c>
       <c r="B69" s="31" t="inlineStr">
         <is>
-          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
+          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D69" s="32" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="E69" s="33" t="n"/>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 98</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 104</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -3250,9 +3246,13 @@
           <t>14 18</t>
         </is>
       </c>
-      <c r="I69" s="36" t="n"/>
-    </row>
-    <row r="70" ht="45" customHeight="1">
+      <c r="I69" s="36" t="inlineStr">
+        <is>
+          <t>п. 11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
       <c r="A70" s="30" t="inlineStr">
         <is>
           <t>59</t>
@@ -3260,21 +3260,21 @@
       </c>
       <c r="B70" s="31" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента у ввода и выпусков эластичным водогазонепроницаемым материалом</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D70" s="32" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E70" s="33" t="n"/>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 99</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 105</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -3289,52 +3289,74 @@
       </c>
       <c r="I70" s="36" t="inlineStr">
         <is>
-          <t>проёмы — КР (ТЗ-1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="27" t="inlineStr">
-        <is>
-          <t>Испытания и пусконаладочные работы</t>
-        </is>
-      </c>
-      <c r="B71" s="28" t="n"/>
-      <c r="C71" s="28" t="n"/>
-      <c r="D71" s="28" t="n"/>
-      <c r="E71" s="28" t="n"/>
-      <c r="F71" s="28" t="n"/>
-      <c r="G71" s="28" t="n"/>
-      <c r="H71" s="28" t="n"/>
-      <c r="I71" s="29" t="n"/>
+          <t>по толщине конструкции</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
+        </is>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="E71" s="33" t="n"/>
+      <c r="F71" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 105</t>
+        </is>
+      </c>
+      <c r="G71" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H71" s="30" t="inlineStr">
+        <is>
+          <t>14 18</t>
+        </is>
+      </c>
+      <c r="I71" s="36" t="inlineStr">
+        <is>
+          <t>п. 11.5</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="45" customHeight="1">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B72" s="31" t="inlineStr">
         <is>
-          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
+          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D72" s="32" t="n">
-        <v>357</v>
-      </c>
-      <c r="E72" s="33" t="inlineStr">
-        <is>
-          <t>11 + 51 + 138 + 155 + 2 = 357</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E72" s="33" t="n"/>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 28, 29, 30, 31, 32</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 106</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -3344,42 +3366,34 @@
       </c>
       <c r="H72" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
-        </is>
-      </c>
-      <c r="I72" s="36" t="inlineStr">
-        <is>
-          <t>в т. ч. до закрытия в конструкциях</t>
-        </is>
-      </c>
+          <t>14 19</t>
+        </is>
+      </c>
+      <c r="I72" s="36" t="n"/>
     </row>
     <row r="73" ht="45" customHeight="1">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B73" s="31" t="inlineStr">
         <is>
-          <t>Испытание системы канализации К1 проливом воды</t>
+          <t>Заделка проёмов фундамента у ввода и выпусков эластичным водогазонепроницаемым материалом</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D73" s="32" t="n">
-        <v>113</v>
-      </c>
-      <c r="E73" s="33" t="inlineStr">
-        <is>
-          <t>28 + 23 + 24 + 1 + 37 = 113</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E73" s="33" t="n"/>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 33, 34, 35, 36, 37</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 107</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -3389,51 +3403,29 @@
       </c>
       <c r="H73" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
-        </is>
-      </c>
-      <c r="I73" s="36" t="n"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="inlineStr">
-        <is>
-          <t>Испытание трубопроводов К1 в грунте наполнением водой до засыпки</t>
-        </is>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>61</v>
-      </c>
-      <c r="E74" s="33" t="inlineStr">
-        <is>
-          <t>24 + 37 = 61</t>
-        </is>
-      </c>
-      <c r="F74" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 35, 37</t>
-        </is>
-      </c>
-      <c r="G74" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H74" s="30" t="inlineStr">
-        <is>
-          <t>2 14 16</t>
-        </is>
-      </c>
-      <c r="I74" s="36" t="n"/>
+          <t>14 19</t>
+        </is>
+      </c>
+      <c r="I73" s="36" t="inlineStr">
+        <is>
+          <t>проёмы — КР (ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>Испытания и пусконаладочные работы</t>
+        </is>
+      </c>
+      <c r="B74" s="28" t="n"/>
+      <c r="C74" s="28" t="n"/>
+      <c r="D74" s="28" t="n"/>
+      <c r="E74" s="28" t="n"/>
+      <c r="F74" s="28" t="n"/>
+      <c r="G74" s="28" t="n"/>
+      <c r="H74" s="28" t="n"/>
+      <c r="I74" s="29" t="n"/>
     </row>
     <row r="75" ht="45" customHeight="1">
       <c r="A75" s="30" t="inlineStr">
@@ -3443,7 +3435,7 @@
       </c>
       <c r="B75" s="31" t="inlineStr">
         <is>
-          <t>Промывка и дезинфекция трубопроводов систем В1, Т3, Т4</t>
+          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -3452,11 +3444,11 @@
         </is>
       </c>
       <c r="D75" s="32" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E75" s="33" t="inlineStr">
         <is>
-          <t>11 + 51 + 138 + 155 + 2 = 357</t>
+          <t>11 + 55 + 138 + 155 + 2 = 361</t>
         </is>
       </c>
       <c r="F75" s="34" t="inlineStr">
@@ -3474,9 +3466,13 @@
           <t>1 2 16</t>
         </is>
       </c>
-      <c r="I75" s="36" t="n"/>
-    </row>
-    <row r="76" ht="30" customHeight="1">
+      <c r="I75" s="36" t="inlineStr">
+        <is>
+          <t>в т. ч. до закрытия в конструкциях</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
       <c r="A76" s="30" t="inlineStr">
         <is>
           <t>64</t>
@@ -3484,21 +3480,25 @@
       </c>
       <c r="B76" s="31" t="inlineStr">
         <is>
-          <t>Наладка циркуляции ГВС: настройка балансировочных клапанов по П4</t>
+          <t>Испытание системы канализации К1 проливом воды</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D76" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E76" s="33" t="n"/>
+        <v>114</v>
+      </c>
+      <c r="E76" s="33" t="inlineStr">
+        <is>
+          <t>19 + 12 + 1 + 9 + 12 + 24 + 37 = 114</t>
+        </is>
+      </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 67</t>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 33, 34, 35, 36, 37, 38, 39</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3508,14 +3508,10 @@
       </c>
       <c r="H76" s="30" t="inlineStr">
         <is>
-          <t>13 17</t>
-        </is>
-      </c>
-      <c r="I76" s="36" t="inlineStr">
-        <is>
-          <t>П4</t>
-        </is>
-      </c>
+          <t>1 2 16</t>
+        </is>
+      </c>
+      <c r="I76" s="36" t="n"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="30" t="inlineStr">
@@ -3525,50 +3521,173 @@
       </c>
       <c r="B77" s="31" t="inlineStr">
         <is>
+          <t>Испытание трубопроводов К1 в грунте наполнением водой до засыпки</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>61</v>
+      </c>
+      <c r="E77" s="33" t="inlineStr">
+        <is>
+          <t>24 + 37 = 61</t>
+        </is>
+      </c>
+      <c r="F77" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 38, 39</t>
+        </is>
+      </c>
+      <c r="G77" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>2 14 16</t>
+        </is>
+      </c>
+      <c r="I77" s="36" t="n"/>
+    </row>
+    <row r="78" ht="45" customHeight="1">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="inlineStr">
+        <is>
+          <t>Промывка и дезинфекция трубопроводов систем В1, Т3, Т4</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>361</v>
+      </c>
+      <c r="E78" s="33" t="inlineStr">
+        <is>
+          <t>11 + 55 + 138 + 155 + 2 = 361</t>
+        </is>
+      </c>
+      <c r="F78" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 28, 29, 30, 31, 32</t>
+        </is>
+      </c>
+      <c r="G78" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H78" s="30" t="inlineStr">
+        <is>
+          <t>1 2 16</t>
+        </is>
+      </c>
+      <c r="I78" s="36" t="n"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="30" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B79" s="31" t="inlineStr">
+        <is>
+          <t>Наладка циркуляции ГВС: настройка балансировочных клапанов по П4</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="33" t="n"/>
+      <c r="F79" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 75</t>
+        </is>
+      </c>
+      <c r="G79" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H79" s="30" t="inlineStr">
+        <is>
+          <t>13 17</t>
+        </is>
+      </c>
+      <c r="I79" s="36" t="inlineStr">
+        <is>
+          <t>П4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="30" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B80" s="31" t="inlineStr">
+        <is>
           <t>Пусконаладочные работы циркуляционных насосов Н8, Н9</t>
         </is>
       </c>
-      <c r="C77" s="32" t="inlineStr">
+      <c r="C80" s="32" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D77" s="32" t="n">
+      <c r="D80" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="33" t="inlineStr">
+      <c r="E80" s="33" t="inlineStr">
         <is>
           <t>1 + 1 = 2</t>
         </is>
       </c>
-      <c r="F77" s="34" t="inlineStr">
+      <c r="F80" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 7, 8; И05.09.26-ВК.СО, поз. 1, 2</t>
         </is>
       </c>
-      <c r="G77" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="G80" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H80" s="30" t="inlineStr">
         <is>
           <t>7 8 15</t>
         </is>
       </c>
-      <c r="I77" s="36" t="n"/>
+      <c r="I80" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A74:I74"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A51:I51"/>
-    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A61:I61"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="55" fitToHeight="0" fitToWidth="1"/>
@@ -3581,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -3632,7 +3751,14 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="38" t="inlineStr">
         <is>
-          <t>6. Прокладка К1 под плитой принята по варианту А до решения Заказчика (п. 18.38 СП 30.13330.2020); при варианте Б объёмы раздела К1 уточняются.</t>
+          <t>6. Сети К1 первого этажа дома и бани — в грунте под плитой пола по решению Заказчика (плита пола не забетонирована).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>7. Система автополива участка (трассы, клапаны, контроллер) — по ландшафтному проекту; в ведомости — подводка КХ-8.</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -863,7 +863,7 @@
       <c r="E5" s="33" t="n"/>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 54</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 53</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 41, 42, 43</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 40, 41, 42</t>
         </is>
       </c>
       <c r="G16" s="35" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="F17" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 44, 45, 46, 47</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 43, 44, 45, 46</t>
         </is>
       </c>
       <c r="G17" s="35" t="inlineStr">
@@ -1362,7 +1362,7 @@
       <c r="E18" s="33" t="n"/>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 48</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 47</t>
         </is>
       </c>
       <c r="G18" s="35" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 49, 50, 51, 52</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 48, 49, 50, 51</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -1440,7 +1440,7 @@
       <c r="E20" s="33" t="n"/>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 53</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 52</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 101, 102</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 108, 109</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H21" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 18</t>
+          <t>3 4 5 8 19</t>
         </is>
       </c>
       <c r="I21" s="36" t="n"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 108, 109, 110, 111</t>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 115, 116, 117, 118</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -1563,7 +1563,7 @@
       <c r="E23" s="33" t="n"/>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 115</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 122</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -1610,16 +1610,16 @@
         </is>
       </c>
       <c r="D25" s="32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="33" t="inlineStr">
         <is>
-          <t>2 + 3 = 5</t>
+          <t>2 + 1 + 3 = 6</t>
         </is>
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 69, 70</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 68, 69, 97</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="H25" s="30" t="inlineStr">
         <is>
-          <t>7 8 10 11 17</t>
+          <t>7 8 10 11 17 18</t>
         </is>
       </c>
       <c r="I25" s="36" t="n"/>
@@ -1656,7 +1656,7 @@
       <c r="E26" s="33" t="n"/>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 71</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 70</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -1693,7 +1693,7 @@
       <c r="E27" s="33" t="n"/>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 75</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 74</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>Установка кранов поливочных незамерзающих с выносом через стену</t>
+          <t>Установка кранов поливочных (сезонных) с выносом через стену</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -1734,7 +1734,7 @@
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 76</t>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 75</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1771,7 +1771,7 @@
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 77</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 76</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 72, 73, 74</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 71, 72, 73</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1853,7 +1853,7 @@
       <c r="E31" s="33" t="n"/>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 78</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 77</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из малошумных канализационных труб Ø110 (стояк Ст.К1-1 с вытяжной частью, сборный под потолком гаража) с фасонными частями</t>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø110 (стояки с вытяжными частями, сборный под потолком гаража, подъёмы к приборам) с фасонными частями</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -2079,12 +2079,12 @@
         </is>
       </c>
       <c r="D38" s="32" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E38" s="33" t="n"/>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 12; И05.09.26-ВК.СО, поз. 33, 55</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 33, 54</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="H38" s="30" t="inlineStr">
         <is>
-          <t>5 12 16 17</t>
+          <t>5 6 9 12 16 17</t>
         </is>
       </c>
       <c r="I38" s="36" t="n"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из малошумных канализационных труб Ø50 (отводы от приборов 2 этажа) с фасонными частями</t>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø50 (отводы и подъёмы к приборам) с фасонными частями</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -2116,12 +2116,12 @@
         </is>
       </c>
       <c r="D39" s="32" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E39" s="33" t="n"/>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 12; И05.09.26-ВК.СО, поз. 34, 56</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 34, 55</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="H39" s="30" t="inlineStr">
         <is>
-          <t>5 12 16 17</t>
+          <t>5 6 9 12 16 17</t>
         </is>
       </c>
       <c r="I39" s="36" t="n"/>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из малошумных канализационных труб Ø32 (конденсат на 2 этаже) с фасонными частями</t>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø32 (конденсат кондиционеров) с фасонными частями</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -2158,7 +2158,7 @@
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 12; И05.09.26-ВК.СО, поз. 35, 57</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 35, 56</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="H40" s="30" t="inlineStr">
         <is>
-          <t>5 12 16 17</t>
+          <t>5 6 9 12 16 17</t>
         </is>
       </c>
       <c r="I40" s="36" t="n"/>
     </row>
-    <row r="41" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="41" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="30" t="inlineStr">
         <is>
           <t>33</t>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП канализационных труб Ø110 внутри здания (баня: стояк с вытяжной частью; подъёмы к приборам 1 этажа) с фасонными частями</t>
+          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 в грунте под плитой на песчаном основании</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -2190,12 +2190,12 @@
         </is>
       </c>
       <c r="D41" s="32" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12; И05.09.26-ВК.СО, поз. 36, 61</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 36</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -2205,12 +2205,16 @@
       </c>
       <c r="H41" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 16 17</t>
-        </is>
-      </c>
-      <c r="I41" s="36" t="n"/>
-    </row>
-    <row r="42" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>6 9 12 14 16</t>
+        </is>
+      </c>
+      <c r="I41" s="36" t="inlineStr">
+        <is>
+          <t>под плитой — решение Заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A42" s="30" t="inlineStr">
         <is>
           <t>34</t>
@@ -2218,7 +2222,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 внутри здания с фасонными частями</t>
+          <t>Прокладка трубопроводов из ПП наружных труб Ø110 SN8 в грунте под плитой на песчаном основании с фасонными частями</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -2227,12 +2231,12 @@
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 37, 62</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 37</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -2242,10 +2246,14 @@
       </c>
       <c r="H42" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 12 16 17</t>
-        </is>
-      </c>
-      <c r="I42" s="36" t="n"/>
+          <t>6 9 12 14 16</t>
+        </is>
+      </c>
+      <c r="I42" s="36" t="inlineStr">
+        <is>
+          <t>в т. ч. выпуски до границы с НВК</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A43" s="30" t="inlineStr">
@@ -2255,7 +2263,7 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 в грунте под плитой на песчаном основании</t>
+          <t>Устройство песчаного основания 100 мм и обсыпки 300 мм над верхом трубы с ручным уплотнением</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -2264,12 +2272,16 @@
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>24</v>
-      </c>
-      <c r="E43" s="33" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="E43" s="33" t="inlineStr">
+        <is>
+          <t>25 + 37 + 3 = 65</t>
+        </is>
+      </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 38</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 36, 37, 38</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -2279,16 +2291,16 @@
       </c>
       <c r="H43" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 14 16</t>
+          <t>14 16</t>
         </is>
       </c>
       <c r="I43" s="36" t="inlineStr">
         <is>
-          <t>под плитой — решение Заказчика</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>до бетонирования плиты</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="30" t="inlineStr">
         <is>
           <t>36</t>
@@ -2296,21 +2308,21 @@
       </c>
       <c r="B44" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП наружных труб Ø110 SN8 в грунте под плитой на песчаном основании с фасонными частями</t>
+          <t>Установка футляров Ø160 SN8 на выпусках под краем плиты</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D44" s="32" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E44" s="33" t="n"/>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 39</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 39</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -2320,12 +2332,12 @@
       </c>
       <c r="H44" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 14 16</t>
+          <t>14 16</t>
         </is>
       </c>
       <c r="I44" s="36" t="inlineStr">
         <is>
-          <t>в т. ч. выпуски до границы с НВК</t>
+          <t>узел 2</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2349,7 @@
       </c>
       <c r="B45" s="31" t="inlineStr">
         <is>
-          <t>Устройство песчаного основания 100 мм и обсыпки 300 мм над верхом трубы с ручным уплотнением</t>
+          <t>Прокладка трубопровода К2 Ø110 SN8 от пескоуловителя гаража под плитой на песчаном основании</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -2346,16 +2358,12 @@
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>61</v>
-      </c>
-      <c r="E45" s="33" t="inlineStr">
-        <is>
-          <t>24 + 37 = 61</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E45" s="33" t="n"/>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 38, 39</t>
+          <t>И05.09.26-ВК, см. листы 4, 14; И05.09.26-ВК.СО, поз. 38</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -2365,12 +2373,12 @@
       </c>
       <c r="H45" s="30" t="inlineStr">
         <is>
-          <t>14 16</t>
+          <t>4 14 16</t>
         </is>
       </c>
       <c r="I45" s="36" t="inlineStr">
         <is>
-          <t>до бетонирования плиты</t>
+          <t>до границы с НВК (ливневая сеть)</t>
         </is>
       </c>
     </row>
@@ -2382,21 +2390,21 @@
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>Установка футляров Ø160 SN8 на выпусках под краем плиты</t>
+          <t>Устройство лотка водоотводного DN100 с решёткой C250 в полу гаража</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="E46" s="33" t="n"/>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 40</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 93</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -2406,16 +2414,16 @@
       </c>
       <c r="H46" s="30" t="inlineStr">
         <is>
-          <t>14 16</t>
+          <t>4 18</t>
         </is>
       </c>
       <c r="I46" s="36" t="inlineStr">
         <is>
-          <t>узел 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>углубление в стяжке — АР/КР (ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="30" t="inlineStr">
         <is>
           <t>39</t>
@@ -2423,85 +2431,89 @@
       </c>
       <c r="B47" s="31" t="inlineStr">
         <is>
+          <t>Установка пескоуловителя DN100 с корзиной</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="33" t="n"/>
+      <c r="F47" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 94</t>
+        </is>
+      </c>
+      <c r="G47" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H47" s="30" t="inlineStr">
+        <is>
+          <t>4 18</t>
+        </is>
+      </c>
+      <c r="I47" s="36" t="inlineStr">
+        <is>
+          <t>понижение плиты — КР (ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
           <t>Установка тройников косых канализационных</t>
         </is>
       </c>
-      <c r="C47" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D47" s="32" t="n">
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="E47" s="33" t="inlineStr">
+      <c r="E48" s="33" t="inlineStr">
         <is>
           <t>3 + 1 + 2 + 2 + 6 + 1 = 15</t>
         </is>
       </c>
-      <c r="F47" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 58, 59, 60, 63, 64, 65</t>
-        </is>
-      </c>
-      <c r="G47" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H47" s="30" t="inlineStr">
+      <c r="F48" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 57, 58, 59, 62, 63, 64</t>
+        </is>
+      </c>
+      <c r="G48" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H48" s="30" t="inlineStr">
         <is>
           <t>5 6 9 12 17</t>
         </is>
       </c>
-      <c r="I47" s="36" t="n"/>
-    </row>
-    <row r="48" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A48" s="30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B48" s="31" t="inlineStr">
+      <c r="I48" s="36" t="n"/>
+    </row>
+    <row r="49" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="inlineStr">
         <is>
           <t>Установка ревизий Ø110</t>
-        </is>
-      </c>
-      <c r="C48" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D48" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E48" s="33" t="n"/>
-      <c r="F48" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 66</t>
-        </is>
-      </c>
-      <c r="G48" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H48" s="30" t="inlineStr">
-        <is>
-          <t>5 6 12 17</t>
-        </is>
-      </c>
-      <c r="I48" s="36" t="n"/>
-    </row>
-    <row r="49" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>Устройство прочисток в грунте с выводом к люку в полу (тройник, отвод, стояк, заглушка, гильза, люк)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -2515,7 +2527,7 @@
       <c r="E49" s="33" t="n"/>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 92</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 65</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2525,14 +2537,10 @@
       </c>
       <c r="H49" s="30" t="inlineStr">
         <is>
-          <t>6 9 14 18</t>
-        </is>
-      </c>
-      <c r="I49" s="36" t="inlineStr">
-        <is>
-          <t>узел 5 листа 14</t>
-        </is>
-      </c>
+          <t>5 6 12 17</t>
+        </is>
+      </c>
+      <c r="I49" s="36" t="n"/>
     </row>
     <row r="50" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="30" t="inlineStr">
@@ -2542,7 +2550,7 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>Установка трапов с сухим затвором</t>
+          <t>Устройство прочисток в грунте с выводом к люку в полу (тройник, отвод, стояк, заглушка, гильза, люк)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -2551,16 +2559,12 @@
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" s="33" t="inlineStr">
-        <is>
-          <t>2 + 1 + 1 = 4</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E50" s="33" t="n"/>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 85, 86, 87</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 92</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2570,10 +2574,14 @@
       </c>
       <c r="H50" s="30" t="inlineStr">
         <is>
-          <t>4 6 9 18</t>
-        </is>
-      </c>
-      <c r="I50" s="36" t="n"/>
+          <t>6 9 14 18</t>
+        </is>
+      </c>
+      <c r="I50" s="36" t="inlineStr">
+        <is>
+          <t>узел 5 листа 14</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A51" s="30" t="inlineStr">
@@ -2583,7 +2591,7 @@
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>Установка сифонов конденсата, сифона стиральной машины и воронки с разрывом струи</t>
+          <t>Установка трапов с сухим затвором</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -2596,12 +2604,12 @@
       </c>
       <c r="E51" s="33" t="inlineStr">
         <is>
-          <t>3 + 1 + 1 = 5</t>
+          <t>2 + 1 + 1 + 1 = 5</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 88, 89, 90</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 84, 85, 86, 87</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -2611,14 +2619,10 @@
       </c>
       <c r="H51" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 14 18</t>
-        </is>
-      </c>
-      <c r="I51" s="36" t="inlineStr">
-        <is>
-          <t>узел 7 листа 14</t>
-        </is>
-      </c>
+          <t>4 6 9 18</t>
+        </is>
+      </c>
+      <c r="I51" s="36" t="n"/>
     </row>
     <row r="52" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A52" s="30" t="inlineStr">
@@ -2628,7 +2632,7 @@
       </c>
       <c r="B52" s="31" t="inlineStr">
         <is>
-          <t>Установка проходных кровельных элементов для вытяжных частей стояков Ø110</t>
+          <t>Установка сифонов конденсата, сифона стиральной машины и воронки с разрывом струи</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -2637,12 +2641,16 @@
         </is>
       </c>
       <c r="D52" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="33" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="E52" s="33" t="inlineStr">
+        <is>
+          <t>3 + 1 + 1 = 5</t>
+        </is>
+      </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 91</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 88, 89, 90</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2652,12 +2660,12 @@
       </c>
       <c r="H52" s="30" t="inlineStr">
         <is>
-          <t>12 14 18</t>
+          <t>5 6 9 14 18</t>
         </is>
       </c>
       <c r="I52" s="36" t="inlineStr">
         <is>
-          <t>узел 6 листа 14</t>
+          <t>узел 7 листа 14</t>
         </is>
       </c>
     </row>
@@ -2669,92 +2677,96 @@
       </c>
       <c r="B53" s="31" t="inlineStr">
         <is>
+          <t>Установка проходных кровельных элементов для вытяжных частей стояков Ø110</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="33" t="n"/>
+      <c r="F53" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 91</t>
+        </is>
+      </c>
+      <c r="G53" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H53" s="30" t="inlineStr">
+        <is>
+          <t>12 14 18</t>
+        </is>
+      </c>
+      <c r="I53" s="36" t="inlineStr">
+        <is>
+          <t>узел 6 листа 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="inlineStr">
+        <is>
           <t>Крепление трубопроводов К1 хомутами с резиновым вкладышем</t>
         </is>
       </c>
-      <c r="C53" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D53" s="32" t="n">
-        <v>57</v>
-      </c>
-      <c r="E53" s="33" t="inlineStr">
-        <is>
-          <t>23 + 2 + 32 = 57</t>
-        </is>
-      </c>
-      <c r="F53" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 112, 113, 114</t>
-        </is>
-      </c>
-      <c r="G53" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H53" s="30" t="inlineStr">
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="E54" s="33" t="inlineStr">
+        <is>
+          <t>23 + 2 + 33 = 58</t>
+        </is>
+      </c>
+      <c r="F54" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 119, 120, 121</t>
+        </is>
+      </c>
+      <c r="G54" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H54" s="30" t="inlineStr">
         <is>
           <t>5 14 19</t>
         </is>
       </c>
-      <c r="I53" s="36" t="n"/>
-    </row>
-    <row r="54" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A54" s="27" t="inlineStr">
-        <is>
-          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
-        </is>
-      </c>
-      <c r="B54" s="28" t="n"/>
-      <c r="C54" s="28" t="n"/>
-      <c r="D54" s="28" t="n"/>
-      <c r="E54" s="28" t="n"/>
-      <c r="F54" s="28" t="n"/>
-      <c r="G54" s="28" t="n"/>
-      <c r="H54" s="28" t="n"/>
-      <c r="I54" s="29" t="n"/>
-    </row>
-    <row r="55" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A55" s="30" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B55" s="31" t="inlineStr">
-        <is>
-          <t>Установка унитазов подвесных с инсталляциями</t>
-        </is>
-      </c>
-      <c r="C55" s="32" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" s="33" t="n"/>
-      <c r="F55" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 79</t>
-        </is>
-      </c>
-      <c r="G55" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H55" s="30" t="inlineStr">
-        <is>
-          <t>3 5 6 8 9 18</t>
-        </is>
-      </c>
-      <c r="I55" s="36" t="n"/>
-    </row>
-    <row r="56" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="I54" s="36" t="n"/>
+    </row>
+    <row r="55" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>Защита от протечек</t>
+        </is>
+      </c>
+      <c r="B55" s="28" t="n"/>
+      <c r="C55" s="28" t="n"/>
+      <c r="D55" s="28" t="n"/>
+      <c r="E55" s="28" t="n"/>
+      <c r="F55" s="28" t="n"/>
+      <c r="G55" s="28" t="n"/>
+      <c r="H55" s="28" t="n"/>
+      <c r="I55" s="29" t="n"/>
+    </row>
+    <row r="56" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="30" t="inlineStr">
         <is>
           <t>47</t>
@@ -2762,21 +2774,21 @@
       </c>
       <c r="B56" s="31" t="inlineStr">
         <is>
-          <t>Установка умывальников со смесителями и сифонами</t>
+          <t>Установка контроллеров системы защиты от протечек с подключением кранов и датчиков</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" s="33" t="n"/>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 80</t>
+          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 95</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -2786,10 +2798,14 @@
       </c>
       <c r="H56" s="30" t="inlineStr">
         <is>
-          <t>3 5 8 18</t>
-        </is>
-      </c>
-      <c r="I56" s="36" t="n"/>
+          <t>2 4 8 18</t>
+        </is>
+      </c>
+      <c r="I56" s="36" t="inlineStr">
+        <is>
+          <t>питание 230 В и сигнал в умный дом — ЭОМ/СС (ТЗ-2)</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A57" s="30" t="inlineStr">
@@ -2799,21 +2815,25 @@
       </c>
       <c r="B57" s="31" t="inlineStr">
         <is>
-          <t>Установка ванн со смесителями и сифонами</t>
+          <t>Установка кранов шаровых с электроприводом Ду 20–32</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D57" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E57" s="33" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E57" s="33" t="inlineStr">
+        <is>
+          <t>1 + 1 = 2</t>
+        </is>
+      </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 81</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 96, 97</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -2823,7 +2843,7 @@
       </c>
       <c r="H57" s="30" t="inlineStr">
         <is>
-          <t>5 8 18</t>
+          <t>4 7 8 18</t>
         </is>
       </c>
       <c r="I57" s="36" t="n"/>
@@ -2836,21 +2856,21 @@
       </c>
       <c r="B58" s="31" t="inlineStr">
         <is>
-          <t>Установка душевых систем, кабины, подключение трапов</t>
+          <t>Установка датчиков протечки проводных на полу</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D58" s="32" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E58" s="33" t="n"/>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 82</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 98</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -2860,7 +2880,7 @@
       </c>
       <c r="H58" s="30" t="inlineStr">
         <is>
-          <t>4 5 8 18</t>
+          <t>3 4 5 8 18</t>
         </is>
       </c>
       <c r="I58" s="36" t="n"/>
@@ -2873,21 +2893,21 @@
       </c>
       <c r="B59" s="31" t="inlineStr">
         <is>
-          <t>Установка моек кухонных со смесителями и сифонами</t>
+          <t>Прокладка кабелей датчиков протечки в гофротрубе</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D59" s="32" t="n">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="E59" s="33" t="n"/>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 83</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 99</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -2897,64 +2917,68 @@
       </c>
       <c r="H59" s="30" t="inlineStr">
         <is>
-          <t>3 8 18</t>
-        </is>
-      </c>
-      <c r="I59" s="36" t="n"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
+          <t>3 4 5 8 18</t>
+        </is>
+      </c>
+      <c r="I59" s="36" t="inlineStr">
+        <is>
+          <t>совместно с ЭОМ/СС</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
+        </is>
+      </c>
+      <c r="B60" s="28" t="n"/>
+      <c r="C60" s="28" t="n"/>
+      <c r="D60" s="28" t="n"/>
+      <c r="E60" s="28" t="n"/>
+      <c r="F60" s="28" t="n"/>
+      <c r="G60" s="28" t="n"/>
+      <c r="H60" s="28" t="n"/>
+      <c r="I60" s="29" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B60" s="31" t="inlineStr">
-        <is>
-          <t>Установка смесителя для наполнения СПА</t>
-        </is>
-      </c>
-      <c r="C60" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D60" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="33" t="n"/>
-      <c r="F60" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 84</t>
-        </is>
-      </c>
-      <c r="G60" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H60" s="30" t="inlineStr">
-        <is>
-          <t>8 18</t>
-        </is>
-      </c>
-      <c r="I60" s="36" t="n"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="27" t="inlineStr">
-        <is>
-          <t>Тепловая изоляция</t>
-        </is>
-      </c>
-      <c r="B61" s="28" t="n"/>
-      <c r="C61" s="28" t="n"/>
-      <c r="D61" s="28" t="n"/>
-      <c r="E61" s="28" t="n"/>
-      <c r="F61" s="28" t="n"/>
-      <c r="G61" s="28" t="n"/>
-      <c r="H61" s="28" t="n"/>
-      <c r="I61" s="29" t="n"/>
-    </row>
-    <row r="62" ht="45" customHeight="1">
+      <c r="B61" s="31" t="inlineStr">
+        <is>
+          <t>Установка унитазов подвесных с инсталляциями</t>
+        </is>
+      </c>
+      <c r="C61" s="32" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" s="33" t="n"/>
+      <c r="F61" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 78</t>
+        </is>
+      </c>
+      <c r="G61" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H61" s="30" t="inlineStr">
+        <is>
+          <t>3 5 6 8 9 18</t>
+        </is>
+      </c>
+      <c r="I61" s="36" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="30" t="inlineStr">
         <is>
           <t>52</t>
@@ -2962,25 +2986,21 @@
       </c>
       <c r="B62" s="31" t="inlineStr">
         <is>
-          <t>Изоляция трубопроводов Т3, Т4 трубками из вспененного полиэтилена толщиной 13 мм</t>
+          <t>Установка умывальников со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D62" s="32" t="n">
-        <v>159</v>
-      </c>
-      <c r="E62" s="33" t="inlineStr">
-        <is>
-          <t>65 + 85 + 9 = 159</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E62" s="33" t="n"/>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 93, 94, 95</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 79</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -2990,12 +3010,12 @@
       </c>
       <c r="H62" s="30" t="inlineStr">
         <is>
-          <t>3 5 8 10 11 18</t>
+          <t>3 5 8 18</t>
         </is>
       </c>
       <c r="I62" s="36" t="n"/>
     </row>
-    <row r="63" ht="45" customHeight="1">
+    <row r="63" ht="30" customHeight="1">
       <c r="A63" s="30" t="inlineStr">
         <is>
           <t>53</t>
@@ -3003,25 +3023,21 @@
       </c>
       <c r="B63" s="31" t="inlineStr">
         <is>
-          <t>Изоляция трубопроводов В1 трубками из вспененного полиэтилена толщиной 9 мм</t>
+          <t>Установка ванн со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D63" s="32" t="n">
-        <v>202</v>
-      </c>
-      <c r="E63" s="33" t="inlineStr">
-        <is>
-          <t>91 + 53 + 47 + 11 = 202</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E63" s="33" t="n"/>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 96, 97, 98, 99</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 80</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -3031,7 +3047,7 @@
       </c>
       <c r="H63" s="30" t="inlineStr">
         <is>
-          <t>3 5 8 10 11 18</t>
+          <t>5 8 18</t>
         </is>
       </c>
       <c r="I63" s="36" t="n"/>
@@ -3044,21 +3060,21 @@
       </c>
       <c r="B64" s="31" t="inlineStr">
         <is>
-          <t>Изоляция ввода ПЭ 32 в проёме фундамента</t>
+          <t>Установка душевых систем, кабины, подключение трапов</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D64" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" s="33" t="n"/>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 100</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 81</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -3068,35 +3084,57 @@
       </c>
       <c r="H64" s="30" t="inlineStr">
         <is>
-          <t>14 18</t>
+          <t>4 5 8 18</t>
         </is>
       </c>
       <c r="I64" s="36" t="n"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="27" t="inlineStr">
-        <is>
-          <t>Проходы через строительные конструкции</t>
-        </is>
-      </c>
-      <c r="B65" s="28" t="n"/>
-      <c r="C65" s="28" t="n"/>
-      <c r="D65" s="28" t="n"/>
-      <c r="E65" s="28" t="n"/>
-      <c r="F65" s="28" t="n"/>
-      <c r="G65" s="28" t="n"/>
-      <c r="H65" s="28" t="n"/>
-      <c r="I65" s="29" t="n"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>Установка моек кухонных со смесителями и сифонами</t>
+        </is>
+      </c>
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="D65" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="33" t="n"/>
+      <c r="F65" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 82</t>
+        </is>
+      </c>
+      <c r="G65" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H65" s="30" t="inlineStr">
+        <is>
+          <t>3 8 18</t>
+        </is>
+      </c>
+      <c r="I65" s="36" t="n"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B66" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
+          <t>Установка смесителя для наполнения СПА</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -3105,12 +3143,12 @@
         </is>
       </c>
       <c r="D66" s="32" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 103</t>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 83</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3120,57 +3158,27 @@
       </c>
       <c r="H66" s="30" t="inlineStr">
         <is>
-          <t>14 18</t>
-        </is>
-      </c>
-      <c r="I66" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="30" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B67" s="31" t="inlineStr">
-        <is>
-          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
-        </is>
-      </c>
-      <c r="C67" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="E67" s="33" t="n"/>
-      <c r="F67" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 103</t>
-        </is>
-      </c>
-      <c r="G67" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H67" s="30" t="inlineStr">
-        <is>
-          <t>14 18</t>
-        </is>
-      </c>
-      <c r="I67" s="36" t="inlineStr">
-        <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
+          <t>8 18</t>
+        </is>
+      </c>
+      <c r="I66" s="36" t="n"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>Тепловая изоляция</t>
+        </is>
+      </c>
+      <c r="B67" s="28" t="n"/>
+      <c r="C67" s="28" t="n"/>
+      <c r="D67" s="28" t="n"/>
+      <c r="E67" s="28" t="n"/>
+      <c r="F67" s="28" t="n"/>
+      <c r="G67" s="28" t="n"/>
+      <c r="H67" s="28" t="n"/>
+      <c r="I67" s="29" t="n"/>
+    </row>
+    <row r="68" ht="45" customHeight="1">
       <c r="A68" s="30" t="inlineStr">
         <is>
           <t>57</t>
@@ -3178,21 +3186,25 @@
       </c>
       <c r="B68" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
+          <t>Изоляция трубопроводов Т3, Т4 трубками из вспененного полиэтилена толщиной 13 мм</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D68" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="E68" s="33" t="n"/>
+        <v>159</v>
+      </c>
+      <c r="E68" s="33" t="inlineStr">
+        <is>
+          <t>65 + 85 + 9 = 159</t>
+        </is>
+      </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 104</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 100, 101, 102</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3202,16 +3214,12 @@
       </c>
       <c r="H68" s="30" t="inlineStr">
         <is>
-          <t>14 18</t>
-        </is>
-      </c>
-      <c r="I68" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
+          <t>3 5 8 10 11 18</t>
+        </is>
+      </c>
+      <c r="I68" s="36" t="n"/>
+    </row>
+    <row r="69" ht="45" customHeight="1">
       <c r="A69" s="30" t="inlineStr">
         <is>
           <t>58</t>
@@ -3219,21 +3227,25 @@
       </c>
       <c r="B69" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
+          <t>Изоляция трубопроводов В1 трубками из вспененного полиэтилена толщиной 9 мм</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D69" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="E69" s="33" t="n"/>
+        <v>202</v>
+      </c>
+      <c r="E69" s="33" t="inlineStr">
+        <is>
+          <t>91 + 53 + 47 + 11 = 202</t>
+        </is>
+      </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 104</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 103, 104, 105, 106</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -3243,14 +3255,10 @@
       </c>
       <c r="H69" s="30" t="inlineStr">
         <is>
-          <t>14 18</t>
-        </is>
-      </c>
-      <c r="I69" s="36" t="inlineStr">
-        <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
+          <t>3 5 8 10 11 18 19</t>
+        </is>
+      </c>
+      <c r="I69" s="36" t="n"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="30" t="inlineStr">
@@ -3260,21 +3268,21 @@
       </c>
       <c r="B70" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
+          <t>Изоляция ввода ПЭ 32 в проёме фундамента</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D70" s="32" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E70" s="33" t="n"/>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 105</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 107</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -3284,79 +3292,49 @@
       </c>
       <c r="H70" s="30" t="inlineStr">
         <is>
-          <t>14 18</t>
-        </is>
-      </c>
-      <c r="I70" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="30" t="inlineStr">
+          <t>14 19</t>
+        </is>
+      </c>
+      <c r="I70" s="36" t="n"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>Проходы через строительные конструкции</t>
+        </is>
+      </c>
+      <c r="B71" s="28" t="n"/>
+      <c r="C71" s="28" t="n"/>
+      <c r="D71" s="28" t="n"/>
+      <c r="E71" s="28" t="n"/>
+      <c r="F71" s="28" t="n"/>
+      <c r="G71" s="28" t="n"/>
+      <c r="H71" s="28" t="n"/>
+      <c r="I71" s="29" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B71" s="31" t="inlineStr">
-        <is>
-          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
-        </is>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>13</v>
-      </c>
-      <c r="E71" s="33" t="n"/>
-      <c r="F71" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 105</t>
-        </is>
-      </c>
-      <c r="G71" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H71" s="30" t="inlineStr">
-        <is>
-          <t>14 18</t>
-        </is>
-      </c>
-      <c r="I71" s="36" t="inlineStr">
-        <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="B72" s="31" t="inlineStr">
         <is>
-          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D72" s="32" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E72" s="33" t="n"/>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 106</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 110</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -3369,31 +3347,35 @@
           <t>14 19</t>
         </is>
       </c>
-      <c r="I72" s="36" t="n"/>
-    </row>
-    <row r="73" ht="45" customHeight="1">
+      <c r="I72" s="36" t="inlineStr">
+        <is>
+          <t>по толщине конструкции</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B73" s="31" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента у ввода и выпусков эластичным водогазонепроницаемым материалом</t>
+          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D73" s="32" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E73" s="33" t="n"/>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 107</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 110</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -3408,26 +3390,52 @@
       </c>
       <c r="I73" s="36" t="inlineStr">
         <is>
-          <t>проёмы — КР (ТЗ-1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="27" t="inlineStr">
-        <is>
-          <t>Испытания и пусконаладочные работы</t>
-        </is>
-      </c>
-      <c r="B74" s="28" t="n"/>
-      <c r="C74" s="28" t="n"/>
-      <c r="D74" s="28" t="n"/>
-      <c r="E74" s="28" t="n"/>
-      <c r="F74" s="28" t="n"/>
-      <c r="G74" s="28" t="n"/>
-      <c r="H74" s="28" t="n"/>
-      <c r="I74" s="29" t="n"/>
-    </row>
-    <row r="75" ht="45" customHeight="1">
+          <t>п. 11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="inlineStr">
+        <is>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>36</v>
+      </c>
+      <c r="E74" s="33" t="n"/>
+      <c r="F74" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 111</t>
+        </is>
+      </c>
+      <c r="G74" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H74" s="30" t="inlineStr">
+        <is>
+          <t>14 19</t>
+        </is>
+      </c>
+      <c r="I74" s="36" t="inlineStr">
+        <is>
+          <t>по толщине конструкции</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
       <c r="A75" s="30" t="inlineStr">
         <is>
           <t>63</t>
@@ -3435,25 +3443,21 @@
       </c>
       <c r="B75" s="31" t="inlineStr">
         <is>
-          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
+          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D75" s="32" t="n">
-        <v>361</v>
-      </c>
-      <c r="E75" s="33" t="inlineStr">
-        <is>
-          <t>11 + 55 + 138 + 155 + 2 = 361</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 28, 29, 30, 31, 32</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 111</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -3463,16 +3467,16 @@
       </c>
       <c r="H75" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
+          <t>14 19</t>
         </is>
       </c>
       <c r="I75" s="36" t="inlineStr">
         <is>
-          <t>в т. ч. до закрытия в конструкциях</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
+          <t>п. 11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
       <c r="A76" s="30" t="inlineStr">
         <is>
           <t>64</t>
@@ -3480,25 +3484,21 @@
       </c>
       <c r="B76" s="31" t="inlineStr">
         <is>
-          <t>Испытание системы канализации К1 проливом воды</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D76" s="32" t="n">
-        <v>114</v>
-      </c>
-      <c r="E76" s="33" t="inlineStr">
-        <is>
-          <t>19 + 12 + 1 + 9 + 12 + 24 + 37 = 114</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 33, 34, 35, 36, 37, 38, 39</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 112</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3508,10 +3508,14 @@
       </c>
       <c r="H76" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
-        </is>
-      </c>
-      <c r="I76" s="36" t="n"/>
+          <t>14 19</t>
+        </is>
+      </c>
+      <c r="I76" s="36" t="inlineStr">
+        <is>
+          <t>по толщине конструкции</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="30" t="inlineStr">
@@ -3521,25 +3525,21 @@
       </c>
       <c r="B77" s="31" t="inlineStr">
         <is>
-          <t>Испытание трубопроводов К1 в грунте наполнением водой до засыпки</t>
+          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D77" s="32" t="n">
-        <v>61</v>
-      </c>
-      <c r="E77" s="33" t="inlineStr">
-        <is>
-          <t>24 + 37 = 61</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 38, 39</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 112</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -3549,10 +3549,14 @@
       </c>
       <c r="H77" s="30" t="inlineStr">
         <is>
-          <t>2 14 16</t>
-        </is>
-      </c>
-      <c r="I77" s="36" t="n"/>
+          <t>14 19</t>
+        </is>
+      </c>
+      <c r="I77" s="36" t="inlineStr">
+        <is>
+          <t>п. 11.5</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="45" customHeight="1">
       <c r="A78" s="30" t="inlineStr">
@@ -3562,25 +3566,21 @@
       </c>
       <c r="B78" s="31" t="inlineStr">
         <is>
-          <t>Промывка и дезинфекция трубопроводов систем В1, Т3, Т4</t>
+          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D78" s="32" t="n">
-        <v>361</v>
-      </c>
-      <c r="E78" s="33" t="inlineStr">
-        <is>
-          <t>11 + 55 + 138 + 155 + 2 = 361</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E78" s="33" t="n"/>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 28, 29, 30, 31, 32</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 113</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H78" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
+          <t>14 19</t>
         </is>
       </c>
       <c r="I78" s="36" t="n"/>
     </row>
-    <row r="79" ht="30" customHeight="1">
+    <row r="79" ht="45" customHeight="1">
       <c r="A79" s="30" t="inlineStr">
         <is>
           <t>67</t>
@@ -3603,21 +3603,21 @@
       </c>
       <c r="B79" s="31" t="inlineStr">
         <is>
-          <t>Наладка циркуляции ГВС: настройка балансировочных клапанов по П4</t>
+          <t>Заделка проёмов фундамента у ввода и выпусков эластичным водогазонепроницаемым материалом</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D79" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" s="33" t="n"/>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 75</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 114</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -3627,67 +3627,292 @@
       </c>
       <c r="H79" s="30" t="inlineStr">
         <is>
+          <t>14 19</t>
+        </is>
+      </c>
+      <c r="I79" s="36" t="inlineStr">
+        <is>
+          <t>проёмы — КР (ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>Испытания и пусконаладочные работы</t>
+        </is>
+      </c>
+      <c r="B80" s="28" t="n"/>
+      <c r="C80" s="28" t="n"/>
+      <c r="D80" s="28" t="n"/>
+      <c r="E80" s="28" t="n"/>
+      <c r="F80" s="28" t="n"/>
+      <c r="G80" s="28" t="n"/>
+      <c r="H80" s="28" t="n"/>
+      <c r="I80" s="29" t="n"/>
+    </row>
+    <row r="81" ht="45" customHeight="1">
+      <c r="A81" s="30" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="inlineStr">
+        <is>
+          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
+        </is>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>361</v>
+      </c>
+      <c r="E81" s="33" t="inlineStr">
+        <is>
+          <t>11 + 55 + 138 + 155 + 2 = 361</t>
+        </is>
+      </c>
+      <c r="F81" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 28, 29, 30, 31, 32</t>
+        </is>
+      </c>
+      <c r="G81" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H81" s="30" t="inlineStr">
+        <is>
+          <t>1 2 16</t>
+        </is>
+      </c>
+      <c r="I81" s="36" t="inlineStr">
+        <is>
+          <t>в т. ч. до закрытия в конструкциях</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="45" customHeight="1">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="inlineStr">
+        <is>
+          <t>Испытание системы канализации К1 проливом воды</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>118</v>
+      </c>
+      <c r="E82" s="33" t="inlineStr">
+        <is>
+          <t>28 + 24 + 1 + 25 + 37 + 3 = 118</t>
+        </is>
+      </c>
+      <c r="F82" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 33, 34, 35, 36, 37, 38</t>
+        </is>
+      </c>
+      <c r="G82" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H82" s="30" t="inlineStr">
+        <is>
+          <t>1 2 16</t>
+        </is>
+      </c>
+      <c r="I82" s="36" t="n"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B83" s="31" t="inlineStr">
+        <is>
+          <t>Испытание трубопроводов К1, К2 в грунте наполнением водой до засыпки</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E83" s="33" t="inlineStr">
+        <is>
+          <t>25 + 37 + 3 = 65</t>
+        </is>
+      </c>
+      <c r="F83" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 36, 37, 38</t>
+        </is>
+      </c>
+      <c r="G83" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H83" s="30" t="inlineStr">
+        <is>
+          <t>2 14 16</t>
+        </is>
+      </c>
+      <c r="I83" s="36" t="n"/>
+    </row>
+    <row r="84" ht="45" customHeight="1">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>Промывка и дезинфекция трубопроводов систем В1, Т3, Т4</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="n">
+        <v>361</v>
+      </c>
+      <c r="E84" s="33" t="inlineStr">
+        <is>
+          <t>11 + 55 + 138 + 155 + 2 = 361</t>
+        </is>
+      </c>
+      <c r="F84" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 28, 29, 30, 31, 32</t>
+        </is>
+      </c>
+      <c r="G84" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H84" s="30" t="inlineStr">
+        <is>
+          <t>1 2 16</t>
+        </is>
+      </c>
+      <c r="I84" s="36" t="n"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="30" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>Наладка циркуляции ГВС: настройка балансировочных клапанов по П4</t>
+        </is>
+      </c>
+      <c r="C85" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D85" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="33" t="n"/>
+      <c r="F85" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 74</t>
+        </is>
+      </c>
+      <c r="G85" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H85" s="30" t="inlineStr">
+        <is>
           <t>13 17</t>
         </is>
       </c>
-      <c r="I79" s="36" t="inlineStr">
+      <c r="I85" s="36" t="inlineStr">
         <is>
           <t>П4</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B80" s="31" t="inlineStr">
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="30" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B86" s="31" t="inlineStr">
         <is>
           <t>Пусконаладочные работы циркуляционных насосов Н8, Н9</t>
         </is>
       </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="n">
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D86" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E80" s="33" t="inlineStr">
+      <c r="E86" s="33" t="inlineStr">
         <is>
           <t>1 + 1 = 2</t>
         </is>
       </c>
-      <c r="F80" s="34" t="inlineStr">
+      <c r="F86" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 7, 8; И05.09.26-ВК.СО, поз. 1, 2</t>
         </is>
       </c>
-      <c r="G80" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H80" s="30" t="inlineStr">
+      <c r="G86" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H86" s="30" t="inlineStr">
         <is>
           <t>7 8 15</t>
         </is>
       </c>
-      <c r="I80" s="36" t="n"/>
+      <c r="I86" s="36" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A65:I65"/>
+  <mergeCells count="10">
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A60:I60"/>
     <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A61:I61"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="55" fitToHeight="0" fitToWidth="1"/>
@@ -3700,7 +3925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -3758,7 +3983,14 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="38" t="inlineStr">
         <is>
-          <t>7. Система автополива участка (трассы, клапаны, контроллер) — по ландшафтному проекту; в ведомости — подводка КХ-8.</t>
+          <t>7. Система автополива и водопровод беседки по участку — по ландшафтному проекту и НВК; в ведомости — подводка КХ-8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>8. Состав работ уточнён по опросному листу Заказчика: бесшумная канализация, защита от протечек в мокрых зонах, трап в парной, лоток гаража с пескоуловителем в ливневую сеть.</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="D41" s="32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
@@ -2272,11 +2272,11 @@
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E43" s="33" t="inlineStr">
         <is>
-          <t>25 + 37 + 3 = 65</t>
+          <t>26 + 39 + 3 = 68</t>
         </is>
       </c>
       <c r="F43" s="34" t="inlineStr">
@@ -2481,11 +2481,11 @@
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E48" s="33" t="inlineStr">
         <is>
-          <t>3 + 1 + 2 + 2 + 6 + 1 = 15</t>
+          <t>5 + 1 + 3 + 2 + 6 + 1 = 18</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="33" t="n"/>
       <c r="F50" s="34" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" s="33" t="inlineStr">
         <is>
-          <t>23 + 2 + 33 = 58</t>
+          <t>24 + 2 + 33 = 59</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="D76" s="32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="D77" s="32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
@@ -3713,11 +3713,11 @@
         </is>
       </c>
       <c r="D82" s="32" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E82" s="33" t="inlineStr">
         <is>
-          <t>28 + 24 + 1 + 25 + 37 + 3 = 118</t>
+          <t>28 + 24 + 1 + 26 + 39 + 3 = 121</t>
         </is>
       </c>
       <c r="F82" s="34" t="inlineStr">
@@ -3754,11 +3754,11 @@
         </is>
       </c>
       <c r="D83" s="32" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E83" s="33" t="inlineStr">
         <is>
-          <t>25 + 37 + 3 = 65</t>
+          <t>26 + 39 + 3 = 68</t>
         </is>
       </c>
       <c r="F83" s="34" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -863,7 +863,7 @@
       <c r="E5" s="33" t="n"/>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 53</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 54</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="D15" s="32" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 82,0, Т3 58,4 м + 10 %</t>
+          <t>по модели В1 83,9, Т3 63,8 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1316,11 +1316,11 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>24 + 30 + 17 + 4 = 75</t>
+          <t>26 + 30 + 17 + 4 = 77</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
@@ -1357,12 +1357,16 @@
         </is>
       </c>
       <c r="D18" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="33" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>2 + 1 = 3</t>
+        </is>
+      </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 47</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 47, 48</t>
         </is>
       </c>
       <c r="G18" s="35" t="inlineStr">
@@ -1403,7 +1407,7 @@
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 48, 49, 50, 51</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 49, 50, 51, 52</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -1413,7 +1417,7 @@
       </c>
       <c r="H19" s="30" t="inlineStr">
         <is>
-          <t>3 4 8 16 17</t>
+          <t>3 4 8 17</t>
         </is>
       </c>
       <c r="I19" s="36" t="n"/>
@@ -1440,7 +1444,7 @@
       <c r="E20" s="33" t="n"/>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 52</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 53</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
@@ -1472,16 +1476,16 @@
         </is>
       </c>
       <c r="D21" s="32" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E21" s="33" t="inlineStr">
         <is>
-          <t>39 + 19 = 58</t>
+          <t>40 + 22 = 62</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 108, 109</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 109, 110</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -1513,16 +1517,16 @@
         </is>
       </c>
       <c r="D22" s="32" t="n">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="E22" s="33" t="inlineStr">
         <is>
-          <t>76 + 133 + 43 + 21 = 273</t>
+          <t>93 + 133 + 43 + 21 = 290</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 115, 116, 117, 118</t>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 116, 117, 118, 119</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -1563,7 +1567,7 @@
       <c r="E23" s="33" t="n"/>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 122</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 123</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -1619,7 +1623,7 @@
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 68, 69, 97</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 69, 70, 98</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -1656,7 +1660,7 @@
       <c r="E26" s="33" t="n"/>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 70</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 71</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -1693,7 +1697,7 @@
       <c r="E27" s="33" t="n"/>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 74</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 75</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1734,7 +1738,7 @@
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 75</t>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 76</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1771,7 +1775,7 @@
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 76</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 77</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1781,7 +1785,7 @@
       </c>
       <c r="H29" s="30" t="inlineStr">
         <is>
-          <t>4 17</t>
+          <t>4 18</t>
         </is>
       </c>
       <c r="I29" s="36" t="n"/>
@@ -1812,7 +1816,7 @@
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 71, 72, 73</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 72, 73, 74</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1848,12 +1852,12 @@
         </is>
       </c>
       <c r="D31" s="32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E31" s="33" t="n"/>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 77</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 78</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -2084,7 +2088,7 @@
       <c r="E38" s="33" t="n"/>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 33, 54</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 33, 55</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -2116,12 +2120,12 @@
         </is>
       </c>
       <c r="D39" s="32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E39" s="33" t="n"/>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 34, 55</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 34, 56</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -2158,7 +2162,7 @@
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 35, 56</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 35, 57</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2190,7 +2194,7 @@
         </is>
       </c>
       <c r="D41" s="32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
@@ -2272,11 +2276,11 @@
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E43" s="33" t="inlineStr">
         <is>
-          <t>26 + 39 + 3 = 68</t>
+          <t>27 + 39 + 3 = 69</t>
         </is>
       </c>
       <c r="F43" s="34" t="inlineStr">
@@ -2404,7 +2408,7 @@
       <c r="E46" s="33" t="n"/>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 93</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 94</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -2445,7 +2449,7 @@
       <c r="E47" s="33" t="n"/>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 94</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 95</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -2481,16 +2485,16 @@
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48" s="33" t="inlineStr">
         <is>
-          <t>5 + 1 + 3 + 2 + 6 + 1 = 18</t>
+          <t>5 + 2 + 3 + 2 + 6 + 1 = 19</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 57, 58, 59, 62, 63, 64</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 58, 59, 60, 63, 64, 65</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -2527,7 +2531,7 @@
       <c r="E49" s="33" t="n"/>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 65</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 66</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2564,7 +2568,7 @@
       <c r="E50" s="33" t="n"/>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 92</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 93</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2609,7 +2613,7 @@
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 84, 85, 86, 87</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 85, 86, 87, 88</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -2650,7 +2654,7 @@
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 88, 89, 90</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 89, 90, 91</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2691,7 +2695,7 @@
       <c r="E53" s="33" t="n"/>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 91</t>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 92</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -2727,16 +2731,16 @@
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E54" s="33" t="inlineStr">
         <is>
-          <t>24 + 2 + 33 = 59</t>
+          <t>24 + 2 + 34 = 60</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 119, 120, 121</t>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 120, 121, 122</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -2788,7 +2792,7 @@
       <c r="E56" s="33" t="n"/>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 95</t>
+          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 96</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -2833,7 +2837,7 @@
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 96, 97</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 97, 98</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -2870,7 +2874,7 @@
       <c r="E58" s="33" t="n"/>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 98</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 99</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -2907,7 +2911,7 @@
       <c r="E59" s="33" t="n"/>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 99</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 100</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -2963,7 +2967,7 @@
       <c r="E61" s="33" t="n"/>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 78</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 79</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -2995,12 +2999,12 @@
         </is>
       </c>
       <c r="D62" s="32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E62" s="33" t="n"/>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 79</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 80</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -3037,7 +3041,7 @@
       <c r="E63" s="33" t="n"/>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 80</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 81</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -3074,7 +3078,7 @@
       <c r="E64" s="33" t="n"/>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 81</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 82</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -3111,7 +3115,7 @@
       <c r="E65" s="33" t="n"/>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 82</t>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 83</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -3148,7 +3152,7 @@
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 83</t>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 84</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3195,16 +3199,16 @@
         </is>
       </c>
       <c r="D68" s="32" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E68" s="33" t="inlineStr">
         <is>
-          <t>65 + 85 + 9 = 159</t>
+          <t>71 + 85 + 9 = 165</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 100, 101, 102</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 101, 102, 103</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3236,16 +3240,16 @@
         </is>
       </c>
       <c r="D69" s="32" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E69" s="33" t="inlineStr">
         <is>
-          <t>91 + 53 + 47 + 11 = 202</t>
+          <t>93 + 53 + 47 + 11 = 204</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 103, 104, 105, 106</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 104, 105, 106, 107</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -3255,7 +3259,7 @@
       </c>
       <c r="H69" s="30" t="inlineStr">
         <is>
-          <t>3 5 8 10 11 18 19</t>
+          <t>3 5 8 10 11 19</t>
         </is>
       </c>
       <c r="I69" s="36" t="n"/>
@@ -3282,7 +3286,7 @@
       <c r="E70" s="33" t="n"/>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 107</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 108</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -3334,7 +3338,7 @@
       <c r="E72" s="33" t="n"/>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 110</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 111</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -3375,7 +3379,7 @@
       <c r="E73" s="33" t="n"/>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 110</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 111</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -3411,12 +3415,12 @@
         </is>
       </c>
       <c r="D74" s="32" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E74" s="33" t="n"/>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 111</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 112</t>
         </is>
       </c>
       <c r="G74" s="35" t="inlineStr">
@@ -3452,12 +3456,12 @@
         </is>
       </c>
       <c r="D75" s="32" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 111</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 112</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -3498,7 +3502,7 @@
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 112</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 113</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3539,7 +3543,7 @@
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 112</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 113</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -3580,7 +3584,7 @@
       <c r="E78" s="33" t="n"/>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 113</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 114</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -3617,7 +3621,7 @@
       <c r="E79" s="33" t="n"/>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 114</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 115</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -3668,11 +3672,11 @@
         </is>
       </c>
       <c r="D81" s="32" t="n">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E81" s="33" t="inlineStr">
         <is>
-          <t>11 + 55 + 138 + 155 + 2 = 361</t>
+          <t>11 + 55 + 138 + 163 + 2 = 369</t>
         </is>
       </c>
       <c r="F81" s="34" t="inlineStr">
@@ -3713,11 +3717,11 @@
         </is>
       </c>
       <c r="D82" s="32" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E82" s="33" t="inlineStr">
         <is>
-          <t>28 + 24 + 1 + 26 + 39 + 3 = 121</t>
+          <t>28 + 25 + 1 + 27 + 39 + 3 = 123</t>
         </is>
       </c>
       <c r="F82" s="34" t="inlineStr">
@@ -3754,11 +3758,11 @@
         </is>
       </c>
       <c r="D83" s="32" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E83" s="33" t="inlineStr">
         <is>
-          <t>26 + 39 + 3 = 68</t>
+          <t>27 + 39 + 3 = 69</t>
         </is>
       </c>
       <c r="F83" s="34" t="inlineStr">
@@ -3795,11 +3799,11 @@
         </is>
       </c>
       <c r="D84" s="32" t="n">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E84" s="33" t="inlineStr">
         <is>
-          <t>11 + 55 + 138 + 155 + 2 = 361</t>
+          <t>11 + 55 + 138 + 163 + 2 = 369</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
@@ -3841,7 +3845,7 @@
       <c r="E85" s="33" t="n"/>
       <c r="F85" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 74</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 75</t>
         </is>
       </c>
       <c r="G85" s="35" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="D25" s="32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="33" t="inlineStr">
         <is>
-          <t>2 + 1 + 3 = 6</t>
+          <t>2 + 3 = 5</t>
         </is>
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 69, 70, 98</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 69, 70</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H25" s="30" t="inlineStr">
         <is>
-          <t>7 8 10 11 17 18</t>
+          <t>7 8 10 11 17</t>
         </is>
       </c>
       <c r="I25" s="36" t="n"/>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
@@ -2276,11 +2276,11 @@
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E43" s="33" t="inlineStr">
         <is>
-          <t>27 + 39 + 3 = 69</t>
+          <t>27 + 40 + 3 = 70</t>
         </is>
       </c>
       <c r="F43" s="34" t="inlineStr">
@@ -2485,11 +2485,11 @@
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E48" s="33" t="inlineStr">
         <is>
-          <t>5 + 2 + 3 + 2 + 6 + 1 = 19</t>
+          <t>5 + 2 + 4 + 2 + 6 + 1 = 20</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" s="33" t="n"/>
       <c r="F50" s="34" t="inlineStr">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="D76" s="32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="D77" s="32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B82" s="31" t="inlineStr">
         <is>
-          <t>Испытание системы канализации К1 проливом воды</t>
+          <t>Испытание систем канализации К1 и К2 (участок К2-1) проливом воды</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -3717,11 +3717,11 @@
         </is>
       </c>
       <c r="D82" s="32" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E82" s="33" t="inlineStr">
         <is>
-          <t>28 + 25 + 1 + 27 + 39 + 3 = 123</t>
+          <t>28 + 25 + 1 + 27 + 40 + 3 = 124</t>
         </is>
       </c>
       <c r="F82" s="34" t="inlineStr">
@@ -3758,11 +3758,11 @@
         </is>
       </c>
       <c r="D83" s="32" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E83" s="33" t="inlineStr">
         <is>
-          <t>27 + 39 + 3 = 69</t>
+          <t>27 + 40 + 3 = 70</t>
         </is>
       </c>
       <c r="F83" s="34" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -863,7 +863,7 @@
       <c r="E5" s="33" t="n"/>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 54</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 60</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="D7" s="32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
-          <t>1 + 1 + 1 + 1 + 1 + 1 = 6</t>
+          <t>1 + 1 + 1 + 1 + 1 + 1 + 1 + 1 = 8</t>
         </is>
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8, 13; И05.09.26-ВК.СО, поз. 19, 20, 21, 22, 23, 24</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8, 13; И05.09.26-ВК.СО, поз. 19, 20, 21, 22, 23, 24, 25, 26</t>
         </is>
       </c>
       <c r="G7" s="35" t="inlineStr">
@@ -977,12 +977,12 @@
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 25</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 27</t>
         </is>
       </c>
       <c r="G8" s="35" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="I8" s="36" t="n"/>
     </row>
-    <row r="9" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="9" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
           <t>5</t>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>Установка шкафов коллекторных накладных</t>
+          <t>Установка шкафов коллекторных встраиваемых в ниши (ШВК-1, ШВК-2, ШВК-Б2) и в короб (ШВК-Б1)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -1014,109 +1014,113 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>1 + 1 + 1 + 1 = 4</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8, 13, 14; И05.09.26-ВК.СО, поз. 28, 29, 30, 31</t>
+        </is>
+      </c>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>3 4 8 13 14 16</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>узел 10 листа 14; ниши и короб — АР (ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Установка нажимных люков коллекторных шкафов и поддонов под шкафы</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 13, 14; И05.09.26-ВК.СО, поз. 32, 33</t>
+        </is>
+      </c>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>13 14 16</t>
+        </is>
+      </c>
+      <c r="I10" s="36" t="inlineStr">
+        <is>
+          <t>облицовка дверцы — по отделке</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Трубопроводы систем В1, Т3, Т4</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="29" t="n"/>
+    </row>
+    <row r="12" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка трубы ПЭ 100 SDR11 32×3,0 ввода от наружной грани фундамента до приямка</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="n">
         <v>2</v>
-      </c>
-      <c r="E9" s="33" t="inlineStr">
-        <is>
-          <t>1 + 1 = 2</t>
-        </is>
-      </c>
-      <c r="F9" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 4, 8, 13; И05.09.26-ВК.СО, поз. 26, 27</t>
-        </is>
-      </c>
-      <c r="G9" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H9" s="30" t="inlineStr">
-        <is>
-          <t>4 8 13 16</t>
-        </is>
-      </c>
-      <c r="I9" s="36" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>Трубопроводы систем В1, Т3, Т4</t>
-        </is>
-      </c>
-      <c r="B10" s="28" t="n"/>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="28" t="n"/>
-      <c r="E10" s="28" t="n"/>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="29" t="n"/>
-    </row>
-    <row r="11" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка трубы ПЭ 100 SDR11 32×3,0 ввода от наружной грани фундамента до приямка</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="33" t="n"/>
-      <c r="F11" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 28</t>
-        </is>
-      </c>
-      <c r="G11" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H11" s="30" t="inlineStr">
-        <is>
-          <t>7 14 16</t>
-        </is>
-      </c>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>узел 1 листа 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка трубопроводов из труб PE-Xa 32×4,4 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="n">
-        <v>11</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 29</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 34</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -1126,12 +1130,12 @@
       </c>
       <c r="H12" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 10 11 16</t>
+          <t>7 14 16</t>
         </is>
       </c>
       <c r="I12" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 9,9 м + 10 %</t>
+          <t>узел 1 листа 14</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1147,7 @@
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из труб PE-Xa 25×3,5 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
+          <t>Прокладка трубопроводов из труб PE-Xa 32×4,4 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -1152,12 +1156,12 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 30</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 35</t>
         </is>
       </c>
       <c r="G13" s="35" t="inlineStr">
@@ -1172,7 +1176,7 @@
       </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 41,8, Т3 7,9 м + 10 %</t>
+          <t>по модели В1 11,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1188,7 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из труб PE-Xa 20×2,8 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
+          <t>Прокладка трубопроводов из труб PE-Xa 25×3,5 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -1193,12 +1197,12 @@
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 31</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 36</t>
         </is>
       </c>
       <c r="G14" s="35" t="inlineStr">
@@ -1213,7 +1217,7 @@
       </c>
       <c r="I14" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 48,0, Т3 44,6, Т4 32,4 м + 10 %</t>
+          <t>по модели В1 59,2, Т3 31,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1229,7 @@
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из труб PE-Xa 16×2,2 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
+          <t>Прокладка трубопроводов из труб PE-Xa 20×2,8 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -1234,12 +1238,12 @@
         </is>
       </c>
       <c r="D15" s="32" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 32</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 37</t>
         </is>
       </c>
       <c r="G15" s="35" t="inlineStr">
@@ -1254,11 +1258,11 @@
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 83,9, Т3 63,8 м + 10 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>по модели В1 32,6, Т3 29,0, Т4 48,0 м + 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
           <t>11</t>
@@ -1266,236 +1270,236 @@
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
+          <t>Прокладка трубопроводов из труб PE-Xa 16×2,2 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>114</v>
+      </c>
+      <c r="E16" s="33" t="n"/>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 38</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>3 4 5 8 10 11 16</t>
+        </is>
+      </c>
+      <c r="I16" s="36" t="inlineStr">
+        <is>
+          <t>по модели В1 65,0, Т3 38,2 м + 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
           <t>Установка фитингов «евроконус» на выходах коллекторов</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D16" s="32" t="n">
-        <v>32</v>
-      </c>
-      <c r="E16" s="33" t="inlineStr">
-        <is>
-          <t>21 + 10 + 1 = 32</t>
-        </is>
-      </c>
-      <c r="F16" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 40, 41, 42</t>
-        </is>
-      </c>
-      <c r="G16" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H16" s="30" t="inlineStr">
-        <is>
-          <t>13 16</t>
-        </is>
-      </c>
-      <c r="I16" s="36" t="n"/>
-    </row>
-    <row r="17" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>20 + 8 + 2 = 30</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 46, 47, 48</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H17" s="30" t="inlineStr">
+        <is>
+          <t>13 16 17</t>
+        </is>
+      </c>
+      <c r="I17" s="36" t="n"/>
+    </row>
+    <row r="18" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>Установка фитингов PE-Xa с переходом на резьбу (водорозетки, угольники, присоединения оборудования)</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="n">
-        <v>77</v>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>26 + 30 + 17 + 4 = 77</t>
-        </is>
-      </c>
-      <c r="F17" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 43, 44, 45, 46</t>
-        </is>
-      </c>
-      <c r="G17" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H17" s="30" t="inlineStr">
-        <is>
-          <t>3 4 5 8 16</t>
-        </is>
-      </c>
-      <c r="I17" s="36" t="n"/>
-    </row>
-    <row r="18" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>25 + 30 + 22 + 4 = 81</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 49, 50, 51, 52</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>3 4 5 8 17</t>
+        </is>
+      </c>
+      <c r="I18" s="36" t="n"/>
+    </row>
+    <row r="19" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>Установка тройников PE-Xa</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="n">
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>2 + 1 = 3</t>
         </is>
       </c>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 47, 48</t>
-        </is>
-      </c>
-      <c r="G18" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H18" s="30" t="inlineStr">
-        <is>
-          <t>10 11 16</t>
-        </is>
-      </c>
-      <c r="I18" s="36" t="n"/>
-    </row>
-    <row r="19" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 53, 54</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H19" s="30" t="inlineStr">
+        <is>
+          <t>10 11 17</t>
+        </is>
+      </c>
+      <c r="I19" s="36" t="n"/>
+    </row>
+    <row r="20" ht="45" customFormat="1" customHeight="1" s="4">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>Установка фиксаторов поворота 90° на выходах труб из пола</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="n">
-        <v>78</v>
-      </c>
-      <c r="E19" s="33" t="inlineStr">
-        <is>
-          <t>36 + 28 + 13 + 1 = 78</t>
-        </is>
-      </c>
-      <c r="F19" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 49, 50, 51, 52</t>
-        </is>
-      </c>
-      <c r="G19" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H19" s="30" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>92</v>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>34 + 32 + 24 + 2 = 92</t>
+        </is>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 55, 56, 57, 58</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="inlineStr">
         <is>
           <t>3 4 8 17</t>
         </is>
       </c>
-      <c r="I19" s="36" t="n"/>
-    </row>
-    <row r="20" ht="30" customFormat="1" customHeight="1" s="4">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
+      <c r="I20" s="36" t="n"/>
+    </row>
+    <row r="21" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>Установка перехода ПЭ 32 / PE-Xa 32</t>
         </is>
       </c>
-      <c r="C20" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D20" s="32" t="n">
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="33" t="n"/>
-      <c r="F20" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 53</t>
-        </is>
-      </c>
-      <c r="G20" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H20" s="30" t="inlineStr">
+      <c r="E21" s="33" t="n"/>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 59</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H21" s="30" t="inlineStr">
         <is>
           <t>7 14 17</t>
-        </is>
-      </c>
-      <c r="I20" s="36" t="n"/>
-    </row>
-    <row r="21" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка защитной гофротрубы ПНД на подъёмах к приборам в стенах</t>
-        </is>
-      </c>
-      <c r="C21" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="n">
-        <v>62</v>
-      </c>
-      <c r="E21" s="33" t="inlineStr">
-        <is>
-          <t>40 + 22 = 62</t>
-        </is>
-      </c>
-      <c r="F21" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 109, 110</t>
-        </is>
-      </c>
-      <c r="G21" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H21" s="30" t="inlineStr">
-        <is>
-          <t>3 4 5 8 19</t>
         </is>
       </c>
       <c r="I21" s="36" t="n"/>
@@ -1508,159 +1512,163 @@
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
+          <t>Прокладка защитной гофротрубы ПНД на подъёмах к приборам в стенах</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="n">
+        <v>79</v>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>52 + 27 = 79</t>
+        </is>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 115, 116</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H22" s="30" t="inlineStr">
+        <is>
+          <t>3 4 5 8 19</t>
+        </is>
+      </c>
+      <c r="I22" s="36" t="n"/>
+    </row>
+    <row r="23" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
           <t>Крепление трубопроводов PE-Xa хомутами с резиновым вкладышем</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D22" s="32" t="n">
-        <v>290</v>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>93 + 133 + 43 + 21 = 290</t>
-        </is>
-      </c>
-      <c r="F22" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 116, 117, 118, 119</t>
-        </is>
-      </c>
-      <c r="G22" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H22" s="30" t="inlineStr">
-        <is>
-          <t>5 7 14 19</t>
-        </is>
-      </c>
-      <c r="I22" s="36" t="inlineStr">
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="n">
+        <v>296</v>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>45 + 110 + 116 + 25 = 296</t>
+        </is>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 124, 125, 126, 127</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H23" s="30" t="inlineStr">
+        <is>
+          <t>5 7 14 19 20</t>
+        </is>
+      </c>
+      <c r="I23" s="36" t="inlineStr">
         <is>
           <t>шаг — лист 14</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="inlineStr">
+    <row r="24" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>Крепление трубопроводов PE-Xa к утеплителю пола скобами</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="n">
-        <v>450</v>
-      </c>
-      <c r="E23" s="33" t="n"/>
-      <c r="F23" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 123</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H23" s="30" t="inlineStr">
-        <is>
-          <t>3 8 14 19</t>
-        </is>
-      </c>
-      <c r="I23" s="36" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="n">
+        <v>400</v>
+      </c>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 131</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H24" s="30" t="inlineStr">
+        <is>
+          <t>3 8 14 20</t>
+        </is>
+      </c>
+      <c r="I24" s="36" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Арматура</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n"/>
-      <c r="C24" s="28" t="n"/>
-      <c r="D24" s="28" t="n"/>
-      <c r="E24" s="28" t="n"/>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="n"/>
-      <c r="H24" s="28" t="n"/>
-      <c r="I24" s="29" t="n"/>
-    </row>
-    <row r="25" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="28" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Установка кранов шаровых Ду 15–20</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D25" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" s="33" t="inlineStr">
-        <is>
-          <t>2 + 3 = 5</t>
-        </is>
-      </c>
-      <c r="F25" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 69, 70</t>
-        </is>
-      </c>
-      <c r="G25" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H25" s="30" t="inlineStr">
-        <is>
-          <t>7 8 10 11 17</t>
-        </is>
-      </c>
-      <c r="I25" s="36" t="n"/>
-    </row>
-    <row r="26" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="inlineStr">
-        <is>
-          <t>Установка обратных клапанов Ду 15 на Т4</t>
-        </is>
-      </c>
       <c r="C26" s="32" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="D26" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="33" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>3 + 4 = 7</t>
+        </is>
+      </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 71</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 75, 76</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -1670,7 +1678,7 @@
       </c>
       <c r="H26" s="30" t="inlineStr">
         <is>
-          <t>10 11 17</t>
+          <t>7 8 10 11 18</t>
         </is>
       </c>
       <c r="I26" s="36" t="n"/>
@@ -1683,7 +1691,7 @@
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>Установка клапанов балансировочных ручных Ду 15</t>
+          <t>Установка обратных клапанов Ду 15 на Т4</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -1697,7 +1705,7 @@
       <c r="E27" s="33" t="n"/>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 75</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 77</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1707,14 +1715,10 @@
       </c>
       <c r="H27" s="30" t="inlineStr">
         <is>
-          <t>13 17</t>
-        </is>
-      </c>
-      <c r="I27" s="36" t="inlineStr">
-        <is>
-          <t>настройка — П4</t>
-        </is>
-      </c>
+          <t>10 11 18</t>
+        </is>
+      </c>
+      <c r="I27" s="36" t="n"/>
     </row>
     <row r="28" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A28" s="30" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>Установка кранов поливочных (сезонных) с выносом через стену</t>
+          <t>Установка клапанов балансировочных ручных Ду 15</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -1733,12 +1737,12 @@
         </is>
       </c>
       <c r="D28" s="32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 76</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 81</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1748,12 +1752,16 @@
       </c>
       <c r="H28" s="30" t="inlineStr">
         <is>
-          <t>3 8 17</t>
-        </is>
-      </c>
-      <c r="I28" s="36" t="n"/>
-    </row>
-    <row r="29" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>13 18</t>
+        </is>
+      </c>
+      <c r="I28" s="36" t="inlineStr">
+        <is>
+          <t>настройка — П4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
           <t>23</t>
@@ -1761,7 +1769,7 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>Установка крана для стиральной машины</t>
+          <t>Установка кранов поливочных незамерзающих со штоком 350 мм через стену (в гильзе с уклоном наружу)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -1770,12 +1778,12 @@
         </is>
       </c>
       <c r="D29" s="32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 77</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 82</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1785,152 +1793,148 @@
       </c>
       <c r="H29" s="30" t="inlineStr">
         <is>
+          <t>3 8 14 18</t>
+        </is>
+      </c>
+      <c r="I29" s="36" t="inlineStr">
+        <is>
+          <t>узел 9 листа 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" thickBot="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>Установка крана для стиральной машины</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 83</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H30" s="30" t="inlineStr">
+        <is>
           <t>4 18</t>
         </is>
       </c>
-      <c r="I29" s="36" t="n"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" thickBot="1">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B30" s="31" t="inlineStr">
+      <c r="I30" s="36" t="n"/>
+    </row>
+    <row r="31" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>Подводка автополива КХ-8: установка обратного клапана, спускного крана и заглушки на конце трубы</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="n">
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>1 + 1 + 1 = 3</t>
         </is>
       </c>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 72, 73, 74</t>
-        </is>
-      </c>
-      <c r="G30" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H30" s="30" t="inlineStr">
-        <is>
-          <t>4 7 14 17</t>
-        </is>
-      </c>
-      <c r="I30" s="36" t="inlineStr">
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 78, 79, 80</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H31" s="30" t="inlineStr">
+        <is>
+          <t>4 7 14 18</t>
+        </is>
+      </c>
+      <c r="I31" s="36" t="inlineStr">
         <is>
           <t>далее — по ландшафтному проекту</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B31" s="31" t="inlineStr">
+    <row r="32" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>Установка кранов шаровых угловых для гибких подводок приборов</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="n">
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="E31" s="33" t="n"/>
-      <c r="F31" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 78</t>
-        </is>
-      </c>
-      <c r="G31" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H31" s="30" t="inlineStr">
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 84</t>
+        </is>
+      </c>
+      <c r="G32" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H32" s="30" t="inlineStr">
         <is>
           <t>3 4 5 8 18</t>
         </is>
       </c>
-      <c r="I31" s="36" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="I32" s="36" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>Оборудование горячего водоснабжения</t>
         </is>
       </c>
-      <c r="B32" s="28" t="n"/>
-      <c r="C32" s="28" t="n"/>
-      <c r="D32" s="28" t="n"/>
-      <c r="E32" s="28" t="n"/>
-      <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n"/>
-      <c r="H32" s="28" t="n"/>
-      <c r="I32" s="29" t="n"/>
-    </row>
-    <row r="33" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="inlineStr">
-        <is>
-          <t>Установка насосов циркуляционных ГВС Н8, Н9 с подключением</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D33" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="33" t="inlineStr">
-        <is>
-          <t>1 + 1 = 2</t>
-        </is>
-      </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 1, 2</t>
-        </is>
-      </c>
-      <c r="G33" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H33" s="30" t="inlineStr">
-        <is>
-          <t>7 8 10 11 15</t>
-        </is>
-      </c>
-      <c r="I33" s="36" t="inlineStr">
-        <is>
-          <t>подключение к сети — ЭОМ</t>
-        </is>
-      </c>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="29" t="n"/>
     </row>
     <row r="34" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A34" s="30" t="inlineStr">
@@ -1940,7 +1944,7 @@
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>Установка бака мембранного для ГВС 12 л</t>
+          <t>Установка насосов циркуляционных ГВС Н8, Н9 с подключением</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -1949,12 +1953,16 @@
         </is>
       </c>
       <c r="D34" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="33" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
+        <is>
+          <t>1 + 1 = 2</t>
+        </is>
+      </c>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 8, 11; И05.09.26-ВК.СО, поз. 3</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 1, 2</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -1964,10 +1972,14 @@
       </c>
       <c r="H34" s="30" t="inlineStr">
         <is>
-          <t>8 11 15</t>
-        </is>
-      </c>
-      <c r="I34" s="36" t="n"/>
+          <t>7 8 10 11 15</t>
+        </is>
+      </c>
+      <c r="I34" s="36" t="inlineStr">
+        <is>
+          <t>подключение к сети — ЭОМ</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="30" t="inlineStr">
@@ -1977,7 +1989,7 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>Установка группы безопасности бойлера Б2</t>
+          <t>Установка бака мембранного для ГВС 12 л</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -1991,141 +2003,141 @@
       <c r="E35" s="33" t="n"/>
       <c r="F35" s="34" t="inlineStr">
         <is>
+          <t>И05.09.26-ВК, см. листы 8, 11; И05.09.26-ВК.СО, поз. 3</t>
+        </is>
+      </c>
+      <c r="G35" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H35" s="30" t="inlineStr">
+        <is>
+          <t>8 11 15</t>
+        </is>
+      </c>
+      <c r="I35" s="36" t="n"/>
+    </row>
+    <row r="36" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>Установка группы безопасности бойлера Б2</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="34" t="inlineStr">
+        <is>
           <t>И05.09.26-ВК, см. листы 8, 11; И05.09.26-ВК.СО, поз. 4</t>
         </is>
       </c>
-      <c r="G35" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H35" s="30" t="inlineStr">
+      <c r="G36" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>8 11 15</t>
         </is>
       </c>
-      <c r="I35" s="36" t="n"/>
-    </row>
-    <row r="36" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B36" s="31" t="inlineStr">
+      <c r="I36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>Установка полотенцесушителей водяных на Т4 с комплектами запорных клапанов</t>
         </is>
       </c>
-      <c r="C36" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D36" s="32" t="n">
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="E36" s="33" t="inlineStr">
+      <c r="E37" s="33" t="inlineStr">
         <is>
           <t>1 + 1 + 2 + 1 = 5</t>
         </is>
       </c>
-      <c r="F36" s="34" t="inlineStr">
+      <c r="F37" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 5, 6, 7, 8</t>
         </is>
       </c>
-      <c r="G36" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H36" s="30" t="inlineStr">
+      <c r="G37" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H37" s="30" t="inlineStr">
         <is>
           <t>5 8 10 11 15</t>
         </is>
       </c>
-      <c r="I36" s="36" t="inlineStr">
+      <c r="I37" s="36" t="inlineStr">
         <is>
           <t>5 шт.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A37" s="27" t="inlineStr">
+    <row r="38" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>Система бытовой канализации К1</t>
         </is>
       </c>
-      <c r="B37" s="28" t="n"/>
-      <c r="C37" s="28" t="n"/>
-      <c r="D37" s="28" t="n"/>
-      <c r="E37" s="28" t="n"/>
-      <c r="F37" s="28" t="n"/>
-      <c r="G37" s="28" t="n"/>
-      <c r="H37" s="28" t="n"/>
-      <c r="I37" s="29" t="n"/>
-    </row>
-    <row r="38" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A38" s="30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B38" s="31" t="inlineStr">
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="29" t="n"/>
+    </row>
+    <row r="39" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="inlineStr">
         <is>
           <t>Прокладка трубопроводов из малошумных канализационных труб Ø110 (стояки с вытяжными частями, сборный под потолком гаража, подъёмы к приборам) с фасонными частями</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C39" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D38" s="32" t="n">
-        <v>28</v>
-      </c>
-      <c r="E38" s="33" t="n"/>
-      <c r="F38" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 33, 55</t>
-        </is>
-      </c>
-      <c r="G38" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H38" s="30" t="inlineStr">
-        <is>
-          <t>5 6 9 12 16 17</t>
-        </is>
-      </c>
-      <c r="I38" s="36" t="n"/>
-    </row>
-    <row r="39" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A39" s="30" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B39" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка трубопроводов из малошумных канализационных труб Ø50 (отводы и подъёмы к приборам) с фасонными частями</t>
-        </is>
-      </c>
-      <c r="C39" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
       <c r="D39" s="32" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E39" s="33" t="n"/>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 34, 56</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 39, 61</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -2140,7 +2152,7 @@
       </c>
       <c r="I39" s="36" t="n"/>
     </row>
-    <row r="40" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="40" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A40" s="30" t="inlineStr">
         <is>
           <t>32</t>
@@ -2148,7 +2160,7 @@
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из малошумных канализационных труб Ø32 (конденсат кондиционеров) с фасонными частями</t>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø50 (отводы и подъёмы к приборам) с фасонными частями</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -2157,12 +2169,12 @@
         </is>
       </c>
       <c r="D40" s="32" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 35, 57</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 40, 62</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2185,7 +2197,7 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 в грунте под плитой на песчаном основании</t>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø32 (конденсат кондиционеров) с фасонными частями</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -2194,12 +2206,12 @@
         </is>
       </c>
       <c r="D41" s="32" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 36</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 41, 63</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -2209,16 +2221,12 @@
       </c>
       <c r="H41" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 14 16</t>
-        </is>
-      </c>
-      <c r="I41" s="36" t="inlineStr">
-        <is>
-          <t>под плитой — решение Заказчика</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>5 6 9 12 16 17</t>
+        </is>
+      </c>
+      <c r="I41" s="36" t="n"/>
+    </row>
+    <row r="42" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A42" s="30" t="inlineStr">
         <is>
           <t>34</t>
@@ -2226,7 +2234,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП наружных труб Ø110 SN8 в грунте под плитой на песчаном основании с фасонными частями</t>
+          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 в грунте под плитой на песчаном основании</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -2235,12 +2243,12 @@
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 37</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 42</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -2255,97 +2263,97 @@
       </c>
       <c r="I42" s="36" t="inlineStr">
         <is>
+          <t>под плитой — решение Заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A43" s="30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка трубопроводов из ПП наружных труб Ø110 SN8 в грунте под плитой на песчаном основании с фасонными частями</t>
+        </is>
+      </c>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="n">
+        <v>55</v>
+      </c>
+      <c r="E43" s="33" t="n"/>
+      <c r="F43" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 43</t>
+        </is>
+      </c>
+      <c r="G43" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H43" s="30" t="inlineStr">
+        <is>
+          <t>6 9 12 14 16</t>
+        </is>
+      </c>
+      <c r="I43" s="36" t="inlineStr">
+        <is>
           <t>в т. ч. выпуски до границы с НВК</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A43" s="30" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B43" s="31" t="inlineStr">
+    <row r="44" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
         <is>
           <t>Устройство песчаного основания 100 мм и обсыпки 300 мм над верхом трубы с ручным уплотнением</t>
         </is>
       </c>
-      <c r="C43" s="32" t="inlineStr">
+      <c r="C44" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D43" s="32" t="n">
-        <v>70</v>
-      </c>
-      <c r="E43" s="33" t="inlineStr">
-        <is>
-          <t>27 + 40 + 3 = 70</t>
-        </is>
-      </c>
-      <c r="F43" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 36, 37, 38</t>
-        </is>
-      </c>
-      <c r="G43" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H43" s="30" t="inlineStr">
+      <c r="D44" s="32" t="n">
+        <v>83</v>
+      </c>
+      <c r="E44" s="33" t="inlineStr">
+        <is>
+          <t>25 + 55 + 3 = 83</t>
+        </is>
+      </c>
+      <c r="F44" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 42, 43, 44</t>
+        </is>
+      </c>
+      <c r="G44" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H44" s="30" t="inlineStr">
         <is>
           <t>14 16</t>
         </is>
       </c>
-      <c r="I43" s="36" t="inlineStr">
+      <c r="I44" s="36" t="inlineStr">
         <is>
           <t>до бетонирования плиты</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="inlineStr">
-        <is>
-          <t>Установка футляров Ø160 SN8 на выпусках под краем плиты</t>
-        </is>
-      </c>
-      <c r="C44" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D44" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="33" t="n"/>
-      <c r="F44" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 39</t>
-        </is>
-      </c>
-      <c r="G44" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H44" s="30" t="inlineStr">
-        <is>
-          <t>14 16</t>
-        </is>
-      </c>
-      <c r="I44" s="36" t="inlineStr">
-        <is>
-          <t>узел 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="45" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A45" s="30" t="inlineStr">
         <is>
           <t>37</t>
@@ -2353,21 +2361,21 @@
       </c>
       <c r="B45" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопровода К2 Ø110 SN8 от пескоуловителя гаража под плитой на песчаном основании</t>
+          <t>Установка футляров Ø160 SN8 под краем плиты (выпуски, ввод линии бани)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" s="33" t="n"/>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 14; И05.09.26-ВК.СО, поз. 38</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 45</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -2377,16 +2385,16 @@
       </c>
       <c r="H45" s="30" t="inlineStr">
         <is>
-          <t>4 14 16</t>
+          <t>14 16</t>
         </is>
       </c>
       <c r="I45" s="36" t="inlineStr">
         <is>
-          <t>до границы с НВК (ливневая сеть)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>узел 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A46" s="30" t="inlineStr">
         <is>
           <t>38</t>
@@ -2394,7 +2402,7 @@
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>Устройство лотка водоотводного DN100 с решёткой C250 в полу гаража</t>
+          <t>Прокладка трубопровода К2 Ø110 SN8 от пескоуловителя гаража под плитой на песчаном основании</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -2403,12 +2411,12 @@
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="E46" s="33" t="n"/>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 94</t>
+          <t>И05.09.26-ВК, см. листы 4, 14; И05.09.26-ВК.СО, поз. 44</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -2418,12 +2426,12 @@
       </c>
       <c r="H46" s="30" t="inlineStr">
         <is>
-          <t>4 18</t>
+          <t>4 14 16</t>
         </is>
       </c>
       <c r="I46" s="36" t="inlineStr">
         <is>
-          <t>углубление в стяжке — АР/КР (ТЗ-1)</t>
+          <t>до границы с НВК (ливневая сеть)</t>
         </is>
       </c>
     </row>
@@ -2435,21 +2443,21 @@
       </c>
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>Установка пескоуловителя DN100 с корзиной</t>
+          <t>Устройство лотка водоотводного DN100 с решёткой C250 в полу гаража</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D47" s="32" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="E47" s="33" t="n"/>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 95</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 100</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -2464,111 +2472,115 @@
       </c>
       <c r="I47" s="36" t="inlineStr">
         <is>
+          <t>углубление в стяжке — АР/КР (ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>Установка пескоуловителя DN100 с корзиной</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="33" t="n"/>
+      <c r="F48" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 101</t>
+        </is>
+      </c>
+      <c r="G48" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H48" s="30" t="inlineStr">
+        <is>
+          <t>4 19</t>
+        </is>
+      </c>
+      <c r="I48" s="36" t="inlineStr">
+        <is>
           <t>понижение плиты — КР (ТЗ-1)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A48" s="30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B48" s="31" t="inlineStr">
+    <row r="49" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="inlineStr">
         <is>
           <t>Установка тройников косых канализационных</t>
         </is>
       </c>
-      <c r="C48" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D48" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="E48" s="33" t="inlineStr">
-        <is>
-          <t>5 + 2 + 4 + 2 + 6 + 1 = 20</t>
-        </is>
-      </c>
-      <c r="F48" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 58, 59, 60, 63, 64, 65</t>
-        </is>
-      </c>
-      <c r="G48" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H48" s="30" t="inlineStr">
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="E49" s="33" t="inlineStr">
+        <is>
+          <t>6 + 2 + 2 + 6 + 1 = 17</t>
+        </is>
+      </c>
+      <c r="F49" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 64, 65, 66, 68, 69</t>
+        </is>
+      </c>
+      <c r="G49" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H49" s="30" t="inlineStr">
         <is>
           <t>5 6 9 12 17</t>
         </is>
       </c>
-      <c r="I48" s="36" t="n"/>
-    </row>
-    <row r="49" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="inlineStr">
+      <c r="I49" s="36" t="n"/>
+    </row>
+    <row r="50" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>Установка ревизий Ø110</t>
         </is>
       </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" s="33" t="n"/>
-      <c r="F49" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 66</t>
-        </is>
-      </c>
-      <c r="G49" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H49" s="30" t="inlineStr">
-        <is>
-          <t>5 6 12 17</t>
-        </is>
-      </c>
-      <c r="I49" s="36" t="n"/>
-    </row>
-    <row r="50" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A50" s="30" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B50" s="31" t="inlineStr">
-        <is>
-          <t>Устройство прочисток в грунте с выводом к люку в полу (тройник, отвод, стояк, заглушка, гильза, люк)</t>
-        </is>
-      </c>
       <c r="C50" s="32" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50" s="33" t="n"/>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 93</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 71</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2578,55 +2590,51 @@
       </c>
       <c r="H50" s="30" t="inlineStr">
         <is>
-          <t>6 9 14 18</t>
-        </is>
-      </c>
-      <c r="I50" s="36" t="inlineStr">
+          <t>5 6 12 17</t>
+        </is>
+      </c>
+      <c r="I50" s="36" t="n"/>
+    </row>
+    <row r="51" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>Устройство прочисток в грунте с выводом в стену до +0,500 (тройник 45°, отвод, стояк в О-блоке, заглушка, гильза)</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="33" t="n"/>
+      <c r="F51" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 70</t>
+        </is>
+      </c>
+      <c r="G51" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H51" s="30" t="inlineStr">
+        <is>
+          <t>6 9 14 17</t>
+        </is>
+      </c>
+      <c r="I51" s="36" t="inlineStr">
         <is>
           <t>узел 5 листа 14</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A51" s="30" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>Установка трапов с сухим затвором</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E51" s="33" t="inlineStr">
-        <is>
-          <t>2 + 1 + 1 + 1 = 5</t>
-        </is>
-      </c>
-      <c r="F51" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 85, 86, 87, 88</t>
-        </is>
-      </c>
-      <c r="G51" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H51" s="30" t="inlineStr">
-        <is>
-          <t>4 6 9 18</t>
-        </is>
-      </c>
-      <c r="I51" s="36" t="n"/>
     </row>
     <row r="52" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A52" s="30" t="inlineStr">
@@ -2636,7 +2644,7 @@
       </c>
       <c r="B52" s="31" t="inlineStr">
         <is>
-          <t>Установка сифонов конденсата, сифона стиральной машины и воронки с разрывом струи</t>
+          <t>Установка люков ревизионных нажимных 300×400 в стенах у прочисток и ревизий стояков</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -2647,14 +2655,10 @@
       <c r="D52" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="E52" s="33" t="inlineStr">
-        <is>
-          <t>3 + 1 + 1 = 5</t>
-        </is>
-      </c>
+      <c r="E52" s="33" t="n"/>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 89, 90, 91</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 99</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2664,12 +2668,12 @@
       </c>
       <c r="H52" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 14 18</t>
+          <t>6 9 14 18</t>
         </is>
       </c>
       <c r="I52" s="36" t="inlineStr">
         <is>
-          <t>узел 7 листа 14</t>
+          <t>узел 5 листа 14</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2685,7 @@
       </c>
       <c r="B53" s="31" t="inlineStr">
         <is>
-          <t>Установка проходных кровельных элементов для вытяжных частей стояков Ø110</t>
+          <t>Установка трапов с сухим затвором</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -2690,12 +2694,16 @@
         </is>
       </c>
       <c r="D53" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="33" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="E53" s="33" t="inlineStr">
+        <is>
+          <t>2 + 1 + 1 + 1 = 5</t>
+        </is>
+      </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 92</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 91, 92, 93, 94</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -2705,14 +2713,10 @@
       </c>
       <c r="H53" s="30" t="inlineStr">
         <is>
-          <t>12 14 18</t>
-        </is>
-      </c>
-      <c r="I53" s="36" t="inlineStr">
-        <is>
-          <t>узел 6 листа 14</t>
-        </is>
-      </c>
+          <t>4 6 9 18</t>
+        </is>
+      </c>
+      <c r="I53" s="36" t="n"/>
     </row>
     <row r="54" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A54" s="30" t="inlineStr">
@@ -2722,7 +2726,7 @@
       </c>
       <c r="B54" s="31" t="inlineStr">
         <is>
-          <t>Крепление трубопроводов К1 хомутами с резиновым вкладышем</t>
+          <t>Установка сифонов конденсата, сифона стиральной машины и воронки с разрывом струи</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -2731,16 +2735,16 @@
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E54" s="33" t="inlineStr">
         <is>
-          <t>24 + 2 + 34 = 60</t>
+          <t>3 + 1 + 1 = 5</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 120, 121, 122</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 95, 96, 97</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -2750,131 +2754,135 @@
       </c>
       <c r="H54" s="30" t="inlineStr">
         <is>
-          <t>5 14 19</t>
-        </is>
-      </c>
-      <c r="I54" s="36" t="n"/>
-    </row>
-    <row r="55" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A55" s="27" t="inlineStr">
-        <is>
-          <t>Защита от протечек</t>
-        </is>
-      </c>
-      <c r="B55" s="28" t="n"/>
-      <c r="C55" s="28" t="n"/>
-      <c r="D55" s="28" t="n"/>
-      <c r="E55" s="28" t="n"/>
-      <c r="F55" s="28" t="n"/>
-      <c r="G55" s="28" t="n"/>
-      <c r="H55" s="28" t="n"/>
-      <c r="I55" s="29" t="n"/>
+          <t>5 6 9 14 18</t>
+        </is>
+      </c>
+      <c r="I54" s="36" t="inlineStr">
+        <is>
+          <t>узел 7 листа 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A55" s="30" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>Установка проходных кровельных элементов для вытяжных частей стояков Ø110</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="33" t="n"/>
+      <c r="F55" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 98</t>
+        </is>
+      </c>
+      <c r="G55" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H55" s="30" t="inlineStr">
+        <is>
+          <t>12 14 18</t>
+        </is>
+      </c>
+      <c r="I55" s="36" t="inlineStr">
+        <is>
+          <t>узел 6 листа 14</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="30" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B56" s="31" t="inlineStr">
         <is>
+          <t>Крепление трубопроводов К1 хомутами с резиновым вкладышем</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="n">
+        <v>63</v>
+      </c>
+      <c r="E56" s="33" t="inlineStr">
+        <is>
+          <t>26 + 2 + 35 = 63</t>
+        </is>
+      </c>
+      <c r="F56" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 128, 129, 130</t>
+        </is>
+      </c>
+      <c r="G56" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H56" s="30" t="inlineStr">
+        <is>
+          <t>5 14 20</t>
+        </is>
+      </c>
+      <c r="I56" s="36" t="n"/>
+    </row>
+    <row r="57" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>Защита от протечек</t>
+        </is>
+      </c>
+      <c r="B57" s="28" t="n"/>
+      <c r="C57" s="28" t="n"/>
+      <c r="D57" s="28" t="n"/>
+      <c r="E57" s="28" t="n"/>
+      <c r="F57" s="28" t="n"/>
+      <c r="G57" s="28" t="n"/>
+      <c r="H57" s="28" t="n"/>
+      <c r="I57" s="29" t="n"/>
+    </row>
+    <row r="58" ht="45" customHeight="1" thickBot="1">
+      <c r="A58" s="30" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
           <t>Установка контроллеров системы защиты от протечек с подключением кранов и датчиков</t>
         </is>
       </c>
-      <c r="C56" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D56" s="32" t="n">
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="n">
         <v>2</v>
-      </c>
-      <c r="E56" s="33" t="n"/>
-      <c r="F56" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 96</t>
-        </is>
-      </c>
-      <c r="G56" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H56" s="30" t="inlineStr">
-        <is>
-          <t>2 4 8 18</t>
-        </is>
-      </c>
-      <c r="I56" s="36" t="inlineStr">
-        <is>
-          <t>питание 230 В и сигнал в умный дом — ЭОМ/СС (ТЗ-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A57" s="30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B57" s="31" t="inlineStr">
-        <is>
-          <t>Установка кранов шаровых с электроприводом Ду 20–32</t>
-        </is>
-      </c>
-      <c r="C57" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D57" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E57" s="33" t="inlineStr">
-        <is>
-          <t>1 + 1 = 2</t>
-        </is>
-      </c>
-      <c r="F57" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 97, 98</t>
-        </is>
-      </c>
-      <c r="G57" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H57" s="30" t="inlineStr">
-        <is>
-          <t>4 7 8 18</t>
-        </is>
-      </c>
-      <c r="I57" s="36" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1" thickBot="1">
-      <c r="A58" s="30" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="inlineStr">
-        <is>
-          <t>Установка датчиков протечки проводных на полу</t>
-        </is>
-      </c>
-      <c r="C58" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="n">
-        <v>18</v>
       </c>
       <c r="E58" s="33" t="n"/>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 99</t>
+          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 102</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -2884,10 +2892,14 @@
       </c>
       <c r="H58" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 18</t>
-        </is>
-      </c>
-      <c r="I58" s="36" t="n"/>
+          <t>2 4 8 19</t>
+        </is>
+      </c>
+      <c r="I58" s="36" t="inlineStr">
+        <is>
+          <t>питание 230 В и сигнал в умный дом — ЭОМ/СС (ТЗ-2)</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="30" t="inlineStr">
@@ -2897,21 +2909,25 @@
       </c>
       <c r="B59" s="31" t="inlineStr">
         <is>
-          <t>Прокладка кабелей датчиков протечки в гофротрубе</t>
+          <t>Установка кранов шаровых с электроприводом Ду 20–32</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D59" s="32" t="n">
-        <v>160</v>
-      </c>
-      <c r="E59" s="33" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E59" s="33" t="inlineStr">
+        <is>
+          <t>1 + 1 = 2</t>
+        </is>
+      </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 100</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 103, 104</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -2921,53 +2937,71 @@
       </c>
       <c r="H59" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 18</t>
-        </is>
-      </c>
-      <c r="I59" s="36" t="inlineStr">
-        <is>
-          <t>совместно с ЭОМ/СС</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
-        <is>
-          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
-        </is>
-      </c>
-      <c r="B60" s="28" t="n"/>
-      <c r="C60" s="28" t="n"/>
-      <c r="D60" s="28" t="n"/>
-      <c r="E60" s="28" t="n"/>
-      <c r="F60" s="28" t="n"/>
-      <c r="G60" s="28" t="n"/>
-      <c r="H60" s="28" t="n"/>
-      <c r="I60" s="29" t="n"/>
+          <t>4 7 8 19</t>
+        </is>
+      </c>
+      <c r="I59" s="36" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
+          <t>Установка датчиков протечки проводных на полу</t>
+        </is>
+      </c>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="E60" s="33" t="n"/>
+      <c r="F60" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 105</t>
+        </is>
+      </c>
+      <c r="G60" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H60" s="30" t="inlineStr">
+        <is>
+          <t>3 4 5 8 19</t>
+        </is>
+      </c>
+      <c r="I60" s="36" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="30" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>Установка унитазов подвесных с инсталляциями</t>
+          <t>Прокладка кабелей датчиков протечки в гофротрубе</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D61" s="32" t="n">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="E61" s="33" t="n"/>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 79</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 106</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -2977,47 +3011,29 @@
       </c>
       <c r="H61" s="30" t="inlineStr">
         <is>
-          <t>3 5 6 8 9 18</t>
-        </is>
-      </c>
-      <c r="I61" s="36" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="inlineStr">
-        <is>
-          <t>Установка умывальников со смесителями и сифонами</t>
-        </is>
-      </c>
-      <c r="C62" s="32" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="D62" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E62" s="33" t="n"/>
-      <c r="F62" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 80</t>
-        </is>
-      </c>
-      <c r="G62" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H62" s="30" t="inlineStr">
-        <is>
-          <t>3 5 8 18</t>
-        </is>
-      </c>
-      <c r="I62" s="36" t="n"/>
+          <t>3 4 5 8 19</t>
+        </is>
+      </c>
+      <c r="I61" s="36" t="inlineStr">
+        <is>
+          <t>совместно с ЭОМ/СС</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
+        </is>
+      </c>
+      <c r="B62" s="28" t="n"/>
+      <c r="C62" s="28" t="n"/>
+      <c r="D62" s="28" t="n"/>
+      <c r="E62" s="28" t="n"/>
+      <c r="F62" s="28" t="n"/>
+      <c r="G62" s="28" t="n"/>
+      <c r="H62" s="28" t="n"/>
+      <c r="I62" s="29" t="n"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="30" t="inlineStr">
@@ -3027,7 +3043,7 @@
       </c>
       <c r="B63" s="31" t="inlineStr">
         <is>
-          <t>Установка ванн со смесителями и сифонами</t>
+          <t>Установка унитазов подвесных с инсталляциями</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -3036,12 +3052,12 @@
         </is>
       </c>
       <c r="D63" s="32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63" s="33" t="n"/>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 81</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 85</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -3051,7 +3067,7 @@
       </c>
       <c r="H63" s="30" t="inlineStr">
         <is>
-          <t>5 8 18</t>
+          <t>3 5 6 8 9 18</t>
         </is>
       </c>
       <c r="I63" s="36" t="n"/>
@@ -3064,7 +3080,7 @@
       </c>
       <c r="B64" s="31" t="inlineStr">
         <is>
-          <t>Установка душевых систем, кабины, подключение трапов</t>
+          <t>Установка умывальников со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -3073,12 +3089,12 @@
         </is>
       </c>
       <c r="D64" s="32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E64" s="33" t="n"/>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 82</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 86</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -3088,7 +3104,7 @@
       </c>
       <c r="H64" s="30" t="inlineStr">
         <is>
-          <t>4 5 8 18</t>
+          <t>3 5 8 18</t>
         </is>
       </c>
       <c r="I64" s="36" t="n"/>
@@ -3101,7 +3117,7 @@
       </c>
       <c r="B65" s="31" t="inlineStr">
         <is>
-          <t>Установка моек кухонных со смесителями и сифонами</t>
+          <t>Установка ванн со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -3110,12 +3126,12 @@
         </is>
       </c>
       <c r="D65" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" s="33" t="n"/>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 83</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 87</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -3125,7 +3141,7 @@
       </c>
       <c r="H65" s="30" t="inlineStr">
         <is>
-          <t>3 8 18</t>
+          <t>5 8 18</t>
         </is>
       </c>
       <c r="I65" s="36" t="n"/>
@@ -3138,21 +3154,21 @@
       </c>
       <c r="B66" s="31" t="inlineStr">
         <is>
-          <t>Установка смесителя для наполнения СПА</t>
+          <t>Установка душевых систем, кабины, подключение трапов</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D66" s="32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 84</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 88</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3162,183 +3178,205 @@
       </c>
       <c r="H66" s="30" t="inlineStr">
         <is>
+          <t>4 5 8 18</t>
+        </is>
+      </c>
+      <c r="I66" s="36" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>Установка моек кухонных со смесителями и сифонами</t>
+        </is>
+      </c>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="33" t="n"/>
+      <c r="F67" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 89</t>
+        </is>
+      </c>
+      <c r="G67" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>3 8 18</t>
+        </is>
+      </c>
+      <c r="I67" s="36" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>Установка смесителя для наполнения СПА</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="33" t="n"/>
+      <c r="F68" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 90</t>
+        </is>
+      </c>
+      <c r="G68" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
           <t>8 18</t>
         </is>
       </c>
-      <c r="I66" s="36" t="n"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="27" t="inlineStr">
+      <c r="I68" s="36" t="n"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
         <is>
           <t>Тепловая изоляция</t>
         </is>
       </c>
-      <c r="B67" s="28" t="n"/>
-      <c r="C67" s="28" t="n"/>
-      <c r="D67" s="28" t="n"/>
-      <c r="E67" s="28" t="n"/>
-      <c r="F67" s="28" t="n"/>
-      <c r="G67" s="28" t="n"/>
-      <c r="H67" s="28" t="n"/>
-      <c r="I67" s="29" t="n"/>
-    </row>
-    <row r="68" ht="45" customHeight="1">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B68" s="31" t="inlineStr">
+      <c r="B69" s="28" t="n"/>
+      <c r="C69" s="28" t="n"/>
+      <c r="D69" s="28" t="n"/>
+      <c r="E69" s="28" t="n"/>
+      <c r="F69" s="28" t="n"/>
+      <c r="G69" s="28" t="n"/>
+      <c r="H69" s="28" t="n"/>
+      <c r="I69" s="29" t="n"/>
+    </row>
+    <row r="70" ht="45" customHeight="1">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
         <is>
           <t>Изоляция трубопроводов Т3, Т4 трубками из вспененного полиэтилена толщиной 13 мм</t>
         </is>
       </c>
-      <c r="C68" s="32" t="inlineStr">
+      <c r="C70" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D68" s="32" t="n">
-        <v>165</v>
-      </c>
-      <c r="E68" s="33" t="inlineStr">
-        <is>
-          <t>71 + 85 + 9 = 165</t>
-        </is>
-      </c>
-      <c r="F68" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 101, 102, 103</t>
-        </is>
-      </c>
-      <c r="G68" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>3 5 8 10 11 18</t>
-        </is>
-      </c>
-      <c r="I68" s="36" t="n"/>
-    </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="inlineStr">
+      <c r="D70" s="32" t="n">
+        <v>163</v>
+      </c>
+      <c r="E70" s="33" t="inlineStr">
+        <is>
+          <t>42 + 85 + 36 = 163</t>
+        </is>
+      </c>
+      <c r="F70" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 107, 108, 109</t>
+        </is>
+      </c>
+      <c r="G70" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>3 5 8 10 11 19</t>
+        </is>
+      </c>
+      <c r="I70" s="36" t="n"/>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="inlineStr">
         <is>
           <t>Изоляция трубопроводов В1 трубками из вспененного полиэтилена толщиной 9 мм</t>
         </is>
       </c>
-      <c r="C69" s="32" t="inlineStr">
+      <c r="C71" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D69" s="32" t="n">
-        <v>204</v>
-      </c>
-      <c r="E69" s="33" t="inlineStr">
-        <is>
-          <t>93 + 53 + 47 + 11 = 204</t>
-        </is>
-      </c>
-      <c r="F69" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 104, 105, 106, 107</t>
-        </is>
-      </c>
-      <c r="G69" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="D71" s="32" t="n">
+        <v>188</v>
+      </c>
+      <c r="E71" s="33" t="inlineStr">
+        <is>
+          <t>72 + 36 + 66 + 14 = 188</t>
+        </is>
+      </c>
+      <c r="F71" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 110, 111, 112, 113</t>
+        </is>
+      </c>
+      <c r="G71" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H71" s="30" t="inlineStr">
         <is>
           <t>3 5 8 10 11 19</t>
         </is>
       </c>
-      <c r="I69" s="36" t="n"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="inlineStr">
-        <is>
-          <t>Изоляция ввода ПЭ 32 в проёме фундамента</t>
-        </is>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E70" s="33" t="n"/>
-      <c r="F70" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 108</t>
-        </is>
-      </c>
-      <c r="G70" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>14 19</t>
-        </is>
-      </c>
-      <c r="I70" s="36" t="n"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="27" t="inlineStr">
-        <is>
-          <t>Проходы через строительные конструкции</t>
-        </is>
-      </c>
-      <c r="B71" s="28" t="n"/>
-      <c r="C71" s="28" t="n"/>
-      <c r="D71" s="28" t="n"/>
-      <c r="E71" s="28" t="n"/>
-      <c r="F71" s="28" t="n"/>
-      <c r="G71" s="28" t="n"/>
-      <c r="H71" s="28" t="n"/>
-      <c r="I71" s="29" t="n"/>
+      <c r="I71" s="36" t="n"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B72" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
+          <t>Изоляция ввода ПЭ 32 в проёме фундамента</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D72" s="32" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E72" s="33" t="n"/>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 111</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 114</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -3351,52 +3389,22 @@
           <t>14 19</t>
         </is>
       </c>
-      <c r="I72" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="inlineStr">
-        <is>
-          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
-        </is>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="E73" s="33" t="n"/>
-      <c r="F73" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 111</t>
-        </is>
-      </c>
-      <c r="G73" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H73" s="30" t="inlineStr">
-        <is>
-          <t>14 19</t>
-        </is>
-      </c>
-      <c r="I73" s="36" t="inlineStr">
-        <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
+      <c r="I72" s="36" t="n"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>Проходы через строительные конструкции</t>
+        </is>
+      </c>
+      <c r="B73" s="28" t="n"/>
+      <c r="C73" s="28" t="n"/>
+      <c r="D73" s="28" t="n"/>
+      <c r="E73" s="28" t="n"/>
+      <c r="F73" s="28" t="n"/>
+      <c r="G73" s="28" t="n"/>
+      <c r="H73" s="28" t="n"/>
+      <c r="I73" s="29" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="30" t="inlineStr">
@@ -3406,7 +3414,7 @@
       </c>
       <c r="B74" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -3415,12 +3423,12 @@
         </is>
       </c>
       <c r="D74" s="32" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E74" s="33" t="n"/>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 112</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 117</t>
         </is>
       </c>
       <c r="G74" s="35" t="inlineStr">
@@ -3447,7 +3455,7 @@
       </c>
       <c r="B75" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
+          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -3456,12 +3464,12 @@
         </is>
       </c>
       <c r="D75" s="32" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 112</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 117</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -3488,7 +3496,7 @@
       </c>
       <c r="B76" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -3497,12 +3505,12 @@
         </is>
       </c>
       <c r="D76" s="32" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 113</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 118</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3529,7 +3537,7 @@
       </c>
       <c r="B77" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
+          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -3538,12 +3546,12 @@
         </is>
       </c>
       <c r="D77" s="32" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 113</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 118</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -3562,7 +3570,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="45" customHeight="1">
+    <row r="78" ht="30" customHeight="1">
       <c r="A78" s="30" t="inlineStr">
         <is>
           <t>66</t>
@@ -3570,21 +3578,21 @@
       </c>
       <c r="B78" s="31" t="inlineStr">
         <is>
-          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D78" s="32" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E78" s="33" t="n"/>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 114</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 119</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -3597,9 +3605,13 @@
           <t>14 19</t>
         </is>
       </c>
-      <c r="I78" s="36" t="n"/>
-    </row>
-    <row r="79" ht="45" customHeight="1">
+      <c r="I78" s="36" t="inlineStr">
+        <is>
+          <t>по толщине конструкции</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
       <c r="A79" s="30" t="inlineStr">
         <is>
           <t>67</t>
@@ -3607,21 +3619,21 @@
       </c>
       <c r="B79" s="31" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента у ввода и выпусков эластичным водогазонепроницаемым материалом</t>
+          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D79" s="32" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E79" s="33" t="n"/>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 115</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 119</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -3636,52 +3648,70 @@
       </c>
       <c r="I79" s="36" t="inlineStr">
         <is>
-          <t>проёмы — КР (ТЗ-1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="27" t="inlineStr">
-        <is>
-          <t>Испытания и пусконаладочные работы</t>
-        </is>
-      </c>
-      <c r="B80" s="28" t="n"/>
-      <c r="C80" s="28" t="n"/>
-      <c r="D80" s="28" t="n"/>
-      <c r="E80" s="28" t="n"/>
-      <c r="F80" s="28" t="n"/>
-      <c r="G80" s="28" t="n"/>
-      <c r="H80" s="28" t="n"/>
-      <c r="I80" s="29" t="n"/>
+          <t>п. 11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="45" customHeight="1">
+      <c r="A80" s="30" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B80" s="31" t="inlineStr">
+        <is>
+          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="33" t="n"/>
+      <c r="F80" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 120</t>
+        </is>
+      </c>
+      <c r="G80" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H80" s="30" t="inlineStr">
+        <is>
+          <t>14 19</t>
+        </is>
+      </c>
+      <c r="I80" s="36" t="n"/>
     </row>
     <row r="81" ht="45" customHeight="1">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B81" s="31" t="inlineStr">
         <is>
-          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
+          <t>Заделка проёмов фундамента у ввода и футляров эластичным водогазонепроницаемым материалом</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D81" s="32" t="n">
-        <v>369</v>
-      </c>
-      <c r="E81" s="33" t="inlineStr">
-        <is>
-          <t>11 + 55 + 138 + 163 + 2 = 369</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E81" s="33" t="n"/>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 28, 29, 30, 31, 32</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 121</t>
         </is>
       </c>
       <c r="G81" s="35" t="inlineStr">
@@ -3691,42 +3721,38 @@
       </c>
       <c r="H81" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
+          <t>14 19</t>
         </is>
       </c>
       <c r="I81" s="36" t="inlineStr">
         <is>
-          <t>в т. ч. до закрытия в конструкциях</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="45" customHeight="1">
+          <t>проёмы — КР (ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B82" s="31" t="inlineStr">
         <is>
-          <t>Испытание систем канализации К1 и К2 (участок К2-1) проливом воды</t>
+          <t>Заделка проёмов под пучки труб в плитах и стенах</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D82" s="32" t="n">
-        <v>124</v>
-      </c>
-      <c r="E82" s="33" t="inlineStr">
-        <is>
-          <t>28 + 25 + 1 + 27 + 40 + 3 = 124</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E82" s="33" t="n"/>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 33, 34, 35, 36, 37, 38</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 122</t>
         </is>
       </c>
       <c r="G82" s="35" t="inlineStr">
@@ -3736,187 +3762,329 @@
       </c>
       <c r="H82" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
-        </is>
-      </c>
-      <c r="I82" s="36" t="n"/>
+          <t>14 19</t>
+        </is>
+      </c>
+      <c r="I82" s="36" t="inlineStr">
+        <is>
+          <t>ТЗ-1, лист 4</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B83" s="31" t="inlineStr">
         <is>
+          <t>Утепление сборного К1-1 под террасой 1.13 плитами ЭППС 50 мм</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E83" s="33" t="n"/>
+      <c r="F83" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 6; И05.09.26-ВК.СО, поз. 123</t>
+        </is>
+      </c>
+      <c r="G83" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H83" s="30" t="inlineStr">
+        <is>
+          <t>6 19</t>
+        </is>
+      </c>
+      <c r="I83" s="36" t="n"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>Испытания и пусконаладочные работы</t>
+        </is>
+      </c>
+      <c r="B84" s="28" t="n"/>
+      <c r="C84" s="28" t="n"/>
+      <c r="D84" s="28" t="n"/>
+      <c r="E84" s="28" t="n"/>
+      <c r="F84" s="28" t="n"/>
+      <c r="G84" s="28" t="n"/>
+      <c r="H84" s="28" t="n"/>
+      <c r="I84" s="29" t="n"/>
+    </row>
+    <row r="85" ht="45" customHeight="1">
+      <c r="A85" s="30" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
+        </is>
+      </c>
+      <c r="C85" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D85" s="32" t="n">
+        <v>352</v>
+      </c>
+      <c r="E85" s="33" t="inlineStr">
+        <is>
+          <t>14 + 101 + 121 + 114 + 2 = 352</t>
+        </is>
+      </c>
+      <c r="F85" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 34, 35, 36, 37, 38</t>
+        </is>
+      </c>
+      <c r="G85" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H85" s="30" t="inlineStr">
+        <is>
+          <t>1 2 16</t>
+        </is>
+      </c>
+      <c r="I85" s="36" t="inlineStr">
+        <is>
+          <t>в т. ч. до закрытия в конструкциях</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="45" customHeight="1">
+      <c r="A86" s="30" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B86" s="31" t="inlineStr">
+        <is>
+          <t>Испытание систем канализации К1 и К2 (участок К2-1) проливом воды</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D86" s="32" t="n">
+        <v>142</v>
+      </c>
+      <c r="E86" s="33" t="inlineStr">
+        <is>
+          <t>32 + 26 + 1 + 25 + 55 + 3 = 142</t>
+        </is>
+      </c>
+      <c r="F86" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 39, 40, 41, 42, 43, 44</t>
+        </is>
+      </c>
+      <c r="G86" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H86" s="30" t="inlineStr">
+        <is>
+          <t>1 2 16</t>
+        </is>
+      </c>
+      <c r="I86" s="36" t="n"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="30" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B87" s="31" t="inlineStr">
+        <is>
           <t>Испытание трубопроводов К1, К2 в грунте наполнением водой до засыпки</t>
         </is>
       </c>
-      <c r="C83" s="32" t="inlineStr">
+      <c r="C87" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D83" s="32" t="n">
-        <v>70</v>
-      </c>
-      <c r="E83" s="33" t="inlineStr">
-        <is>
-          <t>27 + 40 + 3 = 70</t>
-        </is>
-      </c>
-      <c r="F83" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 36, 37, 38</t>
-        </is>
-      </c>
-      <c r="G83" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H83" s="30" t="inlineStr">
+      <c r="D87" s="32" t="n">
+        <v>83</v>
+      </c>
+      <c r="E87" s="33" t="inlineStr">
+        <is>
+          <t>25 + 55 + 3 = 83</t>
+        </is>
+      </c>
+      <c r="F87" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 42, 43, 44</t>
+        </is>
+      </c>
+      <c r="G87" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H87" s="30" t="inlineStr">
         <is>
           <t>2 14 16</t>
         </is>
       </c>
-      <c r="I83" s="36" t="n"/>
-    </row>
-    <row r="84" ht="45" customHeight="1">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B84" s="31" t="inlineStr">
+      <c r="I87" s="36" t="n"/>
+    </row>
+    <row r="88" ht="45" customHeight="1">
+      <c r="A88" s="30" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B88" s="31" t="inlineStr">
         <is>
           <t>Промывка и дезинфекция трубопроводов систем В1, Т3, Т4</t>
         </is>
       </c>
-      <c r="C84" s="32" t="inlineStr">
+      <c r="C88" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D84" s="32" t="n">
-        <v>369</v>
-      </c>
-      <c r="E84" s="33" t="inlineStr">
-        <is>
-          <t>11 + 55 + 138 + 163 + 2 = 369</t>
-        </is>
-      </c>
-      <c r="F84" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 28, 29, 30, 31, 32</t>
-        </is>
-      </c>
-      <c r="G84" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H84" s="30" t="inlineStr">
+      <c r="D88" s="32" t="n">
+        <v>352</v>
+      </c>
+      <c r="E88" s="33" t="inlineStr">
+        <is>
+          <t>14 + 101 + 121 + 114 + 2 = 352</t>
+        </is>
+      </c>
+      <c r="F88" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 34, 35, 36, 37, 38</t>
+        </is>
+      </c>
+      <c r="G88" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H88" s="30" t="inlineStr">
         <is>
           <t>1 2 16</t>
         </is>
       </c>
-      <c r="I84" s="36" t="n"/>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="30" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B85" s="31" t="inlineStr">
+      <c r="I88" s="36" t="n"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="30" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B89" s="31" t="inlineStr">
         <is>
           <t>Наладка циркуляции ГВС: настройка балансировочных клапанов по П4</t>
         </is>
       </c>
-      <c r="C85" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D85" s="32" t="n">
+      <c r="C89" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D89" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E85" s="33" t="n"/>
-      <c r="F85" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 75</t>
-        </is>
-      </c>
-      <c r="G85" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H85" s="30" t="inlineStr">
-        <is>
-          <t>13 17</t>
-        </is>
-      </c>
-      <c r="I85" s="36" t="inlineStr">
+      <c r="E89" s="33" t="n"/>
+      <c r="F89" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 81</t>
+        </is>
+      </c>
+      <c r="G89" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H89" s="30" t="inlineStr">
+        <is>
+          <t>13 18</t>
+        </is>
+      </c>
+      <c r="I89" s="36" t="inlineStr">
         <is>
           <t>П4</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="30" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B86" s="31" t="inlineStr">
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="30" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B90" s="31" t="inlineStr">
         <is>
           <t>Пусконаладочные работы циркуляционных насосов Н8, Н9</t>
         </is>
       </c>
-      <c r="C86" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D86" s="32" t="n">
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D90" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E86" s="33" t="inlineStr">
+      <c r="E90" s="33" t="inlineStr">
         <is>
           <t>1 + 1 = 2</t>
         </is>
       </c>
-      <c r="F86" s="34" t="inlineStr">
+      <c r="F90" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 7, 8; И05.09.26-ВК.СО, поз. 1, 2</t>
         </is>
       </c>
-      <c r="G86" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H86" s="30" t="inlineStr">
+      <c r="G90" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H90" s="30" t="inlineStr">
         <is>
           <t>7 8 15</t>
         </is>
       </c>
-      <c r="I86" s="36" t="n"/>
+      <c r="I90" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A38:I38"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="55" fitToHeight="0" fitToWidth="1"/>
@@ -3963,10 +4131,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="38" t="inlineStr">
         <is>
-          <t>4. Короба, ниши, люки в коробах, штрабы и проёмы в фундаменте — в объёмах АР и КР (задание И05.09.26-ВК.ТЗ-1).</t>
+          <t>4. Ниши коллекторных шкафов, короба, газобетонные О-блоки под стояки, штробы и проёмы в фундаменте — в объёмах АР и КР (задание И05.09.26-ВК.ТЗ-1).</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="34" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="I14" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 59,2, Т3 31,9 м + 10 %</t>
+          <t>по модели В1 61,1, Т3 33,7 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D15" s="32" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 32,6, Т3 29,0, Т4 48,0 м + 10 %</t>
+          <t>по модели В1 34,7, Т3 31,0, Т4 48,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E16" s="33" t="n"/>
       <c r="F16" s="34" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I16" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 65,0, Т3 38,2 м + 10 %</t>
+          <t>по модели В1 67,0, Т3 41,7 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>20 + 8 + 2 = 30</t>
+          <t>19 + 9 + 2 = 30</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
-          <t>25 + 30 + 22 + 4 = 81</t>
+          <t>26 + 29 + 22 + 4 = 81</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
@@ -1443,11 +1443,11 @@
         </is>
       </c>
       <c r="D20" s="32" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E20" s="33" t="inlineStr">
         <is>
-          <t>34 + 32 + 24 + 2 = 92</t>
+          <t>38 + 32 + 24 + 2 = 96</t>
         </is>
       </c>
       <c r="F20" s="34" t="inlineStr">
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="D22" s="32" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E22" s="33" t="inlineStr">
         <is>
-          <t>52 + 27 = 79</t>
+          <t>53 + 28 = 81</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="D23" s="32" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
-          <t>45 + 110 + 116 + 25 = 296</t>
+          <t>36 + 110 + 122 + 25 = 293</t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="D24" s="32" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E24" s="33" t="n"/>
       <c r="F24" s="34" t="inlineStr">
@@ -3289,11 +3289,11 @@
         </is>
       </c>
       <c r="D70" s="32" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E70" s="33" t="inlineStr">
         <is>
-          <t>42 + 85 + 36 = 163</t>
+          <t>46 + 87 + 38 = 171</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
@@ -3330,11 +3330,11 @@
         </is>
       </c>
       <c r="D71" s="32" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E71" s="33" t="inlineStr">
         <is>
-          <t>72 + 36 + 66 + 14 = 188</t>
+          <t>74 + 39 + 68 + 14 = 195</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D74" s="32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E74" s="33" t="n"/>
       <c r="F74" s="34" t="inlineStr">
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="D75" s="32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="D76" s="32" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="D77" s="32" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
@@ -3840,11 +3840,11 @@
         </is>
       </c>
       <c r="D85" s="32" t="n">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="E85" s="33" t="inlineStr">
         <is>
-          <t>14 + 101 + 121 + 114 + 2 = 352</t>
+          <t>14 + 105 + 126 + 120 + 2 = 367</t>
         </is>
       </c>
       <c r="F85" s="34" t="inlineStr">
@@ -3967,11 +3967,11 @@
         </is>
       </c>
       <c r="D88" s="32" t="n">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="E88" s="33" t="inlineStr">
         <is>
-          <t>14 + 101 + 121 + 114 + 2 = 352</t>
+          <t>14 + 105 + 126 + 120 + 2 = 367</t>
         </is>
       </c>
       <c r="F88" s="34" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -863,7 +863,7 @@
       <c r="E5" s="33" t="n"/>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 60</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 62</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>Установка гребёнки ХВС Ду 32 на 8 выходов с шаровыми кранами</t>
+          <t>Установка гребёнки ХВС Ду 32 на 9 выходов с шаровыми кранами</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 11,9 м + 10 %</t>
+          <t>по модели В1 11,7 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D15" s="32" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 34,7, Т3 31,0, Т4 48,0 м + 10 %</t>
+          <t>по модели В1 38,3, Т3 37,9, Т4 61,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1320,11 +1320,11 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>19 + 9 + 2 = 30</t>
+          <t>19 + 8 + 2 = 29</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
@@ -1361,11 +1361,11 @@
         </is>
       </c>
       <c r="D18" s="32" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
-          <t>26 + 29 + 22 + 4 = 81</t>
+          <t>26 + 30 + 22 + 4 = 82</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="I18" s="36" t="n"/>
     </row>
-    <row r="19" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="19" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
           <t>14</t>
@@ -1402,16 +1402,16 @@
         </is>
       </c>
       <c r="D19" s="32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" s="33" t="inlineStr">
         <is>
-          <t>2 + 1 = 3</t>
+          <t>2 + 1 + 1 + 1 = 5</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 53, 54</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 53, 54, 55, 56</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -1443,16 +1443,16 @@
         </is>
       </c>
       <c r="D20" s="32" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E20" s="33" t="inlineStr">
         <is>
-          <t>38 + 32 + 24 + 2 = 96</t>
+          <t>38 + 34 + 24 + 2 = 98</t>
         </is>
       </c>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 55, 56, 57, 58</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 57, 58, 59, 60</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
@@ -1489,7 +1489,7 @@
       <c r="E21" s="33" t="n"/>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 59</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 61</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -1521,16 +1521,16 @@
         </is>
       </c>
       <c r="D22" s="32" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E22" s="33" t="inlineStr">
         <is>
-          <t>53 + 28 = 81</t>
+          <t>54 + 35 = 89</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 115, 116</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 118, 119</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="D23" s="32" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
-          <t>36 + 110 + 122 + 25 = 293</t>
+          <t>36 + 105 + 122 + 25 = 288</t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 124, 125, 126, 127</t>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 127, 128, 129, 130</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H23" s="30" t="inlineStr">
         <is>
-          <t>5 7 14 19 20</t>
+          <t>5 7 14 20</t>
         </is>
       </c>
       <c r="I23" s="36" t="inlineStr">
@@ -1607,12 +1607,12 @@
         </is>
       </c>
       <c r="D24" s="32" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E24" s="33" t="n"/>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 131</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 134</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
@@ -1659,16 +1659,16 @@
         </is>
       </c>
       <c r="D26" s="32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" s="33" t="inlineStr">
         <is>
-          <t>3 + 4 = 7</t>
+          <t>3 + 7 = 10</t>
         </is>
       </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 75, 76</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 78, 79</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -1705,7 +1705,7 @@
       <c r="E27" s="33" t="n"/>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 77</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 80</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1737,12 +1737,12 @@
         </is>
       </c>
       <c r="D28" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 81</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 84</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1783,7 +1783,7 @@
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 82</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 85</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1824,7 +1824,7 @@
       <c r="E30" s="33" t="n"/>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 83</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 86</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 78, 79, 80</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 81, 82, 83</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -1906,7 +1906,7 @@
       <c r="E32" s="33" t="n"/>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 84</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 87</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -2132,12 +2132,12 @@
         </is>
       </c>
       <c r="D39" s="32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E39" s="33" t="n"/>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 39, 61</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 39, 63</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -2174,7 +2174,7 @@
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 40, 62</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 40, 64</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2211,7 +2211,7 @@
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 41, 63</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 41, 65</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -2457,7 +2457,7 @@
       <c r="E47" s="33" t="n"/>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 100</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 103</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="H47" s="30" t="inlineStr">
         <is>
-          <t>4 18</t>
+          <t>4 19</t>
         </is>
       </c>
       <c r="I47" s="36" t="inlineStr">
@@ -2498,7 +2498,7 @@
       <c r="E48" s="33" t="n"/>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 101</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 104</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 64, 65, 66, 68, 69</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 66, 67, 68, 71, 72</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2580,7 +2580,7 @@
       <c r="E50" s="33" t="n"/>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 71</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 74</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2617,7 +2617,7 @@
       <c r="E51" s="33" t="n"/>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 70</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 73</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -2658,7 +2658,7 @@
       <c r="E52" s="33" t="n"/>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 99</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 102</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="H52" s="30" t="inlineStr">
         <is>
-          <t>6 9 14 18</t>
+          <t>6 9 14 19</t>
         </is>
       </c>
       <c r="I52" s="36" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 91, 92, 93, 94</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 94, 95, 96, 97</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 95, 96, 97</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 98, 99, 100</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="H54" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 14 18</t>
+          <t>5 6 9 14 18 19</t>
         </is>
       </c>
       <c r="I54" s="36" t="inlineStr">
@@ -2785,7 +2785,7 @@
       <c r="E55" s="33" t="n"/>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 98</t>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 101</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="H55" s="30" t="inlineStr">
         <is>
-          <t>12 14 18</t>
+          <t>12 14 19</t>
         </is>
       </c>
       <c r="I55" s="36" t="inlineStr">
@@ -2821,16 +2821,16 @@
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E56" s="33" t="inlineStr">
         <is>
-          <t>26 + 2 + 35 = 63</t>
+          <t>25 + 2 + 35 = 62</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 128, 129, 130</t>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 131, 132, 133</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -2882,7 +2882,7 @@
       <c r="E58" s="33" t="n"/>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 102</t>
+          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 105</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 103, 104</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 106, 107</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -2964,7 +2964,7 @@
       <c r="E60" s="33" t="n"/>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 105</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 108</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -3001,7 +3001,7 @@
       <c r="E61" s="33" t="n"/>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 106</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 109</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -3057,7 +3057,7 @@
       <c r="E63" s="33" t="n"/>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 85</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 88</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -3094,7 +3094,7 @@
       <c r="E64" s="33" t="n"/>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 86</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 89</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -3131,7 +3131,7 @@
       <c r="E65" s="33" t="n"/>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 87</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 90</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -3168,7 +3168,7 @@
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 88</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 91</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3205,7 +3205,7 @@
       <c r="E67" s="33" t="n"/>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 89</t>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 92</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -3242,7 +3242,7 @@
       <c r="E68" s="33" t="n"/>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 90</t>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 93</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3289,16 +3289,16 @@
         </is>
       </c>
       <c r="D70" s="32" t="n">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="E70" s="33" t="inlineStr">
         <is>
-          <t>46 + 87 + 38 = 171</t>
+          <t>46 + 109 + 38 = 193</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 107, 108, 109</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 110, 111, 112</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -3330,16 +3330,16 @@
         </is>
       </c>
       <c r="D71" s="32" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E71" s="33" t="inlineStr">
         <is>
-          <t>74 + 39 + 68 + 14 = 195</t>
+          <t>74 + 43 + 68 + 13 = 198</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 110, 111, 112, 113</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 113, 114, 115, 116</t>
         </is>
       </c>
       <c r="G71" s="35" t="inlineStr">
@@ -3376,7 +3376,7 @@
       <c r="E72" s="33" t="n"/>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 114</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 117</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -3423,12 +3423,12 @@
         </is>
       </c>
       <c r="D74" s="32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E74" s="33" t="n"/>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 117</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 120</t>
         </is>
       </c>
       <c r="G74" s="35" t="inlineStr">
@@ -3464,12 +3464,12 @@
         </is>
       </c>
       <c r="D75" s="32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 117</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 120</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -3510,7 +3510,7 @@
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 118</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 121</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3551,7 +3551,7 @@
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 118</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 121</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -3592,7 +3592,7 @@
       <c r="E78" s="33" t="n"/>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 119</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 122</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -3633,7 +3633,7 @@
       <c r="E79" s="33" t="n"/>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 119</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 122</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -3674,7 +3674,7 @@
       <c r="E80" s="33" t="n"/>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 120</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 123</t>
         </is>
       </c>
       <c r="G80" s="35" t="inlineStr">
@@ -3711,7 +3711,7 @@
       <c r="E81" s="33" t="n"/>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 121</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 124</t>
         </is>
       </c>
       <c r="G81" s="35" t="inlineStr">
@@ -3752,7 +3752,7 @@
       <c r="E82" s="33" t="n"/>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 122</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 125</t>
         </is>
       </c>
       <c r="G82" s="35" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="H82" s="30" t="inlineStr">
         <is>
-          <t>14 19</t>
+          <t>14 20</t>
         </is>
       </c>
       <c r="I82" s="36" t="inlineStr">
@@ -3793,7 +3793,7 @@
       <c r="E83" s="33" t="n"/>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 6; И05.09.26-ВК.СО, поз. 123</t>
+          <t>И05.09.26-ВК, см. лист 6; И05.09.26-ВК.СО, поз. 126</t>
         </is>
       </c>
       <c r="G83" s="35" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="H83" s="30" t="inlineStr">
         <is>
-          <t>6 19</t>
+          <t>6 20</t>
         </is>
       </c>
       <c r="I83" s="36" t="n"/>
@@ -3840,11 +3840,11 @@
         </is>
       </c>
       <c r="D85" s="32" t="n">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="E85" s="33" t="inlineStr">
         <is>
-          <t>14 + 105 + 126 + 120 + 2 = 367</t>
+          <t>13 + 105 + 151 + 120 + 2 = 391</t>
         </is>
       </c>
       <c r="F85" s="34" t="inlineStr">
@@ -3885,11 +3885,11 @@
         </is>
       </c>
       <c r="D86" s="32" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E86" s="33" t="inlineStr">
         <is>
-          <t>32 + 26 + 1 + 25 + 55 + 3 = 142</t>
+          <t>31 + 26 + 1 + 25 + 55 + 3 = 141</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
@@ -3967,11 +3967,11 @@
         </is>
       </c>
       <c r="D88" s="32" t="n">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="E88" s="33" t="inlineStr">
         <is>
-          <t>14 + 105 + 126 + 120 + 2 = 367</t>
+          <t>13 + 105 + 151 + 120 + 2 = 391</t>
         </is>
       </c>
       <c r="F88" s="34" t="inlineStr">
@@ -4008,12 +4008,12 @@
         </is>
       </c>
       <c r="D89" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" s="33" t="n"/>
       <c r="F89" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 81</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 84</t>
         </is>
       </c>
       <c r="G89" s="35" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -863,7 +863,7 @@
       <c r="E5" s="33" t="n"/>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 62</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 66</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>Установка гребёнки ХВС Ду 32 на 9 выходов с шаровыми кранами</t>
+          <t>Установка гребёнки ХВС Ду 32 на 10 выходов с шаровыми кранами</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>Установка шкафов коллекторных встраиваемых в ниши (ШВК-1, ШВК-2, ШВК-Б2) и в короб (ШВК-Б1)</t>
+          <t>Установка шкафов коллекторных встраиваемых в ниши (ШВК-1, ШВК-2, ШВК-Б1, ШВК-Б2)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
-          <t>узел 10 листа 14; ниши и короб — АР (ТЗ-1)</t>
+          <t>узел 10 листа 14; ниши — АР (ТЗ-1)</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       <c r="H11" s="28" t="n"/>
       <c r="I11" s="29" t="n"/>
     </row>
-    <row r="12" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="12" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A12" s="30" t="inlineStr">
         <is>
           <t>7</t>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубы ПЭ 100 SDR11 32×3,0 ввода от наружной грани фундамента до приямка</t>
+          <t>Укладка футляров ПЭ Ø75 с плавными отводами под краем плиты и сквозь плиту (ввод В1, подводка КХ-8) до бетонирования</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -1115,12 +1115,12 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 34</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 46</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="H12" s="30" t="inlineStr">
         <is>
-          <t>7 14 16</t>
+          <t>7 14 17</t>
         </is>
       </c>
       <c r="I12" s="36" t="inlineStr">
         <is>
-          <t>узел 1 листа 14</t>
+          <t>узел 1 листа 14; отводы R ≥ 0,3 м — поз. 47</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из труб PE-Xa 32×4,4 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
+          <t>Прокладка трубы ПЭ 100 SDR11 32×3,0 ввода от наружной грани фундамента в футляре под краем плиты и сквозь плиту до перехода на PE-Xa</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -1156,12 +1156,12 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 35</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 34</t>
         </is>
       </c>
       <c r="G13" s="35" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="H13" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 10 11 16</t>
+          <t>7 14 16</t>
         </is>
       </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 11,7 м + 10 %</t>
+          <t>узел 1 листа 14; без приямка</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из труб PE-Xa 25×3,5 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
+          <t>Прокладка трубопроводов из труб PE-Xa 32×4,4 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -1197,12 +1197,12 @@
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>105</v>
+        <v>12</v>
       </c>
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 36</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 35</t>
         </is>
       </c>
       <c r="G14" s="35" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="I14" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 61,1, Т3 33,7 м + 10 %</t>
+          <t>по модели В1 10,2 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из труб PE-Xa 20×2,8 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
+          <t>Прокладка трубопроводов из труб PE-Xa 25×3,5 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -1238,12 +1238,12 @@
         </is>
       </c>
       <c r="D15" s="32" t="n">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 37</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 36</t>
         </is>
       </c>
       <c r="G15" s="35" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 38,3, Т3 37,9, Т4 61,0 м + 10 %</t>
+          <t>по модели В1 69,6, Т3 41,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из труб PE-Xa 16×2,2 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
+          <t>Прокладка трубопроводов из труб PE-Xa 20×2,8 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -1279,98 +1279,98 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="E16" s="33" t="n"/>
       <c r="F16" s="34" t="inlineStr">
         <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 37</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>3 4 5 8 10 11 16</t>
+        </is>
+      </c>
+      <c r="I16" s="36" t="inlineStr">
+        <is>
+          <t>по модели В1 36,6, Т3 63,7, Т4 67,0 м + 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка трубопроводов из труб PE-Xa 16×2,2 цельными отрезками (в утеплителе пола, в коробе под потолком гаража, в штрабах)</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>104</v>
+      </c>
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
           <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 38</t>
         </is>
       </c>
-      <c r="G16" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H17" s="30" t="inlineStr">
         <is>
           <t>3 4 5 8 10 11 16</t>
         </is>
       </c>
-      <c r="I16" s="36" t="inlineStr">
-        <is>
-          <t>по модели В1 67,0, Т3 41,7 м + 10 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="I17" s="36" t="inlineStr">
+        <is>
+          <t>по модели В1 69,6, Т3 24,7 м + 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>Установка фитингов «евроконус» на выходах коллекторов</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="n">
-        <v>29</v>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>19 + 8 + 2 = 29</t>
-        </is>
-      </c>
-      <c r="F17" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 46, 47, 48</t>
-        </is>
-      </c>
-      <c r="G17" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H17" s="30" t="inlineStr">
-        <is>
-          <t>13 16 17</t>
-        </is>
-      </c>
-      <c r="I17" s="36" t="n"/>
-    </row>
-    <row r="18" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>Установка фитингов PE-Xa с переходом на резьбу (водорозетки, угольники, присоединения оборудования)</t>
-        </is>
-      </c>
       <c r="C18" s="32" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="D18" s="32" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
-          <t>26 + 30 + 22 + 4 = 82</t>
+          <t>17 + 9 + 1 = 27</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 49, 50, 51, 52</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 48, 49, 50</t>
         </is>
       </c>
       <c r="G18" s="35" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H18" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 17</t>
+          <t>13 17</t>
         </is>
       </c>
       <c r="I18" s="36" t="n"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>Установка тройников PE-Xa</t>
+          <t>Установка фитингов PE-Xa с переходом на резьбу (водорозетки, угольники, присоединения оборудования)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -1402,16 +1402,16 @@
         </is>
       </c>
       <c r="D19" s="32" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="E19" s="33" t="inlineStr">
         <is>
-          <t>2 + 1 + 1 + 1 = 5</t>
+          <t>24 + 31 + 20 + 4 = 79</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 53, 54, 55, 56</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 51, 52, 53, 54</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H19" s="30" t="inlineStr">
         <is>
-          <t>10 11 17</t>
+          <t>3 4 5 8 17</t>
         </is>
       </c>
       <c r="I19" s="36" t="n"/>
@@ -1434,113 +1434,113 @@
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
+          <t>Установка тройников PE-Xa</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>2 + 3 + 1 + 1 + 1 + 2 = 10</t>
+        </is>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 55, 56, 57, 58, 59, 60</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="inlineStr">
+        <is>
+          <t>10 11 17</t>
+        </is>
+      </c>
+      <c r="I20" s="36" t="n"/>
+    </row>
+    <row r="21" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
           <t>Установка фиксаторов поворота 90° на выходах труб из пола</t>
         </is>
       </c>
-      <c r="C20" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D20" s="32" t="n">
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="n">
         <v>98</v>
       </c>
-      <c r="E20" s="33" t="inlineStr">
-        <is>
-          <t>38 + 34 + 24 + 2 = 98</t>
-        </is>
-      </c>
-      <c r="F20" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 57, 58, 59, 60</t>
-        </is>
-      </c>
-      <c r="G20" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H20" s="30" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>34 + 41 + 21 + 2 = 98</t>
+        </is>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 61, 62, 63, 64</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H21" s="30" t="inlineStr">
         <is>
           <t>3 4 8 17</t>
         </is>
       </c>
-      <c r="I20" s="36" t="n"/>
-    </row>
-    <row r="21" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="I21" s="36" t="n"/>
+    </row>
+    <row r="22" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>Установка перехода ПЭ 32 / PE-Xa 32</t>
         </is>
       </c>
-      <c r="C21" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="n">
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="33" t="n"/>
-      <c r="F21" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 61</t>
-        </is>
-      </c>
-      <c r="G21" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H21" s="30" t="inlineStr">
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 65</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H22" s="30" t="inlineStr">
         <is>
           <t>7 14 17</t>
-        </is>
-      </c>
-      <c r="I21" s="36" t="n"/>
-    </row>
-    <row r="22" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка защитной гофротрубы ПНД на подъёмах к приборам в стенах</t>
-        </is>
-      </c>
-      <c r="C22" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D22" s="32" t="n">
-        <v>89</v>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>54 + 35 = 89</t>
-        </is>
-      </c>
-      <c r="F22" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 118, 119</t>
-        </is>
-      </c>
-      <c r="G22" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H22" s="30" t="inlineStr">
-        <is>
-          <t>3 4 5 8 19</t>
         </is>
       </c>
       <c r="I22" s="36" t="n"/>
@@ -1553,169 +1553,173 @@
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
+          <t>Прокладка защитной гофротрубы ПНД на подъёмах к приборам в стенах</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="n">
+        <v>91</v>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>54 + 37 = 91</t>
+        </is>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 129, 130</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H23" s="30" t="inlineStr">
+        <is>
+          <t>3 4 5 8 20</t>
+        </is>
+      </c>
+      <c r="I23" s="36" t="n"/>
+    </row>
+    <row r="24" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
           <t>Крепление трубопроводов PE-Xa хомутами с резиновым вкладышем</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="n">
-        <v>288</v>
-      </c>
-      <c r="E23" s="33" t="inlineStr">
-        <is>
-          <t>36 + 105 + 122 + 25 = 288</t>
-        </is>
-      </c>
-      <c r="F23" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 127, 128, 129, 130</t>
-        </is>
-      </c>
-      <c r="G23" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H23" s="30" t="inlineStr">
-        <is>
-          <t>5 7 14 20</t>
-        </is>
-      </c>
-      <c r="I23" s="36" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="n">
+        <v>230</v>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>36 + 81 + 89 + 24 = 230</t>
+        </is>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 139, 140, 141, 142</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H24" s="30" t="inlineStr">
+        <is>
+          <t>5 7 14 20 21</t>
+        </is>
+      </c>
+      <c r="I24" s="36" t="inlineStr">
         <is>
           <t>шаг — лист 14</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B24" s="31" t="inlineStr">
+    <row r="25" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>Крепление трубопроводов PE-Xa к утеплителю пола скобами</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D24" s="32" t="n">
-        <v>500</v>
-      </c>
-      <c r="E24" s="33" t="n"/>
-      <c r="F24" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 134</t>
-        </is>
-      </c>
-      <c r="G24" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H24" s="30" t="inlineStr">
-        <is>
-          <t>3 8 14 20</t>
-        </is>
-      </c>
-      <c r="I24" s="36" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="n">
+        <v>650</v>
+      </c>
+      <c r="E25" s="33" t="n"/>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 146</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H25" s="30" t="inlineStr">
+        <is>
+          <t>3 8 14 21</t>
+        </is>
+      </c>
+      <c r="I25" s="36" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Арматура</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n"/>
-      <c r="C25" s="28" t="n"/>
-      <c r="D25" s="28" t="n"/>
-      <c r="E25" s="28" t="n"/>
-      <c r="F25" s="28" t="n"/>
-      <c r="G25" s="28" t="n"/>
-      <c r="H25" s="28" t="n"/>
-      <c r="I25" s="29" t="n"/>
-    </row>
-    <row r="26" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="29" t="n"/>
+    </row>
+    <row r="27" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>Установка кранов шаровых Ду 15–20</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D26" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" s="33" t="inlineStr">
-        <is>
-          <t>3 + 7 = 10</t>
-        </is>
-      </c>
-      <c r="F26" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 78, 79</t>
-        </is>
-      </c>
-      <c r="G26" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H26" s="30" t="inlineStr">
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>6 + 10 = 16</t>
+        </is>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 89, 90</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H27" s="30" t="inlineStr">
         <is>
           <t>7 8 10 11 18</t>
-        </is>
-      </c>
-      <c r="I26" s="36" t="n"/>
-    </row>
-    <row r="27" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B27" s="31" t="inlineStr">
-        <is>
-          <t>Установка обратных клапанов Ду 15 на Т4</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="33" t="n"/>
-      <c r="F27" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 80</t>
-        </is>
-      </c>
-      <c r="G27" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H27" s="30" t="inlineStr">
-        <is>
-          <t>10 11 18</t>
         </is>
       </c>
       <c r="I27" s="36" t="n"/>
@@ -1728,7 +1732,7 @@
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>Установка клапанов балансировочных ручных Ду 15</t>
+          <t>Установка обратных клапанов Ду 15 на Т4</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -1737,12 +1741,12 @@
         </is>
       </c>
       <c r="D28" s="32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 84</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 91</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1752,16 +1756,12 @@
       </c>
       <c r="H28" s="30" t="inlineStr">
         <is>
-          <t>13 18</t>
-        </is>
-      </c>
-      <c r="I28" s="36" t="inlineStr">
-        <is>
-          <t>настройка — П4</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>10 11 18</t>
+        </is>
+      </c>
+      <c r="I28" s="36" t="n"/>
+    </row>
+    <row r="29" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
           <t>23</t>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>Установка кранов поливочных незамерзающих со штоком 350 мм через стену (в гильзе с уклоном наружу)</t>
+          <t>Установка клапанов балансировочных ручных Ду 15</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -1778,12 +1778,12 @@
         </is>
       </c>
       <c r="D29" s="32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 85</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 95</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1793,16 +1793,16 @@
       </c>
       <c r="H29" s="30" t="inlineStr">
         <is>
-          <t>3 8 14 18</t>
+          <t>13 19</t>
         </is>
       </c>
       <c r="I29" s="36" t="inlineStr">
         <is>
-          <t>узел 9 листа 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1" thickBot="1">
+          <t>настройка — П4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1" thickBot="1">
       <c r="A30" s="30" t="inlineStr">
         <is>
           <t>24</t>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>Установка крана для стиральной машины</t>
+          <t>Установка кранов поливочных незамерзающих со штоком 350 мм через стену (в гильзе с уклоном наружу)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -1819,12 +1819,12 @@
         </is>
       </c>
       <c r="D30" s="32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" s="33" t="n"/>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 86</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 96</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1834,12 +1834,16 @@
       </c>
       <c r="H30" s="30" t="inlineStr">
         <is>
-          <t>4 18</t>
-        </is>
-      </c>
-      <c r="I30" s="36" t="n"/>
-    </row>
-    <row r="31" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>3 8 14 19</t>
+        </is>
+      </c>
+      <c r="I30" s="36" t="inlineStr">
+        <is>
+          <t>узел 9 листа 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
           <t>25</t>
@@ -1847,139 +1851,131 @@
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
+          <t>Установка крана для стиральной машины</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="33" t="n"/>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 97</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H31" s="30" t="inlineStr">
+        <is>
+          <t>4 19</t>
+        </is>
+      </c>
+      <c r="I31" s="36" t="n"/>
+    </row>
+    <row r="32" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
           <t>Подводка автополива КХ-8: установка обратного клапана, спускного крана и заглушки на конце трубы</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="n">
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>1 + 1 + 1 = 3</t>
         </is>
       </c>
-      <c r="F31" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 81, 82, 83</t>
-        </is>
-      </c>
-      <c r="G31" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H31" s="30" t="inlineStr">
-        <is>
-          <t>4 7 14 18</t>
-        </is>
-      </c>
-      <c r="I31" s="36" t="inlineStr">
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 92, 93, 94</t>
+        </is>
+      </c>
+      <c r="G32" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H32" s="30" t="inlineStr">
+        <is>
+          <t>4 7 14 19</t>
+        </is>
+      </c>
+      <c r="I32" s="36" t="inlineStr">
         <is>
           <t>далее — по ландшафтному проекту</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="inlineStr">
+    <row r="33" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>Установка кранов шаровых угловых для гибких подводок приборов</t>
         </is>
       </c>
-      <c r="C32" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D32" s="32" t="n">
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="E32" s="33" t="n"/>
-      <c r="F32" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 87</t>
-        </is>
-      </c>
-      <c r="G32" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H32" s="30" t="inlineStr">
-        <is>
-          <t>3 4 5 8 18</t>
-        </is>
-      </c>
-      <c r="I32" s="36" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="E33" s="33" t="n"/>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 98</t>
+        </is>
+      </c>
+      <c r="G33" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H33" s="30" t="inlineStr">
+        <is>
+          <t>3 4 5 8 19</t>
+        </is>
+      </c>
+      <c r="I33" s="36" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Оборудование горячего водоснабжения</t>
         </is>
       </c>
-      <c r="B33" s="28" t="n"/>
-      <c r="C33" s="28" t="n"/>
-      <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n"/>
-      <c r="F33" s="28" t="n"/>
-      <c r="G33" s="28" t="n"/>
-      <c r="H33" s="28" t="n"/>
-      <c r="I33" s="29" t="n"/>
-    </row>
-    <row r="34" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B34" s="31" t="inlineStr">
-        <is>
-          <t>Установка насосов циркуляционных ГВС Н8, Н9 с подключением</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D34" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="33" t="inlineStr">
-        <is>
-          <t>1 + 1 = 2</t>
-        </is>
-      </c>
-      <c r="F34" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 1, 2</t>
-        </is>
-      </c>
-      <c r="G34" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H34" s="30" t="inlineStr">
-        <is>
-          <t>7 8 10 11 15</t>
-        </is>
-      </c>
-      <c r="I34" s="36" t="inlineStr">
-        <is>
-          <t>подключение к сети — ЭОМ</t>
-        </is>
-      </c>
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+      <c r="H34" s="28" t="n"/>
+      <c r="I34" s="29" t="n"/>
     </row>
     <row r="35" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="30" t="inlineStr">
@@ -1989,7 +1985,7 @@
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>Установка бака мембранного для ГВС 12 л</t>
+          <t>Установка насосов циркуляционных ГВС Н8, Н9 с подключением</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -1998,12 +1994,16 @@
         </is>
       </c>
       <c r="D35" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="33" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E35" s="33" t="inlineStr">
+        <is>
+          <t>1 + 1 = 2</t>
+        </is>
+      </c>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 8, 11; И05.09.26-ВК.СО, поз. 3</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 1, 2</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -2013,10 +2013,14 @@
       </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>8 11 15</t>
-        </is>
-      </c>
-      <c r="I35" s="36" t="n"/>
+          <t>7 8 10 11 15</t>
+        </is>
+      </c>
+      <c r="I35" s="36" t="inlineStr">
+        <is>
+          <t>подключение к сети — ЭОМ</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A36" s="30" t="inlineStr">
@@ -2026,7 +2030,7 @@
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>Установка группы безопасности бойлера Б2</t>
+          <t>Установка бака мембранного для ГВС 12 л</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -2040,141 +2044,141 @@
       <c r="E36" s="33" t="n"/>
       <c r="F36" s="34" t="inlineStr">
         <is>
+          <t>И05.09.26-ВК, см. листы 8, 11; И05.09.26-ВК.СО, поз. 3</t>
+        </is>
+      </c>
+      <c r="G36" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H36" s="30" t="inlineStr">
+        <is>
+          <t>8 11 15</t>
+        </is>
+      </c>
+      <c r="I36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>Установка группы безопасности бойлера Б2</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="33" t="n"/>
+      <c r="F37" s="34" t="inlineStr">
+        <is>
           <t>И05.09.26-ВК, см. листы 8, 11; И05.09.26-ВК.СО, поз. 4</t>
         </is>
       </c>
-      <c r="G36" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H36" s="30" t="inlineStr">
+      <c r="G37" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H37" s="30" t="inlineStr">
         <is>
           <t>8 11 15</t>
         </is>
       </c>
-      <c r="I36" s="36" t="n"/>
-    </row>
-    <row r="37" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="inlineStr">
+      <c r="I37" s="36" t="n"/>
+    </row>
+    <row r="38" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>Установка полотенцесушителей водяных на Т4 с комплектами запорных клапанов</t>
         </is>
       </c>
-      <c r="C37" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D37" s="32" t="n">
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="33" t="inlineStr">
+      <c r="E38" s="33" t="inlineStr">
         <is>
           <t>1 + 1 + 2 + 1 = 5</t>
         </is>
       </c>
-      <c r="F37" s="34" t="inlineStr">
+      <c r="F38" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 5, 6, 7, 8</t>
         </is>
       </c>
-      <c r="G37" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H37" s="30" t="inlineStr">
+      <c r="G38" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H38" s="30" t="inlineStr">
         <is>
           <t>5 8 10 11 15</t>
         </is>
       </c>
-      <c r="I37" s="36" t="inlineStr">
+      <c r="I38" s="36" t="inlineStr">
         <is>
           <t>5 шт.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A38" s="27" t="inlineStr">
+    <row r="39" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>Система бытовой канализации К1</t>
         </is>
       </c>
-      <c r="B38" s="28" t="n"/>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
-      <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28" t="n"/>
-      <c r="I38" s="29" t="n"/>
-    </row>
-    <row r="39" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A39" s="30" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B39" s="31" t="inlineStr">
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="29" t="n"/>
+    </row>
+    <row r="40" ht="75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
         <is>
           <t>Прокладка трубопроводов из малошумных канализационных труб Ø110 (стояки с вытяжными частями, сборный под потолком гаража, подъёмы к приборам) с фасонными частями</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C40" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D39" s="32" t="n">
-        <v>31</v>
-      </c>
-      <c r="E39" s="33" t="n"/>
-      <c r="F39" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 39, 63</t>
-        </is>
-      </c>
-      <c r="G39" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H39" s="30" t="inlineStr">
-        <is>
-          <t>5 6 9 12 16 17</t>
-        </is>
-      </c>
-      <c r="I39" s="36" t="n"/>
-    </row>
-    <row r="40" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B40" s="31" t="inlineStr">
-        <is>
-          <t>Прокладка трубопроводов из малошумных канализационных труб Ø50 (отводы и подъёмы к приборам) с фасонными частями</t>
-        </is>
-      </c>
-      <c r="C40" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
       <c r="D40" s="32" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 40, 64</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 39, 67</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2189,7 +2193,7 @@
       </c>
       <c r="I40" s="36" t="n"/>
     </row>
-    <row r="41" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="41" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="30" t="inlineStr">
         <is>
           <t>33</t>
@@ -2197,7 +2201,7 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из малошумных канализационных труб Ø32 (конденсат кондиционеров) с фасонными частями</t>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø50 (отводы и подъёмы к приборам) с фасонными частями</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -2206,12 +2210,12 @@
         </is>
       </c>
       <c r="D41" s="32" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 41, 65</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 40, 68, 69</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -2234,7 +2238,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 в грунте под плитой на песчаном основании</t>
+          <t>Прокладка трубопроводов из малошумных канализационных труб Ø32 (конденсат кондиционеров) с фасонными частями</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -2243,12 +2247,12 @@
         </is>
       </c>
       <c r="D42" s="32" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 42</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 41, 70, 71</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -2258,16 +2262,12 @@
       </c>
       <c r="H42" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 14 16</t>
-        </is>
-      </c>
-      <c r="I42" s="36" t="inlineStr">
-        <is>
-          <t>под плитой — решение Заказчика</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>5 6 9 12 16 18</t>
+        </is>
+      </c>
+      <c r="I42" s="36" t="n"/>
+    </row>
+    <row r="43" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A43" s="30" t="inlineStr">
         <is>
           <t>35</t>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B43" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов из ПП наружных труб Ø110 SN8 в грунте под плитой на песчаном основании с фасонными частями</t>
+          <t>Прокладка трубопроводов из ПП канализационных труб Ø50 в грунте под плитой на песчаном основании</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -2284,113 +2284,113 @@
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="E43" s="33" t="n"/>
       <c r="F43" s="34" t="inlineStr">
         <is>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 42</t>
+        </is>
+      </c>
+      <c r="G43" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H43" s="30" t="inlineStr">
+        <is>
+          <t>6 9 12 14 16</t>
+        </is>
+      </c>
+      <c r="I43" s="36" t="inlineStr">
+        <is>
+          <t>под плитой — решение Заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>Прокладка трубопроводов из ПП наружных труб Ø110 SN8 в грунте под плитой на песчаном основании с фасонными частями</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="n">
+        <v>52</v>
+      </c>
+      <c r="E44" s="33" t="n"/>
+      <c r="F44" s="34" t="inlineStr">
+        <is>
           <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 43</t>
         </is>
       </c>
-      <c r="G43" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H43" s="30" t="inlineStr">
+      <c r="G44" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H44" s="30" t="inlineStr">
         <is>
           <t>6 9 12 14 16</t>
         </is>
       </c>
-      <c r="I43" s="36" t="inlineStr">
+      <c r="I44" s="36" t="inlineStr">
         <is>
           <t>в т. ч. выпуски до границы с НВК</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="inlineStr">
+    <row r="45" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A45" s="30" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="inlineStr">
         <is>
           <t>Устройство песчаного основания 100 мм и обсыпки 300 мм над верхом трубы с ручным уплотнением</t>
         </is>
       </c>
-      <c r="C44" s="32" t="inlineStr">
+      <c r="C45" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D44" s="32" t="n">
-        <v>83</v>
-      </c>
-      <c r="E44" s="33" t="inlineStr">
-        <is>
-          <t>25 + 55 + 3 = 83</t>
-        </is>
-      </c>
-      <c r="F44" s="34" t="inlineStr">
+      <c r="D45" s="32" t="n">
+        <v>84</v>
+      </c>
+      <c r="E45" s="33" t="inlineStr">
+        <is>
+          <t>29 + 52 + 3 = 84</t>
+        </is>
+      </c>
+      <c r="F45" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 42, 43, 44</t>
         </is>
       </c>
-      <c r="G44" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H44" s="30" t="inlineStr">
+      <c r="G45" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H45" s="30" t="inlineStr">
         <is>
           <t>14 16</t>
         </is>
       </c>
-      <c r="I44" s="36" t="inlineStr">
+      <c r="I45" s="36" t="inlineStr">
         <is>
           <t>до бетонирования плиты</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A45" s="30" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>Установка футляров Ø160 SN8 под краем плиты (выпуски, ввод линии бани)</t>
-        </is>
-      </c>
-      <c r="C45" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D45" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="33" t="n"/>
-      <c r="F45" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 45</t>
-        </is>
-      </c>
-      <c r="G45" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H45" s="30" t="inlineStr">
-        <is>
-          <t>14 16</t>
-        </is>
-      </c>
-      <c r="I45" s="36" t="inlineStr">
-        <is>
-          <t>узел 2</t>
         </is>
       </c>
     </row>
@@ -2402,21 +2402,21 @@
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>Прокладка трубопровода К2 Ø110 SN8 от пескоуловителя гаража под плитой на песчаном основании</t>
+          <t>Установка футляров Ø160 SN8 под краем плиты (выпуски дома и бани, ввод линии бани в дом, К2-1)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46" s="33" t="n"/>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 14; И05.09.26-ВК.СО, поз. 44</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 45</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -2426,16 +2426,16 @@
       </c>
       <c r="H46" s="30" t="inlineStr">
         <is>
-          <t>4 14 16</t>
+          <t>14 17</t>
         </is>
       </c>
       <c r="I46" s="36" t="inlineStr">
         <is>
-          <t>до границы с НВК (ливневая сеть)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+          <t>узел 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="30" t="inlineStr">
         <is>
           <t>39</t>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B47" s="31" t="inlineStr">
         <is>
-          <t>Устройство лотка водоотводного DN100 с решёткой C250 в полу гаража</t>
+          <t>Прокладка трубопровода К2 Ø110 SN8 от пескоуловителя гаража под плитой на песчаном основании</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -2452,12 +2452,12 @@
         </is>
       </c>
       <c r="D47" s="32" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="E47" s="33" t="n"/>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 103</t>
+          <t>И05.09.26-ВК, см. листы 4, 14; И05.09.26-ВК.СО, поз. 44</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="H47" s="30" t="inlineStr">
         <is>
-          <t>4 19</t>
+          <t>4 14 16</t>
         </is>
       </c>
       <c r="I47" s="36" t="inlineStr">
         <is>
-          <t>углубление в стяжке — АР/КР (ТЗ-1)</t>
+          <t>до границы с НВК (ливневая сеть)</t>
         </is>
       </c>
     </row>
@@ -2484,21 +2484,21 @@
       </c>
       <c r="B48" s="31" t="inlineStr">
         <is>
-          <t>Установка пескоуловителя DN100 с корзиной</t>
+          <t>Устройство лотка водоотводного DN100 с решёткой C250 в полу гаража</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="E48" s="33" t="n"/>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 104</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 115</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -2513,52 +2513,52 @@
       </c>
       <c r="I48" s="36" t="inlineStr">
         <is>
+          <t>углубление в стяжке — АР/КР (ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>Установка пескоуловителя DN100 с корзиной</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="33" t="n"/>
+      <c r="F49" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 116</t>
+        </is>
+      </c>
+      <c r="G49" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H49" s="30" t="inlineStr">
+        <is>
+          <t>4 19</t>
+        </is>
+      </c>
+      <c r="I49" s="36" t="inlineStr">
+        <is>
           <t>понижение плиты — КР (ТЗ-1)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>Установка тройников косых канализационных</t>
-        </is>
-      </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="n">
-        <v>17</v>
-      </c>
-      <c r="E49" s="33" t="inlineStr">
-        <is>
-          <t>6 + 2 + 2 + 6 + 1 = 17</t>
-        </is>
-      </c>
-      <c r="F49" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 66, 67, 68, 71, 72</t>
-        </is>
-      </c>
-      <c r="G49" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H49" s="30" t="inlineStr">
-        <is>
-          <t>5 6 9 12 17</t>
-        </is>
-      </c>
-      <c r="I49" s="36" t="n"/>
-    </row>
-    <row r="50" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+    <row r="50" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="30" t="inlineStr">
         <is>
           <t>42</t>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>Установка ревизий Ø110</t>
+          <t>Установка тройников косых и крестовины канализационных</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -2575,12 +2575,16 @@
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" s="33" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="E50" s="33" t="inlineStr">
+        <is>
+          <t>4 + 8 + 3 + 2 + 6 + 1 + 1 = 25</t>
+        </is>
+      </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 74</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 72, 73, 74, 80, 81, 82, 84</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2590,10 +2594,14 @@
       </c>
       <c r="H50" s="30" t="inlineStr">
         <is>
-          <t>5 6 12 17</t>
-        </is>
-      </c>
-      <c r="I50" s="36" t="n"/>
+          <t>5 6 9 12 18</t>
+        </is>
+      </c>
+      <c r="I50" s="36" t="inlineStr">
+        <is>
+          <t>крестовина двухплоскостная — низ Ст.К1-б</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A51" s="30" t="inlineStr">
@@ -2603,7 +2611,7 @@
       </c>
       <c r="B51" s="31" t="inlineStr">
         <is>
-          <t>Устройство прочисток в грунте с выводом в стену до +0,500 (тройник 45°, отвод, стояк в О-блоке, заглушка, гильза)</t>
+          <t>Установка отводов ПП канализационных Ø50, Ø110 в грунте (повороты, низ подъёмов от приборов и стояков, прочистки)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -2612,53 +2620,57 @@
         </is>
       </c>
       <c r="D51" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="E51" s="33" t="inlineStr">
+        <is>
+          <t>17 + 1 + 23 + 1 + 1 = 43</t>
+        </is>
+      </c>
+      <c r="F51" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 75, 76, 77, 78, 79</t>
+        </is>
+      </c>
+      <c r="G51" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H51" s="30" t="inlineStr">
+        <is>
+          <t>6 9 12 14 18</t>
+        </is>
+      </c>
+      <c r="I51" s="36" t="inlineStr">
+        <is>
+          <t>45°, 30°, 15° — по позициям СО</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>Установка ревизий Ø110</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="n">
         <v>3</v>
-      </c>
-      <c r="E51" s="33" t="n"/>
-      <c r="F51" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 73</t>
-        </is>
-      </c>
-      <c r="G51" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H51" s="30" t="inlineStr">
-        <is>
-          <t>6 9 14 17</t>
-        </is>
-      </c>
-      <c r="I51" s="36" t="inlineStr">
-        <is>
-          <t>узел 5 листа 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A52" s="30" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>Установка люков ревизионных нажимных 300×400 в стенах у прочисток и ревизий стояков</t>
-        </is>
-      </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="n">
-        <v>5</v>
       </c>
       <c r="E52" s="33" t="n"/>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 102</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 85</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2668,55 +2680,51 @@
       </c>
       <c r="H52" s="30" t="inlineStr">
         <is>
-          <t>6 9 14 19</t>
-        </is>
-      </c>
-      <c r="I52" s="36" t="inlineStr">
+          <t>5 6 12 18</t>
+        </is>
+      </c>
+      <c r="I52" s="36" t="n"/>
+    </row>
+    <row r="53" ht="60" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>Устройство прочисток в грунте с коротким прямым выводом, заглушка +0,200 (тройник 45°, отвод, патрубок в О-блоке, заглушка, гильза)</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="33" t="n"/>
+      <c r="F53" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 83</t>
+        </is>
+      </c>
+      <c r="G53" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H53" s="30" t="inlineStr">
+        <is>
+          <t>6 9 14 18</t>
+        </is>
+      </c>
+      <c r="I53" s="36" t="inlineStr">
         <is>
           <t>узел 5 листа 14</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A53" s="30" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="inlineStr">
-        <is>
-          <t>Установка трапов с сухим затвором</t>
-        </is>
-      </c>
-      <c r="C53" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D53" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E53" s="33" t="inlineStr">
-        <is>
-          <t>2 + 1 + 1 + 1 = 5</t>
-        </is>
-      </c>
-      <c r="F53" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 94, 95, 96, 97</t>
-        </is>
-      </c>
-      <c r="G53" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H53" s="30" t="inlineStr">
-        <is>
-          <t>4 6 9 18</t>
-        </is>
-      </c>
-      <c r="I53" s="36" t="n"/>
     </row>
     <row r="54" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A54" s="30" t="inlineStr">
@@ -2726,7 +2734,7 @@
       </c>
       <c r="B54" s="31" t="inlineStr">
         <is>
-          <t>Установка сифонов конденсата, сифона стиральной машины и воронки с разрывом струи</t>
+          <t>Установка люков ревизионных нажимных 300×400 в стенах у прочисток и ревизий стояков</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -2737,14 +2745,10 @@
       <c r="D54" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="E54" s="33" t="inlineStr">
-        <is>
-          <t>3 + 1 + 1 = 5</t>
-        </is>
-      </c>
+      <c r="E54" s="33" t="n"/>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 98, 99, 100</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 114</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -2754,12 +2758,12 @@
       </c>
       <c r="H54" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 14 18 19</t>
+          <t>6 9 14 19</t>
         </is>
       </c>
       <c r="I54" s="36" t="inlineStr">
         <is>
-          <t>узел 7 листа 14</t>
+          <t>узел 5 листа 14</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2775,7 @@
       </c>
       <c r="B55" s="31" t="inlineStr">
         <is>
-          <t>Установка проходных кровельных элементов для вытяжных частей стояков Ø110</t>
+          <t>Установка трапов с сухим затвором</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -2780,12 +2784,16 @@
         </is>
       </c>
       <c r="D55" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E55" s="33" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="E55" s="33" t="inlineStr">
+        <is>
+          <t>2 + 1 + 1 + 1 = 5</t>
+        </is>
+      </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 101</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 105, 106, 107, 108</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -2795,14 +2803,10 @@
       </c>
       <c r="H55" s="30" t="inlineStr">
         <is>
-          <t>12 14 19</t>
-        </is>
-      </c>
-      <c r="I55" s="36" t="inlineStr">
-        <is>
-          <t>узел 6 листа 14</t>
-        </is>
-      </c>
+          <t>4 6 9 19</t>
+        </is>
+      </c>
+      <c r="I55" s="36" t="n"/>
     </row>
     <row r="56" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="30" t="inlineStr">
@@ -2812,7 +2816,7 @@
       </c>
       <c r="B56" s="31" t="inlineStr">
         <is>
-          <t>Крепление трубопроводов К1 хомутами с резиновым вкладышем</t>
+          <t>Установка сифонов конденсата, сифона стиральной машины, сифона слива СПА и воронки с разрывом струи</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -2821,16 +2825,16 @@
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="E56" s="33" t="inlineStr">
         <is>
-          <t>25 + 2 + 35 = 62</t>
+          <t>3 + 1 + 1 + 1 = 6</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 131, 132, 133</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 109, 110, 111, 112</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -2840,131 +2844,135 @@
       </c>
       <c r="H56" s="30" t="inlineStr">
         <is>
-          <t>5 14 20</t>
-        </is>
-      </c>
-      <c r="I56" s="36" t="n"/>
-    </row>
-    <row r="57" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>Защита от протечек</t>
-        </is>
-      </c>
-      <c r="B57" s="28" t="n"/>
-      <c r="C57" s="28" t="n"/>
-      <c r="D57" s="28" t="n"/>
-      <c r="E57" s="28" t="n"/>
-      <c r="F57" s="28" t="n"/>
-      <c r="G57" s="28" t="n"/>
-      <c r="H57" s="28" t="n"/>
-      <c r="I57" s="29" t="n"/>
+          <t>5 6 9 14 19</t>
+        </is>
+      </c>
+      <c r="I56" s="36" t="inlineStr">
+        <is>
+          <t>узел 7 листа 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A57" s="30" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>Установка проходных кровельных элементов для вытяжных частей стояков Ø110</t>
+        </is>
+      </c>
+      <c r="C57" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="33" t="n"/>
+      <c r="F57" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 113</t>
+        </is>
+      </c>
+      <c r="G57" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H57" s="30" t="inlineStr">
+        <is>
+          <t>12 14 19</t>
+        </is>
+      </c>
+      <c r="I57" s="36" t="inlineStr">
+        <is>
+          <t>узел 6 листа 14</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="45" customHeight="1" thickBot="1">
       <c r="A58" s="30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B58" s="31" t="inlineStr">
         <is>
+          <t>Крепление трубопроводов К1 хомутами с резиновым вкладышем</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="n">
+        <v>66</v>
+      </c>
+      <c r="E58" s="33" t="inlineStr">
+        <is>
+          <t>25 + 2 + 39 = 66</t>
+        </is>
+      </c>
+      <c r="F58" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 143, 144, 145</t>
+        </is>
+      </c>
+      <c r="G58" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H58" s="30" t="inlineStr">
+        <is>
+          <t>5 14 21</t>
+        </is>
+      </c>
+      <c r="I58" s="36" t="n"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>Защита от протечек</t>
+        </is>
+      </c>
+      <c r="B59" s="28" t="n"/>
+      <c r="C59" s="28" t="n"/>
+      <c r="D59" s="28" t="n"/>
+      <c r="E59" s="28" t="n"/>
+      <c r="F59" s="28" t="n"/>
+      <c r="G59" s="28" t="n"/>
+      <c r="H59" s="28" t="n"/>
+      <c r="I59" s="29" t="n"/>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
           <t>Установка контроллеров системы защиты от протечек с подключением кранов и датчиков</t>
         </is>
       </c>
-      <c r="C58" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="n">
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="n">
         <v>2</v>
-      </c>
-      <c r="E58" s="33" t="n"/>
-      <c r="F58" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 105</t>
-        </is>
-      </c>
-      <c r="G58" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H58" s="30" t="inlineStr">
-        <is>
-          <t>2 4 8 19</t>
-        </is>
-      </c>
-      <c r="I58" s="36" t="inlineStr">
-        <is>
-          <t>питание 230 В и сигнал в умный дом — ЭОМ/СС (ТЗ-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B59" s="31" t="inlineStr">
-        <is>
-          <t>Установка кранов шаровых с электроприводом Ду 20–32</t>
-        </is>
-      </c>
-      <c r="C59" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D59" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" s="33" t="inlineStr">
-        <is>
-          <t>1 + 1 = 2</t>
-        </is>
-      </c>
-      <c r="F59" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 106, 107</t>
-        </is>
-      </c>
-      <c r="G59" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H59" s="30" t="inlineStr">
-        <is>
-          <t>4 7 8 19</t>
-        </is>
-      </c>
-      <c r="I59" s="36" t="n"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="inlineStr">
-        <is>
-          <t>Установка датчиков протечки проводных на полу</t>
-        </is>
-      </c>
-      <c r="C60" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D60" s="32" t="n">
-        <v>19</v>
       </c>
       <c r="E60" s="33" t="n"/>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 108</t>
+          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 117</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -2974,10 +2982,14 @@
       </c>
       <c r="H60" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 19</t>
-        </is>
-      </c>
-      <c r="I60" s="36" t="n"/>
+          <t>2 4 8 20</t>
+        </is>
+      </c>
+      <c r="I60" s="36" t="inlineStr">
+        <is>
+          <t>питание 230 В и сигнал в умный дом — ЭОМ/СС (ТЗ-2)</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="30" t="inlineStr">
@@ -2987,21 +2999,25 @@
       </c>
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>Прокладка кабелей датчиков протечки в гофротрубе</t>
+          <t>Установка кранов шаровых с электроприводом Ду 20–32</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D61" s="32" t="n">
-        <v>180</v>
-      </c>
-      <c r="E61" s="33" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="E61" s="33" t="inlineStr">
+        <is>
+          <t>1 + 2 = 3</t>
+        </is>
+      </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 109</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 118, 119</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -3011,53 +3027,71 @@
       </c>
       <c r="H61" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 19</t>
-        </is>
-      </c>
-      <c r="I61" s="36" t="inlineStr">
-        <is>
-          <t>совместно с ЭОМ/СС</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
-        <is>
-          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
-        </is>
-      </c>
-      <c r="B62" s="28" t="n"/>
-      <c r="C62" s="28" t="n"/>
-      <c r="D62" s="28" t="n"/>
-      <c r="E62" s="28" t="n"/>
-      <c r="F62" s="28" t="n"/>
-      <c r="G62" s="28" t="n"/>
-      <c r="H62" s="28" t="n"/>
-      <c r="I62" s="29" t="n"/>
+          <t>4 7 8 20</t>
+        </is>
+      </c>
+      <c r="I61" s="36" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>Установка датчиков протечки проводных на полу</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="E62" s="33" t="n"/>
+      <c r="F62" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 120</t>
+        </is>
+      </c>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H62" s="30" t="inlineStr">
+        <is>
+          <t>3 4 5 8 20</t>
+        </is>
+      </c>
+      <c r="I62" s="36" t="n"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B63" s="31" t="inlineStr">
         <is>
-          <t>Установка унитазов подвесных с инсталляциями</t>
+          <t>Прокладка кабелей датчиков протечки в гофротрубе</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D63" s="32" t="n">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="E63" s="33" t="n"/>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 88</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 121</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -3067,47 +3101,29 @@
       </c>
       <c r="H63" s="30" t="inlineStr">
         <is>
-          <t>3 5 6 8 9 18</t>
-        </is>
-      </c>
-      <c r="I63" s="36" t="n"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="inlineStr">
-        <is>
-          <t>Установка умывальников со смесителями и сифонами</t>
-        </is>
-      </c>
-      <c r="C64" s="32" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="D64" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E64" s="33" t="n"/>
-      <c r="F64" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 89</t>
-        </is>
-      </c>
-      <c r="G64" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H64" s="30" t="inlineStr">
-        <is>
-          <t>3 5 8 18</t>
-        </is>
-      </c>
-      <c r="I64" s="36" t="n"/>
+          <t>3 4 5 8 20</t>
+        </is>
+      </c>
+      <c r="I63" s="36" t="inlineStr">
+        <is>
+          <t>совместно с ЭОМ/СС</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
+        </is>
+      </c>
+      <c r="B64" s="28" t="n"/>
+      <c r="C64" s="28" t="n"/>
+      <c r="D64" s="28" t="n"/>
+      <c r="E64" s="28" t="n"/>
+      <c r="F64" s="28" t="n"/>
+      <c r="G64" s="28" t="n"/>
+      <c r="H64" s="28" t="n"/>
+      <c r="I64" s="29" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="30" t="inlineStr">
@@ -3117,7 +3133,7 @@
       </c>
       <c r="B65" s="31" t="inlineStr">
         <is>
-          <t>Установка ванн со смесителями и сифонами</t>
+          <t>Установка унитазов подвесных с инсталляциями</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -3126,12 +3142,12 @@
         </is>
       </c>
       <c r="D65" s="32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" s="33" t="n"/>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 90</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 99</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -3141,7 +3157,7 @@
       </c>
       <c r="H65" s="30" t="inlineStr">
         <is>
-          <t>5 8 18</t>
+          <t>3 5 6 8 9 19</t>
         </is>
       </c>
       <c r="I65" s="36" t="n"/>
@@ -3154,7 +3170,7 @@
       </c>
       <c r="B66" s="31" t="inlineStr">
         <is>
-          <t>Установка душевых систем, кабины, подключение трапов</t>
+          <t>Установка умывальников со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -3163,12 +3179,12 @@
         </is>
       </c>
       <c r="D66" s="32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 91</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 100</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3178,7 +3194,7 @@
       </c>
       <c r="H66" s="30" t="inlineStr">
         <is>
-          <t>4 5 8 18</t>
+          <t>3 5 8 19</t>
         </is>
       </c>
       <c r="I66" s="36" t="n"/>
@@ -3191,7 +3207,7 @@
       </c>
       <c r="B67" s="31" t="inlineStr">
         <is>
-          <t>Установка моек кухонных со смесителями и сифонами</t>
+          <t>Установка ванн со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -3200,12 +3216,12 @@
         </is>
       </c>
       <c r="D67" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" s="33" t="n"/>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 92</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 101</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -3215,7 +3231,7 @@
       </c>
       <c r="H67" s="30" t="inlineStr">
         <is>
-          <t>3 8 18</t>
+          <t>5 8 19</t>
         </is>
       </c>
       <c r="I67" s="36" t="n"/>
@@ -3228,21 +3244,21 @@
       </c>
       <c r="B68" s="31" t="inlineStr">
         <is>
-          <t>Установка смесителя для наполнения СПА</t>
+          <t>Установка душевых систем, кабины, подключение трапов</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D68" s="32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" s="33" t="n"/>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 93</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 102</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3252,200 +3268,196 @@
       </c>
       <c r="H68" s="30" t="inlineStr">
         <is>
-          <t>8 18</t>
+          <t>4 5 8 19</t>
         </is>
       </c>
       <c r="I68" s="36" t="n"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="27" t="inlineStr">
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>Установка моек кухонных со смесителями и сифонами</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="33" t="n"/>
+      <c r="F69" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 103</t>
+        </is>
+      </c>
+      <c r="G69" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>3 8 19</t>
+        </is>
+      </c>
+      <c r="I69" s="36" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>Установка смесителя для наполнения СПА</t>
+        </is>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="33" t="n"/>
+      <c r="F70" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 104</t>
+        </is>
+      </c>
+      <c r="G70" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>8 19</t>
+        </is>
+      </c>
+      <c r="I70" s="36" t="n"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
         <is>
           <t>Тепловая изоляция</t>
         </is>
       </c>
-      <c r="B69" s="28" t="n"/>
-      <c r="C69" s="28" t="n"/>
-      <c r="D69" s="28" t="n"/>
-      <c r="E69" s="28" t="n"/>
-      <c r="F69" s="28" t="n"/>
-      <c r="G69" s="28" t="n"/>
-      <c r="H69" s="28" t="n"/>
-      <c r="I69" s="29" t="n"/>
-    </row>
-    <row r="70" ht="45" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="inlineStr">
+      <c r="B71" s="28" t="n"/>
+      <c r="C71" s="28" t="n"/>
+      <c r="D71" s="28" t="n"/>
+      <c r="E71" s="28" t="n"/>
+      <c r="F71" s="28" t="n"/>
+      <c r="G71" s="28" t="n"/>
+      <c r="H71" s="28" t="n"/>
+      <c r="I71" s="29" t="n"/>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="inlineStr">
         <is>
           <t>Изоляция трубопроводов Т3, Т4 трубками из вспененного полиэтилена толщиной 13 мм</t>
         </is>
       </c>
-      <c r="C70" s="32" t="inlineStr">
+      <c r="C72" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D70" s="32" t="n">
-        <v>193</v>
-      </c>
-      <c r="E70" s="33" t="inlineStr">
-        <is>
-          <t>46 + 109 + 38 = 193</t>
-        </is>
-      </c>
-      <c r="F70" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 110, 111, 112</t>
-        </is>
-      </c>
-      <c r="G70" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>3 5 8 10 11 19</t>
-        </is>
-      </c>
-      <c r="I70" s="36" t="n"/>
-    </row>
-    <row r="71" ht="45" customHeight="1">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="inlineStr">
+      <c r="D72" s="32" t="n">
+        <v>219</v>
+      </c>
+      <c r="E72" s="33" t="inlineStr">
+        <is>
+          <t>28 + 144 + 47 = 219</t>
+        </is>
+      </c>
+      <c r="F72" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 122, 123, 124</t>
+        </is>
+      </c>
+      <c r="G72" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H72" s="30" t="inlineStr">
+        <is>
+          <t>3 5 8 10 11 20</t>
+        </is>
+      </c>
+      <c r="I72" s="36" t="n"/>
+    </row>
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="inlineStr">
         <is>
           <t>Изоляция трубопроводов В1 трубками из вспененного полиэтилена толщиной 9 мм</t>
         </is>
       </c>
-      <c r="C71" s="32" t="inlineStr">
+      <c r="C73" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D71" s="32" t="n">
-        <v>198</v>
-      </c>
-      <c r="E71" s="33" t="inlineStr">
-        <is>
-          <t>74 + 43 + 68 + 13 = 198</t>
-        </is>
-      </c>
-      <c r="F71" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 113, 114, 115, 116</t>
-        </is>
-      </c>
-      <c r="G71" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H71" s="30" t="inlineStr">
-        <is>
-          <t>3 5 8 10 11 19</t>
-        </is>
-      </c>
-      <c r="I71" s="36" t="n"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B72" s="31" t="inlineStr">
-        <is>
-          <t>Изоляция ввода ПЭ 32 в проёме фундамента</t>
-        </is>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" s="33" t="n"/>
-      <c r="F72" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 117</t>
-        </is>
-      </c>
-      <c r="G72" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H72" s="30" t="inlineStr">
-        <is>
-          <t>14 19</t>
-        </is>
-      </c>
-      <c r="I72" s="36" t="n"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
+      <c r="D73" s="32" t="n">
+        <v>207</v>
+      </c>
+      <c r="E73" s="33" t="inlineStr">
+        <is>
+          <t>77 + 41 + 77 + 12 = 207</t>
+        </is>
+      </c>
+      <c r="F73" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 125, 126, 127, 128</t>
+        </is>
+      </c>
+      <c r="G73" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H73" s="30" t="inlineStr">
+        <is>
+          <t>3 5 8 10 11 20</t>
+        </is>
+      </c>
+      <c r="I73" s="36" t="n"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
         <is>
           <t>Проходы через строительные конструкции</t>
         </is>
       </c>
-      <c r="B73" s="28" t="n"/>
-      <c r="C73" s="28" t="n"/>
-      <c r="D73" s="28" t="n"/>
-      <c r="E73" s="28" t="n"/>
-      <c r="F73" s="28" t="n"/>
-      <c r="G73" s="28" t="n"/>
-      <c r="H73" s="28" t="n"/>
-      <c r="I73" s="29" t="n"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="inlineStr">
-        <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
-        </is>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="E74" s="33" t="n"/>
-      <c r="F74" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 120</t>
-        </is>
-      </c>
-      <c r="G74" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H74" s="30" t="inlineStr">
-        <is>
-          <t>14 19</t>
-        </is>
-      </c>
-      <c r="I74" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
+      <c r="B74" s="28" t="n"/>
+      <c r="C74" s="28" t="n"/>
+      <c r="D74" s="28" t="n"/>
+      <c r="E74" s="28" t="n"/>
+      <c r="F74" s="28" t="n"/>
+      <c r="G74" s="28" t="n"/>
+      <c r="H74" s="28" t="n"/>
+      <c r="I74" s="29" t="n"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="30" t="inlineStr">
@@ -3455,7 +3467,7 @@
       </c>
       <c r="B75" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -3469,7 +3481,7 @@
       <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 120</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -3479,12 +3491,12 @@
       </c>
       <c r="H75" s="30" t="inlineStr">
         <is>
-          <t>14 19</t>
+          <t>14 20</t>
         </is>
       </c>
       <c r="I75" s="36" t="inlineStr">
         <is>
-          <t>п. 11.5</t>
+          <t>по толщине конструкции</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3508,7 @@
       </c>
       <c r="B76" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
+          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -3505,12 +3517,12 @@
         </is>
       </c>
       <c r="D76" s="32" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 121</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3520,12 +3532,12 @@
       </c>
       <c r="H76" s="30" t="inlineStr">
         <is>
-          <t>14 19</t>
+          <t>14 20</t>
         </is>
       </c>
       <c r="I76" s="36" t="inlineStr">
         <is>
-          <t>по толщине конструкции</t>
+          <t>п. 11.5</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3549,7 @@
       </c>
       <c r="B77" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -3546,12 +3558,12 @@
         </is>
       </c>
       <c r="D77" s="32" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 121</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -3561,12 +3573,12 @@
       </c>
       <c r="H77" s="30" t="inlineStr">
         <is>
-          <t>14 19</t>
+          <t>14 20</t>
         </is>
       </c>
       <c r="I77" s="36" t="inlineStr">
         <is>
-          <t>п. 11.5</t>
+          <t>по толщине конструкции</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3590,7 @@
       </c>
       <c r="B78" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
+          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -3587,12 +3599,12 @@
         </is>
       </c>
       <c r="D78" s="32" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E78" s="33" t="n"/>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 122</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -3602,12 +3614,12 @@
       </c>
       <c r="H78" s="30" t="inlineStr">
         <is>
-          <t>14 19</t>
+          <t>14 20</t>
         </is>
       </c>
       <c r="I78" s="36" t="inlineStr">
         <is>
-          <t>по толщине конструкции</t>
+          <t>п. 11.5</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3631,7 @@
       </c>
       <c r="B79" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -3633,7 +3645,7 @@
       <c r="E79" s="33" t="n"/>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 122</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -3643,16 +3655,16 @@
       </c>
       <c r="H79" s="30" t="inlineStr">
         <is>
-          <t>14 19</t>
+          <t>14 20</t>
         </is>
       </c>
       <c r="I79" s="36" t="inlineStr">
         <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="45" customHeight="1">
+          <t>по толщине конструкции</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
       <c r="A80" s="30" t="inlineStr">
         <is>
           <t>68</t>
@@ -3660,21 +3672,21 @@
       </c>
       <c r="B80" s="31" t="inlineStr">
         <is>
-          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
+          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D80" s="32" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E80" s="33" t="n"/>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 123</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
         </is>
       </c>
       <c r="G80" s="35" t="inlineStr">
@@ -3684,10 +3696,14 @@
       </c>
       <c r="H80" s="30" t="inlineStr">
         <is>
-          <t>14 19</t>
-        </is>
-      </c>
-      <c r="I80" s="36" t="n"/>
+          <t>14 20</t>
+        </is>
+      </c>
+      <c r="I80" s="36" t="inlineStr">
+        <is>
+          <t>п. 11.5</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="45" customHeight="1">
       <c r="A81" s="30" t="inlineStr">
@@ -3697,7 +3713,7 @@
       </c>
       <c r="B81" s="31" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента у ввода и футляров эластичным водогазонепроницаемым материалом</t>
+          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -3706,12 +3722,12 @@
         </is>
       </c>
       <c r="D81" s="32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E81" s="33" t="n"/>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 124</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
         </is>
       </c>
       <c r="G81" s="35" t="inlineStr">
@@ -3721,14 +3737,10 @@
       </c>
       <c r="H81" s="30" t="inlineStr">
         <is>
-          <t>14 19</t>
-        </is>
-      </c>
-      <c r="I81" s="36" t="inlineStr">
-        <is>
-          <t>проёмы — КР (ТЗ-1)</t>
-        </is>
-      </c>
+          <t>14 20</t>
+        </is>
+      </c>
+      <c r="I81" s="36" t="n"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="30" t="inlineStr">
@@ -3738,7 +3750,7 @@
       </c>
       <c r="B82" s="31" t="inlineStr">
         <is>
-          <t>Заделка проёмов под пучки труб в плитах и стенах</t>
+          <t>Заделка торцов футляров эластичным водогазонепроницаемым материалом</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -3747,12 +3759,12 @@
         </is>
       </c>
       <c r="D82" s="32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E82" s="33" t="n"/>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 125</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
         </is>
       </c>
       <c r="G82" s="35" t="inlineStr">
@@ -3767,7 +3779,7 @@
       </c>
       <c r="I82" s="36" t="inlineStr">
         <is>
-          <t>ТЗ-1, лист 4</t>
+          <t>футляры Ø75 и Ø160 (п. 8.8)</t>
         </is>
       </c>
     </row>
@@ -3779,21 +3791,21 @@
       </c>
       <c r="B83" s="31" t="inlineStr">
         <is>
-          <t>Утепление сборного К1-1 под террасой 1.13 плитами ЭППС 50 мм</t>
+          <t>Заделка проёмов под пучки труб в плитах и стенах</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D83" s="32" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="E83" s="33" t="n"/>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 6; И05.09.26-ВК.СО, поз. 126</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 136</t>
         </is>
       </c>
       <c r="G83" s="35" t="inlineStr">
@@ -3803,70 +3815,70 @@
       </c>
       <c r="H83" s="30" t="inlineStr">
         <is>
-          <t>6 20</t>
-        </is>
-      </c>
-      <c r="I83" s="36" t="n"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="27" t="inlineStr">
+          <t>14 20</t>
+        </is>
+      </c>
+      <c r="I83" s="36" t="inlineStr">
+        <is>
+          <t>ТЗ-1, лист 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>Утепление К1-1 под террасой 1.13 и К1-б под террасой бани б1 плитами ЭППС 50 мм</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E84" s="33" t="inlineStr">
+        <is>
+          <t>2.4 + 3.1 = 5.5</t>
+        </is>
+      </c>
+      <c r="F84" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 6, 9; И05.09.26-ВК.СО, поз. 137, 138</t>
+        </is>
+      </c>
+      <c r="G84" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H84" s="30" t="inlineStr">
+        <is>
+          <t>6 9 20</t>
+        </is>
+      </c>
+      <c r="I84" s="36" t="n"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
         <is>
           <t>Испытания и пусконаладочные работы</t>
         </is>
       </c>
-      <c r="B84" s="28" t="n"/>
-      <c r="C84" s="28" t="n"/>
-      <c r="D84" s="28" t="n"/>
-      <c r="E84" s="28" t="n"/>
-      <c r="F84" s="28" t="n"/>
-      <c r="G84" s="28" t="n"/>
-      <c r="H84" s="28" t="n"/>
-      <c r="I84" s="29" t="n"/>
-    </row>
-    <row r="85" ht="45" customHeight="1">
-      <c r="A85" s="30" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B85" s="31" t="inlineStr">
-        <is>
-          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
-        </is>
-      </c>
-      <c r="C85" s="32" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D85" s="32" t="n">
-        <v>391</v>
-      </c>
-      <c r="E85" s="33" t="inlineStr">
-        <is>
-          <t>13 + 105 + 151 + 120 + 2 = 391</t>
-        </is>
-      </c>
-      <c r="F85" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 34, 35, 36, 37, 38</t>
-        </is>
-      </c>
-      <c r="G85" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H85" s="30" t="inlineStr">
-        <is>
-          <t>1 2 16</t>
-        </is>
-      </c>
-      <c r="I85" s="36" t="inlineStr">
-        <is>
-          <t>в т. ч. до закрытия в конструкциях</t>
-        </is>
-      </c>
+      <c r="B85" s="28" t="n"/>
+      <c r="C85" s="28" t="n"/>
+      <c r="D85" s="28" t="n"/>
+      <c r="E85" s="28" t="n"/>
+      <c r="F85" s="28" t="n"/>
+      <c r="G85" s="28" t="n"/>
+      <c r="H85" s="28" t="n"/>
+      <c r="I85" s="29" t="n"/>
     </row>
     <row r="86" ht="45" customHeight="1">
       <c r="A86" s="30" t="inlineStr">
@@ -3876,161 +3888,165 @@
       </c>
       <c r="B86" s="31" t="inlineStr">
         <is>
+          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D86" s="32" t="n">
+        <v>427</v>
+      </c>
+      <c r="E86" s="33" t="inlineStr">
+        <is>
+          <t>12 + 123 + 185 + 104 + 3 = 427</t>
+        </is>
+      </c>
+      <c r="F86" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 34, 35, 36, 37, 38</t>
+        </is>
+      </c>
+      <c r="G86" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H86" s="30" t="inlineStr">
+        <is>
+          <t>1 2 16</t>
+        </is>
+      </c>
+      <c r="I86" s="36" t="inlineStr">
+        <is>
+          <t>в т. ч. до закрытия в конструкциях</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="45" customHeight="1">
+      <c r="A87" s="30" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B87" s="31" t="inlineStr">
+        <is>
           <t>Испытание систем канализации К1 и К2 (участок К2-1) проливом воды</t>
         </is>
       </c>
-      <c r="C86" s="32" t="inlineStr">
+      <c r="C87" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D86" s="32" t="n">
-        <v>141</v>
-      </c>
-      <c r="E86" s="33" t="inlineStr">
-        <is>
-          <t>31 + 26 + 1 + 25 + 55 + 3 = 141</t>
-        </is>
-      </c>
-      <c r="F86" s="34" t="inlineStr">
+      <c r="D87" s="32" t="n">
+        <v>142</v>
+      </c>
+      <c r="E87" s="33" t="inlineStr">
+        <is>
+          <t>30 + 27 + 1 + 29 + 52 + 3 = 142</t>
+        </is>
+      </c>
+      <c r="F87" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 39, 40, 41, 42, 43, 44</t>
         </is>
       </c>
-      <c r="G86" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H86" s="30" t="inlineStr">
+      <c r="G87" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H87" s="30" t="inlineStr">
         <is>
           <t>1 2 16</t>
         </is>
       </c>
-      <c r="I86" s="36" t="n"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="30" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B87" s="31" t="inlineStr">
+      <c r="I87" s="36" t="n"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="30" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B88" s="31" t="inlineStr">
         <is>
           <t>Испытание трубопроводов К1, К2 в грунте наполнением водой до засыпки</t>
         </is>
       </c>
-      <c r="C87" s="32" t="inlineStr">
+      <c r="C88" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D87" s="32" t="n">
-        <v>83</v>
-      </c>
-      <c r="E87" s="33" t="inlineStr">
-        <is>
-          <t>25 + 55 + 3 = 83</t>
-        </is>
-      </c>
-      <c r="F87" s="34" t="inlineStr">
+      <c r="D88" s="32" t="n">
+        <v>84</v>
+      </c>
+      <c r="E88" s="33" t="inlineStr">
+        <is>
+          <t>29 + 52 + 3 = 84</t>
+        </is>
+      </c>
+      <c r="F88" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 42, 43, 44</t>
         </is>
       </c>
-      <c r="G87" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H87" s="30" t="inlineStr">
+      <c r="G88" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H88" s="30" t="inlineStr">
         <is>
           <t>2 14 16</t>
         </is>
       </c>
-      <c r="I87" s="36" t="n"/>
-    </row>
-    <row r="88" ht="45" customHeight="1">
-      <c r="A88" s="30" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B88" s="31" t="inlineStr">
+      <c r="I88" s="36" t="n"/>
+    </row>
+    <row r="89" ht="45" customHeight="1">
+      <c r="A89" s="30" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B89" s="31" t="inlineStr">
         <is>
           <t>Промывка и дезинфекция трубопроводов систем В1, Т3, Т4</t>
         </is>
       </c>
-      <c r="C88" s="32" t="inlineStr">
+      <c r="C89" s="32" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="D88" s="32" t="n">
-        <v>391</v>
-      </c>
-      <c r="E88" s="33" t="inlineStr">
-        <is>
-          <t>13 + 105 + 151 + 120 + 2 = 391</t>
-        </is>
-      </c>
-      <c r="F88" s="34" t="inlineStr">
+      <c r="D89" s="32" t="n">
+        <v>427</v>
+      </c>
+      <c r="E89" s="33" t="inlineStr">
+        <is>
+          <t>12 + 123 + 185 + 104 + 3 = 427</t>
+        </is>
+      </c>
+      <c r="F89" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 34, 35, 36, 37, 38</t>
         </is>
       </c>
-      <c r="G88" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H88" s="30" t="inlineStr">
+      <c r="G89" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H89" s="30" t="inlineStr">
         <is>
           <t>1 2 16</t>
         </is>
       </c>
-      <c r="I88" s="36" t="n"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="30" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B89" s="31" t="inlineStr">
-        <is>
-          <t>Наладка циркуляции ГВС: настройка балансировочных клапанов по П4</t>
-        </is>
-      </c>
-      <c r="C89" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D89" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" s="33" t="n"/>
-      <c r="F89" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 84</t>
-        </is>
-      </c>
-      <c r="G89" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H89" s="30" t="inlineStr">
-        <is>
-          <t>13 18</t>
-        </is>
-      </c>
-      <c r="I89" s="36" t="inlineStr">
-        <is>
-          <t>П4</t>
-        </is>
-      </c>
+      <c r="I89" s="36" t="n"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="30" t="inlineStr">
@@ -4040,51 +4056,92 @@
       </c>
       <c r="B90" s="31" t="inlineStr">
         <is>
+          <t>Наладка циркуляции ГВС: настройка балансировочных клапанов по П4</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D90" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" s="33" t="n"/>
+      <c r="F90" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 95</t>
+        </is>
+      </c>
+      <c r="G90" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H90" s="30" t="inlineStr">
+        <is>
+          <t>13 19</t>
+        </is>
+      </c>
+      <c r="I90" s="36" t="inlineStr">
+        <is>
+          <t>П4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="30" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B91" s="31" t="inlineStr">
+        <is>
           <t>Пусконаладочные работы циркуляционных насосов Н8, Н9</t>
         </is>
       </c>
-      <c r="C90" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D90" s="32" t="n">
+      <c r="C91" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D91" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E90" s="33" t="inlineStr">
+      <c r="E91" s="33" t="inlineStr">
         <is>
           <t>1 + 1 = 2</t>
         </is>
       </c>
-      <c r="F90" s="34" t="inlineStr">
+      <c r="F91" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 7, 8; И05.09.26-ВК.СО, поз. 1, 2</t>
         </is>
       </c>
-      <c r="G90" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H90" s="30" t="inlineStr">
+      <c r="G91" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H91" s="30" t="inlineStr">
         <is>
           <t>7 8 15</t>
         </is>
       </c>
-      <c r="I90" s="36" t="n"/>
+      <c r="I91" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A71:I71"/>
     <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A84:I84"/>
-    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A34:I34"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="55" fitToHeight="0" fitToWidth="1"/>
@@ -4124,10 +4181,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="38" t="inlineStr">
         <is>
-          <t>3. Ввод до наружной грани фундамента, выпуски за границей с НВК, колодцы и наружные сети — раздел НВК.</t>
+          <t>3. Ввод до наружной грани фундамента, выпуски за границей с НВК, колодцы и наружные сети — раздел НВК. Ввод — без приямка: под краем плиты и сквозь плиту в футляре Ø75 (футляр закладывается до бетонирования).</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 69,6, Т3 41,9 м + 10 %</t>
+          <t>по модели В1 69,5, Т3 41,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E16" s="33" t="n"/>
       <c r="F16" s="34" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I16" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 36,6, Т3 63,7, Т4 67,0 м + 10 %</t>
+          <t>по модели В1 37,9, Т3 63,7, Т4 67,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="D23" s="32" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
-          <t>54 + 37 = 91</t>
+          <t>56 + 37 = 93</t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 129, 130</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 128, 129</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 139, 140, 141, 142</t>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 138, 139, 140, 141</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
@@ -1653,7 +1653,7 @@
       <c r="E25" s="33" t="n"/>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 146</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 145</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 89, 90</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 88, 89</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1746,7 +1746,7 @@
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 91</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 90</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1783,7 +1783,7 @@
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 95</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 94</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1824,7 +1824,7 @@
       <c r="E30" s="33" t="n"/>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 96</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 95</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1865,7 +1865,7 @@
       <c r="E31" s="33" t="n"/>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 97</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 96</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 92, 93, 94</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 91, 92, 93</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="H32" s="30" t="inlineStr">
         <is>
-          <t>4 7 14 19</t>
+          <t>4 7 14 18 19</t>
         </is>
       </c>
       <c r="I32" s="36" t="inlineStr">
@@ -1947,7 +1947,7 @@
       <c r="E33" s="33" t="n"/>
       <c r="F33" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 98</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 97</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -2498,7 +2498,7 @@
       <c r="E48" s="33" t="n"/>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 115</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 114</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -2539,7 +2539,7 @@
       <c r="E49" s="33" t="n"/>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 116</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 115</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 72, 73, 74, 80, 81, 82, 84</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 72, 73, 74, 79, 80, 81, 83</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="E51" s="33" t="inlineStr">
         <is>
-          <t>17 + 1 + 23 + 1 + 1 = 43</t>
+          <t>17 + 1 + 24 + 1 = 43</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 75, 76, 77, 78, 79</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 75, 76, 77, 78</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -2670,7 +2670,7 @@
       <c r="E52" s="33" t="n"/>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 85</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 84</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2707,7 +2707,7 @@
       <c r="E53" s="33" t="n"/>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 83</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 82</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -2748,7 +2748,7 @@
       <c r="E54" s="33" t="n"/>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 114</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 113</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 105, 106, 107, 108</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 104, 105, 106, 107</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 109, 110, 111, 112</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 108, 109, 110, 111</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -2875,7 +2875,7 @@
       <c r="E57" s="33" t="n"/>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 113</t>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 112</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 143, 144, 145</t>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 142, 143, 144</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -2972,7 +2972,7 @@
       <c r="E60" s="33" t="n"/>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 117</t>
+          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 116</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 118, 119</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 117, 118</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -3054,7 +3054,7 @@
       <c r="E62" s="33" t="n"/>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 120</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 119</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -3091,7 +3091,7 @@
       <c r="E63" s="33" t="n"/>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 121</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 120</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -3147,7 +3147,7 @@
       <c r="E65" s="33" t="n"/>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 99</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 98</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -3184,7 +3184,7 @@
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 100</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 99</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3221,7 +3221,7 @@
       <c r="E67" s="33" t="n"/>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 101</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 100</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -3258,7 +3258,7 @@
       <c r="E68" s="33" t="n"/>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 102</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 101</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3295,7 +3295,7 @@
       <c r="E69" s="33" t="n"/>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 103</t>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 102</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -3332,7 +3332,7 @@
       <c r="E70" s="33" t="n"/>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 104</t>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 103</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 122, 123, 124</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 121, 122, 123</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -3420,16 +3420,16 @@
         </is>
       </c>
       <c r="D73" s="32" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E73" s="33" t="inlineStr">
         <is>
-          <t>77 + 41 + 77 + 12 = 207</t>
+          <t>77 + 42 + 77 + 12 = 208</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 125, 126, 127, 128</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 124, 125, 126, 127</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -3476,12 +3476,12 @@
         </is>
       </c>
       <c r="D75" s="32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 130</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -3517,12 +3517,12 @@
         </is>
       </c>
       <c r="D76" s="32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 130</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3563,7 +3563,7 @@
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -3604,7 +3604,7 @@
       <c r="E78" s="33" t="n"/>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -3645,7 +3645,7 @@
       <c r="E79" s="33" t="n"/>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -3686,7 +3686,7 @@
       <c r="E80" s="33" t="n"/>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
         </is>
       </c>
       <c r="G80" s="35" t="inlineStr">
@@ -3727,7 +3727,7 @@
       <c r="E81" s="33" t="n"/>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
         </is>
       </c>
       <c r="G81" s="35" t="inlineStr">
@@ -3764,7 +3764,7 @@
       <c r="E82" s="33" t="n"/>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
         </is>
       </c>
       <c r="G82" s="35" t="inlineStr">
@@ -3805,7 +3805,7 @@
       <c r="E83" s="33" t="n"/>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 136</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
         </is>
       </c>
       <c r="G83" s="35" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9; И05.09.26-ВК.СО, поз. 137, 138</t>
+          <t>И05.09.26-ВК, см. листы 6, 9; И05.09.26-ВК.СО, поз. 136, 137</t>
         </is>
       </c>
       <c r="G84" s="35" t="inlineStr">
@@ -3897,11 +3897,11 @@
         </is>
       </c>
       <c r="D86" s="32" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E86" s="33" t="inlineStr">
         <is>
-          <t>12 + 123 + 185 + 104 + 3 = 427</t>
+          <t>12 + 123 + 186 + 104 + 3 = 428</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
@@ -4024,11 +4024,11 @@
         </is>
       </c>
       <c r="D89" s="32" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E89" s="33" t="inlineStr">
         <is>
-          <t>12 + 123 + 185 + 104 + 3 = 427</t>
+          <t>12 + 123 + 186 + 104 + 3 = 428</t>
         </is>
       </c>
       <c r="F89" s="34" t="inlineStr">
@@ -4070,7 +4070,7 @@
       <c r="E90" s="33" t="n"/>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 95</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 94</t>
         </is>
       </c>
       <c r="G90" s="35" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>Монтаж водомерного узла Ду 32 на вводе: краны шаровые, фильтр сетчатый, манометр, счётчик Ду 20, обратный клапан, фильтр тонкой очистки, регулятор давления</t>
+          <t>Монтаж водомерного узла Ду 32 на вводе: краны шаровые, фильтр сетчатый, манометр, счётчик Ду 20, контрольный кран, обратный клапан, фильтр тонкой очистки, регулятор давления</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -863,7 +863,7 @@
       <c r="E5" s="33" t="n"/>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 66</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 18, 67</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
@@ -904,7 +904,7 @@
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 7; И05.09.26-ВК.СО, поз. 18</t>
+          <t>И05.09.26-ВК, см. лист 7; И05.09.26-ВК.СО, поз. 19</t>
         </is>
       </c>
       <c r="G6" s="35" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8, 13; И05.09.26-ВК.СО, поз. 19, 20, 21, 22, 23, 24, 25, 26</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8, 13; И05.09.26-ВК.СО, поз. 20, 21, 22, 23, 24, 25, 26, 27</t>
         </is>
       </c>
       <c r="G7" s="35" t="inlineStr">
@@ -982,7 +982,7 @@
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 27</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 28</t>
         </is>
       </c>
       <c r="G8" s="35" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 8, 13, 14; И05.09.26-ВК.СО, поз. 28, 29, 30, 31</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8, 13, 14; И05.09.26-ВК.СО, поз. 29, 30, 31, 32</t>
         </is>
       </c>
       <c r="G9" s="35" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
-          <t>узел 10 листа 14; ниши — АР (ТЗ-1)</t>
+          <t>узел 9 листа 14; ниши — АР (ТЗ-1)</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 13, 14; И05.09.26-ВК.СО, поз. 32, 33</t>
+          <t>И05.09.26-ВК, см. листы 13, 14; И05.09.26-ВК.СО, поз. 33, 34</t>
         </is>
       </c>
       <c r="G10" s="35" t="inlineStr">
@@ -1120,7 +1120,7 @@
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 46</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 47</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="I12" s="36" t="inlineStr">
         <is>
-          <t>узел 1 листа 14; отводы R ≥ 0,3 м — поз. 47</t>
+          <t>узел 1 листа 14; отводы R ≥ 0,3 м — поз. 48</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 34</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 35</t>
         </is>
       </c>
       <c r="G13" s="35" t="inlineStr">
@@ -1202,7 +1202,7 @@
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 35</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 36</t>
         </is>
       </c>
       <c r="G14" s="35" t="inlineStr">
@@ -1243,7 +1243,7 @@
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 36</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 37</t>
         </is>
       </c>
       <c r="G15" s="35" t="inlineStr">
@@ -1284,7 +1284,7 @@
       <c r="E16" s="33" t="n"/>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 37</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 38</t>
         </is>
       </c>
       <c r="G16" s="35" t="inlineStr">
@@ -1325,7 +1325,7 @@
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 38</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 39</t>
         </is>
       </c>
       <c r="G17" s="35" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 48, 49, 50</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 49, 50, 51</t>
         </is>
       </c>
       <c r="G18" s="35" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 51, 52, 53, 54</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 52, 53, 54, 55</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 55, 56, 57, 58, 59, 60</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 56, 57, 58, 59, 60, 61</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 61, 62, 63, 64</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 62, 63, 64, 65</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       <c r="E22" s="33" t="n"/>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 65</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 66</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 128, 129</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 129, 130</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 138, 139, 140, 141</t>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 139, 140, 141, 142</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
@@ -1653,7 +1653,7 @@
       <c r="E25" s="33" t="n"/>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 145</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 146</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>Установка кранов шаровых Ду 15–20</t>
+          <t>Установка кранов шаровых Ду 15–25</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="D27" s="32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" s="33" t="inlineStr">
         <is>
-          <t>6 + 10 = 16</t>
+          <t>1 + 6 + 10 = 17</t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 88, 89</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 88, 89, 90</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1746,7 +1746,7 @@
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 90</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 91</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1783,7 +1783,7 @@
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 94</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 95</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1824,7 +1824,7 @@
       <c r="E30" s="33" t="n"/>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 95</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 96</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="I30" s="36" t="inlineStr">
         <is>
-          <t>узел 9 листа 14</t>
+          <t>узел 8 листа 14</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       <c r="E31" s="33" t="n"/>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 96</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 97</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 91, 92, 93</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 92, 93, 94</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -1947,7 +1947,7 @@
       <c r="E33" s="33" t="n"/>
       <c r="F33" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 97</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 98</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 5, 6, 7, 8</t>
+          <t>И05.09.26-ВК, см. листы 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 5, 6, 7, 8, 9</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -2178,7 +2178,7 @@
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 39, 67</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 40, 68</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2215,7 +2215,7 @@
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 40, 68, 69</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 41, 69, 70</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -2252,7 +2252,7 @@
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 41, 70, 71</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 42, 71, 72</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -2289,7 +2289,7 @@
       <c r="E43" s="33" t="n"/>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 42</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 43</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="E44" s="33" t="n"/>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 43</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 44</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 42, 43, 44</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 43, 44, 45</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -2416,7 +2416,7 @@
       <c r="E46" s="33" t="n"/>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 45</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 46</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -2457,7 +2457,7 @@
       <c r="E47" s="33" t="n"/>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 14; И05.09.26-ВК.СО, поз. 44</t>
+          <t>И05.09.26-ВК, см. листы 4, 14; И05.09.26-ВК.СО, поз. 45</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -2498,7 +2498,7 @@
       <c r="E48" s="33" t="n"/>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 114</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 115</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -2539,7 +2539,7 @@
       <c r="E49" s="33" t="n"/>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 115</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 116</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 72, 73, 74, 79, 80, 81, 83</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 73, 74, 75, 80, 81, 82, 84</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 75, 76, 77, 78</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 76, 77, 78, 79</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -2670,7 +2670,7 @@
       <c r="E52" s="33" t="n"/>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 84</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 85</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2707,7 +2707,7 @@
       <c r="E53" s="33" t="n"/>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 82</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 83, 86</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -2748,7 +2748,7 @@
       <c r="E54" s="33" t="n"/>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 113</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 114</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 104, 105, 106, 107</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 105, 106, 107, 108</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 108, 109, 110, 111</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 109, 110, 111, 112</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -2875,7 +2875,7 @@
       <c r="E57" s="33" t="n"/>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 112</t>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 113</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 142, 143, 144</t>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 143, 144, 145</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -2972,7 +2972,7 @@
       <c r="E60" s="33" t="n"/>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 116</t>
+          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 117</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 117, 118</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 118, 119</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -3054,7 +3054,7 @@
       <c r="E62" s="33" t="n"/>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 119</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 120</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -3091,7 +3091,7 @@
       <c r="E63" s="33" t="n"/>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 120</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 121</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -3147,7 +3147,7 @@
       <c r="E65" s="33" t="n"/>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 98</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 99</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -3184,7 +3184,7 @@
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 99</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 100</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3221,7 +3221,7 @@
       <c r="E67" s="33" t="n"/>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 100</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 101</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -3258,7 +3258,7 @@
       <c r="E68" s="33" t="n"/>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 101</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 102</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3295,7 +3295,7 @@
       <c r="E69" s="33" t="n"/>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 102</t>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 103</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -3332,7 +3332,7 @@
       <c r="E70" s="33" t="n"/>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 103</t>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 104</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 121, 122, 123</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 122, 123, 124</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 124, 125, 126, 127</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 125, 126, 127, 128</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -3481,7 +3481,7 @@
       <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 130</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -3522,7 +3522,7 @@
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 130</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3563,7 +3563,7 @@
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -3604,7 +3604,7 @@
       <c r="E78" s="33" t="n"/>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -3645,7 +3645,7 @@
       <c r="E79" s="33" t="n"/>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -3686,7 +3686,7 @@
       <c r="E80" s="33" t="n"/>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
         </is>
       </c>
       <c r="G80" s="35" t="inlineStr">
@@ -3727,7 +3727,7 @@
       <c r="E81" s="33" t="n"/>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
         </is>
       </c>
       <c r="G81" s="35" t="inlineStr">
@@ -3764,7 +3764,7 @@
       <c r="E82" s="33" t="n"/>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
         </is>
       </c>
       <c r="G82" s="35" t="inlineStr">
@@ -3805,7 +3805,7 @@
       <c r="E83" s="33" t="n"/>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 136</t>
         </is>
       </c>
       <c r="G83" s="35" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9; И05.09.26-ВК.СО, поз. 136, 137</t>
+          <t>И05.09.26-ВК, см. листы 6, 9; И05.09.26-ВК.СО, поз. 137, 138</t>
         </is>
       </c>
       <c r="G84" s="35" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 34, 35, 36, 37, 38</t>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 35, 36, 37, 38, 39</t>
         </is>
       </c>
       <c r="G86" s="35" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 39, 40, 41, 42, 43, 44</t>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 40, 41, 42, 43, 44, 45</t>
         </is>
       </c>
       <c r="G87" s="35" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 42, 43, 44</t>
+          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 43, 44, 45</t>
         </is>
       </c>
       <c r="G88" s="35" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 34, 35, 36, 37, 38</t>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 35, 36, 37, 38, 39</t>
         </is>
       </c>
       <c r="G89" s="35" t="inlineStr">
@@ -4070,7 +4070,7 @@
       <c r="E90" s="33" t="n"/>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 94</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 95</t>
         </is>
       </c>
       <c r="G90" s="35" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 69,5, Т3 41,9 м + 10 %</t>
+          <t>по модели В1 69,5, Т3 42,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I16" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 37,9, Т3 63,7, Т4 67,0 м + 10 %</t>
+          <t>по модели В1 37,9, Т3 63,7, Т4 67,1 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="D17" s="32" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="34" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="I17" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 69,6, Т3 24,7 м + 10 %</t>
+          <t>по модели В1 70,6, Т3 25,2 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 129, 130</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 131, 132</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -1603,16 +1603,16 @@
         </is>
       </c>
       <c r="D24" s="32" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E24" s="33" t="inlineStr">
         <is>
-          <t>36 + 81 + 89 + 24 = 230</t>
+          <t>39 + 81 + 89 + 24 = 233</t>
         </is>
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 139, 140, 141, 142</t>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 141, 142, 143, 144</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H24" s="30" t="inlineStr">
         <is>
-          <t>5 7 14 20 21</t>
+          <t>5 7 14 21</t>
         </is>
       </c>
       <c r="I24" s="36" t="inlineStr">
@@ -1653,7 +1653,7 @@
       <c r="E25" s="33" t="n"/>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 146</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 148</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 88, 89, 90</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 90, 91, 92</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1741,12 +1741,12 @@
         </is>
       </c>
       <c r="D28" s="32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 91</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 93</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H28" s="30" t="inlineStr">
         <is>
-          <t>10 11 18</t>
+          <t>10 11 19</t>
         </is>
       </c>
       <c r="I28" s="36" t="n"/>
@@ -1783,7 +1783,7 @@
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 95</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 97</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1824,7 +1824,7 @@
       <c r="E30" s="33" t="n"/>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 96</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 98</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1865,7 +1865,7 @@
       <c r="E31" s="33" t="n"/>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 97</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 99</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 92, 93, 94</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 94, 95, 96</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="H32" s="30" t="inlineStr">
         <is>
-          <t>4 7 14 18 19</t>
+          <t>4 7 14 19</t>
         </is>
       </c>
       <c r="I32" s="36" t="inlineStr">
@@ -1947,7 +1947,7 @@
       <c r="E33" s="33" t="n"/>
       <c r="F33" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 98</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 100</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="D41" s="32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E43" s="33" t="n"/>
       <c r="F43" s="34" t="inlineStr">
@@ -2366,11 +2366,11 @@
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E45" s="33" t="inlineStr">
         <is>
-          <t>29 + 52 + 3 = 84</t>
+          <t>25 + 52 + 3 = 80</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr">
@@ -2498,7 +2498,7 @@
       <c r="E48" s="33" t="n"/>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 115</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 117</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="H48" s="30" t="inlineStr">
         <is>
-          <t>4 19</t>
+          <t>4 20</t>
         </is>
       </c>
       <c r="I48" s="36" t="inlineStr">
@@ -2539,7 +2539,7 @@
       <c r="E49" s="33" t="n"/>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 116</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 118</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="H49" s="30" t="inlineStr">
         <is>
-          <t>4 19</t>
+          <t>4 20</t>
         </is>
       </c>
       <c r="I49" s="36" t="inlineStr">
@@ -2575,16 +2575,16 @@
         </is>
       </c>
       <c r="D50" s="32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E50" s="33" t="inlineStr">
         <is>
-          <t>4 + 8 + 3 + 2 + 6 + 1 + 1 = 25</t>
+          <t>4 + 1 + 4 + 3 + 2 + 6 + 1 + 1 + 1 = 23</t>
         </is>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 73, 74, 75, 80, 81, 82, 84</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 73, 74, 75, 76, 81, 82, 83, 84, 86</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="I50" s="36" t="inlineStr">
         <is>
-          <t>крестовина двухплоскостная — низ Ст.К1-б</t>
+          <t>крестовина двухплоскостная — низ Ст.К1-б, косая 45° — пол 1.4</t>
         </is>
       </c>
     </row>
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E51" s="33" t="inlineStr">
         <is>
-          <t>17 + 1 + 24 + 1 = 43</t>
+          <t>17 + 1 + 18 + 1 = 37</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 76, 77, 78, 79</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 77, 78, 79, 80</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -2670,7 +2670,7 @@
       <c r="E52" s="33" t="n"/>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 85</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 87</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2707,7 +2707,7 @@
       <c r="E53" s="33" t="n"/>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 83, 86</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 85, 88</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -2748,7 +2748,7 @@
       <c r="E54" s="33" t="n"/>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 114</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 116</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H54" s="30" t="inlineStr">
         <is>
-          <t>6 9 14 19</t>
+          <t>6 9 14 20</t>
         </is>
       </c>
       <c r="I54" s="36" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 105, 106, 107, 108</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 107, 108, 109, 110</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 109, 110, 111, 112</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 111, 112, 113, 114</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -2875,7 +2875,7 @@
       <c r="E57" s="33" t="n"/>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 113</t>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 115</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -2911,16 +2911,16 @@
         </is>
       </c>
       <c r="D58" s="32" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E58" s="33" t="inlineStr">
         <is>
-          <t>25 + 2 + 39 = 66</t>
+          <t>26 + 2 + 48 = 76</t>
         </is>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 143, 144, 145</t>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 145, 146, 147</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -2972,7 +2972,7 @@
       <c r="E60" s="33" t="n"/>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 117</t>
+          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 119</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 118, 119</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 120, 121</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -3054,7 +3054,7 @@
       <c r="E62" s="33" t="n"/>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 120</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 122</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -3091,7 +3091,7 @@
       <c r="E63" s="33" t="n"/>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 121</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 123</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -3147,7 +3147,7 @@
       <c r="E65" s="33" t="n"/>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 99</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 101</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -3184,7 +3184,7 @@
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 100</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 102</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3221,7 +3221,7 @@
       <c r="E67" s="33" t="n"/>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 101</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 103</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -3258,7 +3258,7 @@
       <c r="E68" s="33" t="n"/>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 102</t>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 104</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3295,7 +3295,7 @@
       <c r="E69" s="33" t="n"/>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 103</t>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 105</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -3332,7 +3332,7 @@
       <c r="E70" s="33" t="n"/>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 104</t>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 106</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 122, 123, 124</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 124, 125, 126</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -3420,16 +3420,16 @@
         </is>
       </c>
       <c r="D73" s="32" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E73" s="33" t="inlineStr">
         <is>
-          <t>77 + 42 + 77 + 12 = 208</t>
+          <t>78 + 42 + 77 + 12 = 209</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 125, 126, 127, 128</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 127, 128, 129, 130</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -3481,7 +3481,7 @@
       <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -3522,7 +3522,7 @@
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 131</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3558,12 +3558,12 @@
         </is>
       </c>
       <c r="D77" s="32" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E77" s="33" t="n"/>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -3599,12 +3599,12 @@
         </is>
       </c>
       <c r="D78" s="32" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E78" s="33" t="n"/>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 132</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -3645,7 +3645,7 @@
       <c r="E79" s="33" t="n"/>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -3686,7 +3686,7 @@
       <c r="E80" s="33" t="n"/>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
         </is>
       </c>
       <c r="G80" s="35" t="inlineStr">
@@ -3727,7 +3727,7 @@
       <c r="E81" s="33" t="n"/>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 136</t>
         </is>
       </c>
       <c r="G81" s="35" t="inlineStr">
@@ -3764,7 +3764,7 @@
       <c r="E82" s="33" t="n"/>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 137</t>
         </is>
       </c>
       <c r="G82" s="35" t="inlineStr">
@@ -3805,7 +3805,7 @@
       <c r="E83" s="33" t="n"/>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 136</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 138</t>
         </is>
       </c>
       <c r="G83" s="35" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9; И05.09.26-ВК.СО, поз. 137, 138</t>
+          <t>И05.09.26-ВК, см. листы 6, 9; И05.09.26-ВК.СО, поз. 139, 140</t>
         </is>
       </c>
       <c r="G84" s="35" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H84" s="30" t="inlineStr">
         <is>
-          <t>6 9 20</t>
+          <t>6 9 20 21</t>
         </is>
       </c>
       <c r="I84" s="36" t="n"/>
@@ -3897,11 +3897,11 @@
         </is>
       </c>
       <c r="D86" s="32" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E86" s="33" t="inlineStr">
         <is>
-          <t>12 + 123 + 186 + 104 + 3 = 428</t>
+          <t>12 + 123 + 186 + 106 + 3 = 430</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
@@ -3942,11 +3942,11 @@
         </is>
       </c>
       <c r="D87" s="32" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E87" s="33" t="inlineStr">
         <is>
-          <t>30 + 27 + 1 + 29 + 52 + 3 = 142</t>
+          <t>30 + 28 + 1 + 25 + 52 + 3 = 139</t>
         </is>
       </c>
       <c r="F87" s="34" t="inlineStr">
@@ -3983,11 +3983,11 @@
         </is>
       </c>
       <c r="D88" s="32" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E88" s="33" t="inlineStr">
         <is>
-          <t>29 + 52 + 3 = 84</t>
+          <t>25 + 52 + 3 = 80</t>
         </is>
       </c>
       <c r="F88" s="34" t="inlineStr">
@@ -4024,11 +4024,11 @@
         </is>
       </c>
       <c r="D89" s="32" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E89" s="33" t="inlineStr">
         <is>
-          <t>12 + 123 + 186 + 104 + 3 = 428</t>
+          <t>12 + 123 + 186 + 106 + 3 = 430</t>
         </is>
       </c>
       <c r="F89" s="34" t="inlineStr">
@@ -4070,7 +4070,7 @@
       <c r="E90" s="33" t="n"/>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 95</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 97</t>
         </is>
       </c>
       <c r="G90" s="35" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D16" s="32" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E16" s="33" t="n"/>
       <c r="F16" s="34" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I16" s="36" t="inlineStr">
         <is>
-          <t>по модели В1 37,9, Т3 63,7, Т4 67,1 м + 10 %</t>
+          <t>по модели В1 37,9, Т3 56,3, Т4 83,5 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1443,11 +1443,11 @@
         </is>
       </c>
       <c r="D20" s="32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="33" t="inlineStr">
         <is>
-          <t>2 + 3 + 1 + 1 + 1 + 2 = 10</t>
+          <t>2 + 4 + 1 + 1 + 1 + 2 = 11</t>
         </is>
       </c>
       <c r="F20" s="34" t="inlineStr">
@@ -1484,11 +1484,11 @@
         </is>
       </c>
       <c r="D21" s="32" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E21" s="33" t="inlineStr">
         <is>
-          <t>34 + 41 + 21 + 2 = 98</t>
+          <t>34 + 43 + 21 + 2 = 100</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="D23" s="32" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
-          <t>56 + 37 = 93</t>
+          <t>56 + 39 = 95</t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr">
@@ -1603,11 +1603,11 @@
         </is>
       </c>
       <c r="D24" s="32" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E24" s="33" t="inlineStr">
         <is>
-          <t>39 + 81 + 89 + 24 = 233</t>
+          <t>39 + 83 + 89 + 24 = 235</t>
         </is>
       </c>
       <c r="F24" s="34" t="inlineStr">
@@ -1700,11 +1700,11 @@
         </is>
       </c>
       <c r="D27" s="32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E27" s="33" t="inlineStr">
         <is>
-          <t>1 + 6 + 10 = 17</t>
+          <t>1 + 6 + 12 = 19</t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="H27" s="30" t="inlineStr">
         <is>
-          <t>7 8 10 11 18</t>
+          <t>7 8 10 11 18 19</t>
         </is>
       </c>
       <c r="I27" s="36" t="n"/>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="D28" s="32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="D29" s="32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="H56" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 14 19</t>
+          <t>5 6 9 14 19 20</t>
         </is>
       </c>
       <c r="I56" s="36" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="H57" s="30" t="inlineStr">
         <is>
-          <t>12 14 19</t>
+          <t>12 14 20</t>
         </is>
       </c>
       <c r="I57" s="36" t="inlineStr">
@@ -3379,11 +3379,11 @@
         </is>
       </c>
       <c r="D72" s="32" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E72" s="33" t="inlineStr">
         <is>
-          <t>28 + 144 + 47 = 219</t>
+          <t>28 + 154 + 47 = 229</t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="H82" s="30" t="inlineStr">
         <is>
-          <t>14 20</t>
+          <t>14 21</t>
         </is>
       </c>
       <c r="I82" s="36" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H83" s="30" t="inlineStr">
         <is>
-          <t>14 20</t>
+          <t>14 21</t>
         </is>
       </c>
       <c r="I83" s="36" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H84" s="30" t="inlineStr">
         <is>
-          <t>6 9 20 21</t>
+          <t>6 9 21</t>
         </is>
       </c>
       <c r="I84" s="36" t="n"/>
@@ -3897,11 +3897,11 @@
         </is>
       </c>
       <c r="D86" s="32" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="E86" s="33" t="inlineStr">
         <is>
-          <t>12 + 123 + 186 + 106 + 3 = 430</t>
+          <t>12 + 123 + 196 + 106 + 3 = 440</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
@@ -4024,11 +4024,11 @@
         </is>
       </c>
       <c r="D89" s="32" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="E89" s="33" t="inlineStr">
         <is>
-          <t>12 + 123 + 186 + 106 + 3 = 430</t>
+          <t>12 + 123 + 196 + 106 + 3 = 440</t>
         </is>
       </c>
       <c r="F89" s="34" t="inlineStr">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="D90" s="32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E90" s="33" t="n"/>
       <c r="F90" s="34" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.ВОР Ведомость объёмов работ (форма Заказчика).xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -863,7 +863,7 @@
       <c r="E5" s="33" t="n"/>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 18, 67</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 10, 11, 12, 13, 14, 15, 16, 17, 18, 68</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="H5" s="30" t="inlineStr">
         <is>
-          <t>7 14 15 17</t>
+          <t>7 14 16 18</t>
         </is>
       </c>
       <c r="I5" s="36" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="H6" s="30" t="inlineStr">
         <is>
-          <t>7 15</t>
+          <t>7 16</t>
         </is>
       </c>
       <c r="I6" s="36" t="n"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="H7" s="30" t="inlineStr">
         <is>
-          <t>4 5 8 13 15 16</t>
+          <t>4 5 8 13 16 17</t>
         </is>
       </c>
       <c r="I7" s="36" t="n"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
-          <t>13 16</t>
+          <t>13 17</t>
         </is>
       </c>
       <c r="I8" s="36" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H9" s="30" t="inlineStr">
         <is>
-          <t>3 4 8 13 14 16</t>
+          <t>3 4 8 13 14 17</t>
         </is>
       </c>
       <c r="I9" s="36" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H10" s="30" t="inlineStr">
         <is>
-          <t>13 14 16</t>
+          <t>13 14 17</t>
         </is>
       </c>
       <c r="I10" s="36" t="inlineStr">
@@ -1120,7 +1120,7 @@
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 47</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 48</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="H12" s="30" t="inlineStr">
         <is>
-          <t>7 14 17</t>
+          <t>7 14 18</t>
         </is>
       </c>
       <c r="I12" s="36" t="inlineStr">
         <is>
-          <t>узел 1 листа 14; отводы R ≥ 0,3 м — поз. 48</t>
+          <t>узел 1 листа 14; отводы R ≥ 0,3 м — поз. 49</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H13" s="30" t="inlineStr">
         <is>
-          <t>7 14 16</t>
+          <t>7 14 17</t>
         </is>
       </c>
       <c r="I13" s="36" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H14" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 10 11 16</t>
+          <t>3 4 5 8 10 11 17</t>
         </is>
       </c>
       <c r="I14" s="36" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H15" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 10 11 16</t>
+          <t>3 4 5 8 10 11 17</t>
         </is>
       </c>
       <c r="I15" s="36" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H16" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 10 11 16</t>
+          <t>3 4 5 8 10 11 17</t>
         </is>
       </c>
       <c r="I16" s="36" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="H17" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 10 11 16</t>
+          <t>3 4 5 8 10 11 17</t>
         </is>
       </c>
       <c r="I17" s="36" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 49, 50, 51</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 50, 51, 52</t>
         </is>
       </c>
       <c r="G18" s="35" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H18" s="30" t="inlineStr">
         <is>
-          <t>13 17</t>
+          <t>13 18</t>
         </is>
       </c>
       <c r="I18" s="36" t="n"/>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 52, 53, 54, 55</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 53, 54, 55, 56</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H19" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 17</t>
+          <t>3 4 5 8 18</t>
         </is>
       </c>
       <c r="I19" s="36" t="n"/>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 56, 57, 58, 59, 60, 61</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 57, 58, 59, 60, 61, 62</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H20" s="30" t="inlineStr">
         <is>
-          <t>10 11 17</t>
+          <t>10 11 18</t>
         </is>
       </c>
       <c r="I20" s="36" t="n"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 62, 63, 64, 65</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 8; И05.09.26-ВК.СО, поз. 63, 64, 65, 66</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H21" s="30" t="inlineStr">
         <is>
-          <t>3 4 8 17</t>
+          <t>3 4 8 18</t>
         </is>
       </c>
       <c r="I21" s="36" t="n"/>
@@ -1530,7 +1530,7 @@
       <c r="E22" s="33" t="n"/>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 66</t>
+          <t>И05.09.26-ВК, см. листы 7, 14; И05.09.26-ВК.СО, поз. 67</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H22" s="30" t="inlineStr">
         <is>
-          <t>7 14 17</t>
+          <t>7 14 18</t>
         </is>
       </c>
       <c r="I22" s="36" t="n"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 131, 132</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 138, 139</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H23" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 20</t>
+          <t>3 4 5 8 22</t>
         </is>
       </c>
       <c r="I23" s="36" t="n"/>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 141, 142, 143, 144</t>
+          <t>И05.09.26-ВК, см. листы 5, 7, 14; И05.09.26-ВК.СО, поз. 149, 150, 151, 152</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H24" s="30" t="inlineStr">
         <is>
-          <t>5 7 14 21</t>
+          <t>5 7 14 22</t>
         </is>
       </c>
       <c r="I24" s="36" t="inlineStr">
@@ -1653,7 +1653,7 @@
       <c r="E25" s="33" t="n"/>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 148</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 158</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="H25" s="30" t="inlineStr">
         <is>
-          <t>3 8 14 21</t>
+          <t>3 8 14 22</t>
         </is>
       </c>
       <c r="I25" s="36" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 90, 91, 92</t>
+          <t>И05.09.26-ВК, см. листы 7, 8, 10, 11; И05.09.26-ВК.СО, поз. 95, 96, 97</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="H27" s="30" t="inlineStr">
         <is>
-          <t>7 8 10 11 18 19</t>
+          <t>7 8 10 11 20</t>
         </is>
       </c>
       <c r="I27" s="36" t="n"/>
@@ -1746,7 +1746,7 @@
       <c r="E28" s="33" t="n"/>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 93</t>
+          <t>И05.09.26-ВК, см. листы 10, 11; И05.09.26-ВК.СО, поз. 98</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H28" s="30" t="inlineStr">
         <is>
-          <t>10 11 19</t>
+          <t>10 11 20</t>
         </is>
       </c>
       <c r="I28" s="36" t="n"/>
@@ -1783,7 +1783,7 @@
       <c r="E29" s="33" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 97</t>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 102</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="H29" s="30" t="inlineStr">
         <is>
-          <t>13 19</t>
+          <t>13 20</t>
         </is>
       </c>
       <c r="I29" s="36" t="inlineStr">
@@ -1824,7 +1824,7 @@
       <c r="E30" s="33" t="n"/>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 98</t>
+          <t>И05.09.26-ВК, см. листы 3, 8, 14; И05.09.26-ВК.СО, поз. 103</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H30" s="30" t="inlineStr">
         <is>
-          <t>3 8 14 19</t>
+          <t>3 8 14 20</t>
         </is>
       </c>
       <c r="I30" s="36" t="inlineStr">
@@ -1865,7 +1865,7 @@
       <c r="E31" s="33" t="n"/>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 99</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 104</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="H31" s="30" t="inlineStr">
         <is>
-          <t>4 19</t>
+          <t>4 20</t>
         </is>
       </c>
       <c r="I31" s="36" t="n"/>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 94, 95, 96</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 14; И05.09.26-ВК.СО, поз. 99, 100, 101</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="H32" s="30" t="inlineStr">
         <is>
-          <t>4 7 14 19</t>
+          <t>4 7 14 20</t>
         </is>
       </c>
       <c r="I32" s="36" t="inlineStr">
@@ -1947,7 +1947,7 @@
       <c r="E33" s="33" t="n"/>
       <c r="F33" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 100</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 105</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="H33" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 19</t>
+          <t>3 4 5 8 20</t>
         </is>
       </c>
       <c r="I33" s="36" t="n"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>7 8 10 11 15</t>
+          <t>7 8 10 11 16</t>
         </is>
       </c>
       <c r="I35" s="36" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H36" s="30" t="inlineStr">
         <is>
-          <t>8 11 15</t>
+          <t>8 11 16</t>
         </is>
       </c>
       <c r="I36" s="36" t="n"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="H37" s="30" t="inlineStr">
         <is>
-          <t>8 11 15</t>
+          <t>8 11 16</t>
         </is>
       </c>
       <c r="I37" s="36" t="n"/>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="H38" s="30" t="inlineStr">
         <is>
-          <t>5 8 10 11 15</t>
+          <t>5 8 10 11 16</t>
         </is>
       </c>
       <c r="I38" s="36" t="inlineStr">
@@ -2178,7 +2178,7 @@
       <c r="E40" s="33" t="n"/>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 40, 68</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 40, 69</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="H40" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 12 16 17</t>
+          <t>5 6 9 12 17 18</t>
         </is>
       </c>
       <c r="I40" s="36" t="n"/>
@@ -2215,7 +2215,7 @@
       <c r="E41" s="33" t="n"/>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 41, 69, 70</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 41, 70, 71</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H41" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 12 16 17</t>
+          <t>5 6 9 12 17 19</t>
         </is>
       </c>
       <c r="I41" s="36" t="n"/>
@@ -2252,7 +2252,7 @@
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 42, 71, 72</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 42, 72, 73</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H42" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 12 16 18</t>
+          <t>5 6 9 12 17 19</t>
         </is>
       </c>
       <c r="I42" s="36" t="n"/>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H43" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 14 16</t>
+          <t>6 9 12 14 17</t>
         </is>
       </c>
       <c r="I43" s="36" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="H44" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 14 16</t>
+          <t>6 9 12 14 17</t>
         </is>
       </c>
       <c r="I44" s="36" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="H45" s="30" t="inlineStr">
         <is>
-          <t>14 16</t>
+          <t>14 17</t>
         </is>
       </c>
       <c r="I45" s="36" t="inlineStr">
@@ -2416,7 +2416,7 @@
       <c r="E46" s="33" t="n"/>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 46</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 47</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H46" s="30" t="inlineStr">
         <is>
-          <t>14 17</t>
+          <t>14 18</t>
         </is>
       </c>
       <c r="I46" s="36" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="H47" s="30" t="inlineStr">
         <is>
-          <t>4 14 16</t>
+          <t>4 14 17</t>
         </is>
       </c>
       <c r="I47" s="36" t="inlineStr">
@@ -2498,7 +2498,7 @@
       <c r="E48" s="33" t="n"/>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 117</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 122</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="H48" s="30" t="inlineStr">
         <is>
-          <t>4 20</t>
+          <t>4 21</t>
         </is>
       </c>
       <c r="I48" s="36" t="inlineStr">
@@ -2539,7 +2539,7 @@
       <c r="E49" s="33" t="n"/>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 118</t>
+          <t>И05.09.26-ВК, см. лист 4; И05.09.26-ВК.СО, поз. 123</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="H49" s="30" t="inlineStr">
         <is>
-          <t>4 20</t>
+          <t>4 21</t>
         </is>
       </c>
       <c r="I49" s="36" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 73, 74, 75, 76, 81, 82, 83, 84, 86</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 12; И05.09.26-ВК.СО, поз. 74, 75, 76, 77, 82, 83, 84, 85, 87</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="H50" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 12 18</t>
+          <t>5 6 9 12 19</t>
         </is>
       </c>
       <c r="I50" s="36" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 77, 78, 79, 80</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 12, 14; И05.09.26-ВК.СО, поз. 78, 79, 80, 81</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H51" s="30" t="inlineStr">
         <is>
-          <t>6 9 12 14 18</t>
+          <t>6 9 12 14 19</t>
         </is>
       </c>
       <c r="I51" s="36" t="inlineStr">
@@ -2670,7 +2670,7 @@
       <c r="E52" s="33" t="n"/>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 87</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 12; И05.09.26-ВК.СО, поз. 88</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H52" s="30" t="inlineStr">
         <is>
-          <t>5 6 12 18</t>
+          <t>5 6 12 19</t>
         </is>
       </c>
       <c r="I52" s="36" t="n"/>
@@ -2707,7 +2707,7 @@
       <c r="E53" s="33" t="n"/>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 85, 88</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 86, 89</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="H53" s="30" t="inlineStr">
         <is>
-          <t>6 9 14 18</t>
+          <t>6 9 14 19</t>
         </is>
       </c>
       <c r="I53" s="36" t="inlineStr">
@@ -2748,7 +2748,7 @@
       <c r="E54" s="33" t="n"/>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 116</t>
+          <t>И05.09.26-ВК, см. листы 6, 9, 14; И05.09.26-ВК.СО, поз. 121</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H54" s="30" t="inlineStr">
         <is>
-          <t>6 9 14 20</t>
+          <t>6 9 14 21</t>
         </is>
       </c>
       <c r="I54" s="36" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 107, 108, 109, 110</t>
+          <t>И05.09.26-ВК, см. листы 4, 6, 9; И05.09.26-ВК.СО, поз. 112, 113, 114, 115</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="H55" s="30" t="inlineStr">
         <is>
-          <t>4 6 9 19</t>
+          <t>4 6 9 21</t>
         </is>
       </c>
       <c r="I55" s="36" t="n"/>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 111, 112, 113, 114</t>
+          <t>И05.09.26-ВК, см. листы 5, 6, 9, 14; И05.09.26-ВК.СО, поз. 116, 117, 118, 119</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="H56" s="30" t="inlineStr">
         <is>
-          <t>5 6 9 14 19 20</t>
+          <t>5 6 9 14 21</t>
         </is>
       </c>
       <c r="I56" s="36" t="inlineStr">
@@ -2875,7 +2875,7 @@
       <c r="E57" s="33" t="n"/>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 115</t>
+          <t>И05.09.26-ВК, см. листы 12, 14; И05.09.26-ВК.СО, поз. 120</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="H57" s="30" t="inlineStr">
         <is>
-          <t>12 14 20</t>
+          <t>12 14 21</t>
         </is>
       </c>
       <c r="I57" s="36" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 145, 146, 147</t>
+          <t>И05.09.26-ВК, см. листы 5, 14; И05.09.26-ВК.СО, поз. 153, 154, 155</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="H58" s="30" t="inlineStr">
         <is>
-          <t>5 14 21</t>
+          <t>5 14 22</t>
         </is>
       </c>
       <c r="I58" s="36" t="n"/>
@@ -2938,7 +2938,7 @@
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="27" t="inlineStr">
         <is>
-          <t>Защита от протечек</t>
+          <t>Внутренние водостоки К2</t>
         </is>
       </c>
       <c r="B59" s="28" t="n"/>
@@ -2950,7 +2950,7 @@
       <c r="H59" s="28" t="n"/>
       <c r="I59" s="29" t="n"/>
     </row>
-    <row r="60" ht="45" customHeight="1">
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" s="30" t="inlineStr">
         <is>
           <t>51</t>
@@ -2958,21 +2958,21 @@
       </c>
       <c r="B60" s="31" t="inlineStr">
         <is>
-          <t>Установка контроллеров системы защиты от протечек с подключением кранов и датчиков</t>
+          <t>Прокладка стояков и выпусков из чугунных безраструбных труб SML DN100 в штрабах стен с фасонными частями и соединительными хомутами</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D60" s="32" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="E60" s="33" t="n"/>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 119</t>
+          <t>И05.09.26-ВК, см. лист 15; И05.09.26-ВК.СО, поз. 46, 90, 92, 93</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="H60" s="30" t="inlineStr">
         <is>
-          <t>2 4 8 20</t>
+          <t>15 18 19</t>
         </is>
       </c>
       <c r="I60" s="36" t="inlineStr">
         <is>
-          <t>питание 230 В и сигнал в умный дом — ЭОМ/СС (ТЗ-2)</t>
+          <t>стояки Ст.К2-1…8; выпуски сквозь стену к ДК — до границы с НВК</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>Установка кранов шаровых с электроприводом Ду 20–32</t>
+          <t>Установка ревизий SML DN100 на стояках К2</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -3008,16 +3008,12 @@
         </is>
       </c>
       <c r="D61" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E61" s="33" t="inlineStr">
-        <is>
-          <t>1 + 2 = 3</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E61" s="33" t="n"/>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 120, 121</t>
+          <t>И05.09.26-ВК, см. лист 15; И05.09.26-ВК.СО, поз. 91</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -3027,10 +3023,14 @@
       </c>
       <c r="H61" s="30" t="inlineStr">
         <is>
-          <t>4 7 8 20</t>
-        </is>
-      </c>
-      <c r="I61" s="36" t="n"/>
+          <t>15 19</t>
+        </is>
+      </c>
+      <c r="I61" s="36" t="inlineStr">
+        <is>
+          <t>+1,000</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="30" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B62" s="31" t="inlineStr">
         <is>
-          <t>Установка датчиков протечки проводных на полу</t>
+          <t>Установка кровельных воронок Ø110 с присоединением к стояку</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -3049,12 +3049,12 @@
         </is>
       </c>
       <c r="D62" s="32" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E62" s="33" t="n"/>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 122</t>
+          <t>И05.09.26-ВК, см. лист 15; И05.09.26-ВК.СО, поз. 124</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -3064,12 +3064,16 @@
       </c>
       <c r="H62" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 20</t>
-        </is>
-      </c>
-      <c r="I62" s="36" t="n"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
+          <t>15 21</t>
+        </is>
+      </c>
+      <c r="I62" s="36" t="inlineStr">
+        <is>
+          <t>примыкание к кровле — АР</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
       <c r="A63" s="30" t="inlineStr">
         <is>
           <t>54</t>
@@ -3077,21 +3081,21 @@
       </c>
       <c r="B63" s="31" t="inlineStr">
         <is>
-          <t>Прокладка кабелей датчиков протечки в гофротрубе</t>
+          <t>Установка люков нажимных ревизионных 300×300 в стенах у ревизий водостоков</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D63" s="32" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="E63" s="33" t="n"/>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 123</t>
+          <t>И05.09.26-ВК, см. лист 15; И05.09.26-ВК.СО, поз. 125</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -3101,68 +3105,72 @@
       </c>
       <c r="H63" s="30" t="inlineStr">
         <is>
-          <t>3 4 5 8 20</t>
+          <t>15 21</t>
         </is>
       </c>
       <c r="I63" s="36" t="inlineStr">
         <is>
-          <t>совместно с ЭОМ/СС</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="27" t="inlineStr">
-        <is>
-          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
-        </is>
-      </c>
-      <c r="B64" s="28" t="n"/>
-      <c r="C64" s="28" t="n"/>
-      <c r="D64" s="28" t="n"/>
-      <c r="E64" s="28" t="n"/>
-      <c r="F64" s="28" t="n"/>
-      <c r="G64" s="28" t="n"/>
-      <c r="H64" s="28" t="n"/>
-      <c r="I64" s="29" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="30" t="inlineStr">
+          <t>ниши — АР (ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B65" s="31" t="inlineStr">
-        <is>
-          <t>Установка унитазов подвесных с инсталляциями</t>
-        </is>
-      </c>
-      <c r="C65" s="32" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="D65" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" s="33" t="n"/>
-      <c r="F65" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 101</t>
-        </is>
-      </c>
-      <c r="G65" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H65" s="30" t="inlineStr">
-        <is>
-          <t>3 5 6 8 9 19</t>
-        </is>
-      </c>
-      <c r="I65" s="36" t="n"/>
-    </row>
-    <row r="66" ht="30" customHeight="1">
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>Крепление стояков SML хомутами и опорами стояков</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="E64" s="33" t="inlineStr">
+        <is>
+          <t>42 + 8 = 50</t>
+        </is>
+      </c>
+      <c r="F64" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 15; И05.09.26-ВК.СО, поз. 156, 157</t>
+        </is>
+      </c>
+      <c r="G64" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H64" s="30" t="inlineStr">
+        <is>
+          <t>15 22</t>
+        </is>
+      </c>
+      <c r="I64" s="36" t="n"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>Защита от протечек</t>
+        </is>
+      </c>
+      <c r="B65" s="28" t="n"/>
+      <c r="C65" s="28" t="n"/>
+      <c r="D65" s="28" t="n"/>
+      <c r="E65" s="28" t="n"/>
+      <c r="F65" s="28" t="n"/>
+      <c r="G65" s="28" t="n"/>
+      <c r="H65" s="28" t="n"/>
+      <c r="I65" s="29" t="n"/>
+    </row>
+    <row r="66" ht="45" customHeight="1">
       <c r="A66" s="30" t="inlineStr">
         <is>
           <t>56</t>
@@ -3170,21 +3178,21 @@
       </c>
       <c r="B66" s="31" t="inlineStr">
         <is>
-          <t>Установка умывальников со смесителями и сифонами</t>
+          <t>Установка контроллеров системы защиты от протечек с подключением кранов и датчиков</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D66" s="32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E66" s="33" t="n"/>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 102</t>
+          <t>И05.09.26-ВК, см. листы 2, 4, 8; И05.09.26-ВК.СО, поз. 126</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -3194,10 +3202,14 @@
       </c>
       <c r="H66" s="30" t="inlineStr">
         <is>
-          <t>3 5 8 19</t>
-        </is>
-      </c>
-      <c r="I66" s="36" t="n"/>
+          <t>2 4 8 21</t>
+        </is>
+      </c>
+      <c r="I66" s="36" t="inlineStr">
+        <is>
+          <t>питание 230 В и сигнал в умный дом — ЭОМ/СС (ТЗ-2)</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="30" t="inlineStr">
@@ -3207,21 +3219,25 @@
       </c>
       <c r="B67" s="31" t="inlineStr">
         <is>
-          <t>Установка ванн со смесителями и сифонами</t>
+          <t>Установка кранов шаровых с электроприводом Ду 20–32</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D67" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E67" s="33" t="n"/>
+      <c r="E67" s="33" t="inlineStr">
+        <is>
+          <t>1 + 2 = 3</t>
+        </is>
+      </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 103</t>
+          <t>И05.09.26-ВК, см. листы 4, 7, 8; И05.09.26-ВК.СО, поз. 127, 128</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -3231,7 +3247,7 @@
       </c>
       <c r="H67" s="30" t="inlineStr">
         <is>
-          <t>5 8 19</t>
+          <t>4 7 8 21</t>
         </is>
       </c>
       <c r="I67" s="36" t="n"/>
@@ -3244,21 +3260,21 @@
       </c>
       <c r="B68" s="31" t="inlineStr">
         <is>
-          <t>Установка душевых систем, кабины, подключение трапов</t>
+          <t>Установка датчиков протечки проводных на полу</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D68" s="32" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E68" s="33" t="n"/>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 104</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 129</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -3268,7 +3284,7 @@
       </c>
       <c r="H68" s="30" t="inlineStr">
         <is>
-          <t>4 5 8 19</t>
+          <t>3 4 5 8 21</t>
         </is>
       </c>
       <c r="I68" s="36" t="n"/>
@@ -3281,21 +3297,21 @@
       </c>
       <c r="B69" s="31" t="inlineStr">
         <is>
-          <t>Установка моек кухонных со смесителями и сифонами</t>
+          <t>Прокладка кабелей датчиков протечки в гофротрубе</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D69" s="32" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="E69" s="33" t="n"/>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 105</t>
+          <t>И05.09.26-ВК, см. листы 3, 4, 5, 8; И05.09.26-ВК.СО, поз. 130</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -3305,64 +3321,68 @@
       </c>
       <c r="H69" s="30" t="inlineStr">
         <is>
-          <t>3 8 19</t>
-        </is>
-      </c>
-      <c r="I69" s="36" t="n"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
+          <t>3 4 5 8 21</t>
+        </is>
+      </c>
+      <c r="I69" s="36" t="inlineStr">
+        <is>
+          <t>совместно с ЭОМ/СС</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>Санитарные приборы (поставка — по дизайн-проекту)</t>
+        </is>
+      </c>
+      <c r="B70" s="28" t="n"/>
+      <c r="C70" s="28" t="n"/>
+      <c r="D70" s="28" t="n"/>
+      <c r="E70" s="28" t="n"/>
+      <c r="F70" s="28" t="n"/>
+      <c r="G70" s="28" t="n"/>
+      <c r="H70" s="28" t="n"/>
+      <c r="I70" s="29" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="30" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B70" s="31" t="inlineStr">
-        <is>
-          <t>Установка смесителя для наполнения СПА</t>
-        </is>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="33" t="n"/>
-      <c r="F70" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 106</t>
-        </is>
-      </c>
-      <c r="G70" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>8 19</t>
-        </is>
-      </c>
-      <c r="I70" s="36" t="n"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="27" t="inlineStr">
-        <is>
-          <t>Тепловая изоляция</t>
-        </is>
-      </c>
-      <c r="B71" s="28" t="n"/>
-      <c r="C71" s="28" t="n"/>
-      <c r="D71" s="28" t="n"/>
-      <c r="E71" s="28" t="n"/>
-      <c r="F71" s="28" t="n"/>
-      <c r="G71" s="28" t="n"/>
-      <c r="H71" s="28" t="n"/>
-      <c r="I71" s="29" t="n"/>
-    </row>
-    <row r="72" ht="45" customHeight="1">
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>Установка унитазов подвесных с инсталляциями</t>
+        </is>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" s="33" t="n"/>
+      <c r="F71" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 3, 5, 6, 8, 9; И05.09.26-ВК.СО, поз. 106</t>
+        </is>
+      </c>
+      <c r="G71" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H71" s="30" t="inlineStr">
+        <is>
+          <t>3 5 6 8 9 20</t>
+        </is>
+      </c>
+      <c r="I71" s="36" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
       <c r="A72" s="30" t="inlineStr">
         <is>
           <t>61</t>
@@ -3370,25 +3390,21 @@
       </c>
       <c r="B72" s="31" t="inlineStr">
         <is>
-          <t>Изоляция трубопроводов Т3, Т4 трубками из вспененного полиэтилена толщиной 13 мм</t>
+          <t>Установка умывальников со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D72" s="32" t="n">
-        <v>229</v>
-      </c>
-      <c r="E72" s="33" t="inlineStr">
-        <is>
-          <t>28 + 154 + 47 = 229</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E72" s="33" t="n"/>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 124, 125, 126</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8; И05.09.26-ВК.СО, поз. 107</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -3398,12 +3414,12 @@
       </c>
       <c r="H72" s="30" t="inlineStr">
         <is>
-          <t>3 5 8 10 11 20</t>
+          <t>3 5 8 20</t>
         </is>
       </c>
       <c r="I72" s="36" t="n"/>
     </row>
-    <row r="73" ht="45" customHeight="1">
+    <row r="73" ht="30" customHeight="1">
       <c r="A73" s="30" t="inlineStr">
         <is>
           <t>62</t>
@@ -3411,25 +3427,21 @@
       </c>
       <c r="B73" s="31" t="inlineStr">
         <is>
-          <t>Изоляция трубопроводов В1 трубками из вспененного полиэтилена толщиной 9 мм</t>
+          <t>Установка ванн со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D73" s="32" t="n">
-        <v>209</v>
-      </c>
-      <c r="E73" s="33" t="inlineStr">
-        <is>
-          <t>78 + 42 + 77 + 12 = 209</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E73" s="33" t="n"/>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 127, 128, 129, 130</t>
+          <t>И05.09.26-ВК, см. листы 5, 8; И05.09.26-ВК.СО, поз. 108</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -3439,49 +3451,71 @@
       </c>
       <c r="H73" s="30" t="inlineStr">
         <is>
-          <t>3 5 8 10 11 20</t>
+          <t>5 8 20</t>
         </is>
       </c>
       <c r="I73" s="36" t="n"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="27" t="inlineStr">
-        <is>
-          <t>Проходы через строительные конструкции</t>
-        </is>
-      </c>
-      <c r="B74" s="28" t="n"/>
-      <c r="C74" s="28" t="n"/>
-      <c r="D74" s="28" t="n"/>
-      <c r="E74" s="28" t="n"/>
-      <c r="F74" s="28" t="n"/>
-      <c r="G74" s="28" t="n"/>
-      <c r="H74" s="28" t="n"/>
-      <c r="I74" s="29" t="n"/>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="inlineStr">
+        <is>
+          <t>Установка душевых систем, кабины, подключение трапов</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" s="33" t="n"/>
+      <c r="F74" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 4, 5, 8; И05.09.26-ВК.СО, поз. 109</t>
+        </is>
+      </c>
+      <c r="G74" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H74" s="30" t="inlineStr">
+        <is>
+          <t>4 5 8 20</t>
+        </is>
+      </c>
+      <c r="I74" s="36" t="n"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B75" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
+          <t>Установка моек кухонных со смесителями и сифонами</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D75" s="32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E75" s="33" t="n"/>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
+          <t>И05.09.26-ВК, см. листы 3, 8; И05.09.26-ВК.СО, поз. 110</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -3491,24 +3525,20 @@
       </c>
       <c r="H75" s="30" t="inlineStr">
         <is>
-          <t>14 20</t>
-        </is>
-      </c>
-      <c r="I75" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
+          <t>3 8 20</t>
+        </is>
+      </c>
+      <c r="I75" s="36" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B76" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
+          <t>Установка смесителя для наполнения СПА</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -3517,12 +3547,12 @@
         </is>
       </c>
       <c r="D76" s="32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E76" s="33" t="n"/>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 133</t>
+          <t>И05.09.26-ВК, см. лист 8; И05.09.26-ВК.СО, поз. 111</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -3532,57 +3562,27 @@
       </c>
       <c r="H76" s="30" t="inlineStr">
         <is>
-          <t>14 20</t>
-        </is>
-      </c>
-      <c r="I76" s="36" t="inlineStr">
-        <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="inlineStr">
-        <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
-        </is>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>26</v>
-      </c>
-      <c r="E77" s="33" t="n"/>
-      <c r="F77" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
-        </is>
-      </c>
-      <c r="G77" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>14 20</t>
-        </is>
-      </c>
-      <c r="I77" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="30" customHeight="1">
+          <t>8 21</t>
+        </is>
+      </c>
+      <c r="I76" s="36" t="n"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>Тепловая изоляция</t>
+        </is>
+      </c>
+      <c r="B77" s="28" t="n"/>
+      <c r="C77" s="28" t="n"/>
+      <c r="D77" s="28" t="n"/>
+      <c r="E77" s="28" t="n"/>
+      <c r="F77" s="28" t="n"/>
+      <c r="G77" s="28" t="n"/>
+      <c r="H77" s="28" t="n"/>
+      <c r="I77" s="29" t="n"/>
+    </row>
+    <row r="78" ht="45" customHeight="1">
       <c r="A78" s="30" t="inlineStr">
         <is>
           <t>66</t>
@@ -3590,21 +3590,25 @@
       </c>
       <c r="B78" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
+          <t>Изоляция трубопроводов Т3, Т4 трубками из вспененного полиэтилена толщиной 13 мм</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D78" s="32" t="n">
-        <v>26</v>
-      </c>
-      <c r="E78" s="33" t="n"/>
+        <v>229</v>
+      </c>
+      <c r="E78" s="33" t="inlineStr">
+        <is>
+          <t>28 + 154 + 47 = 229</t>
+        </is>
+      </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 134</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 131, 132, 133</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -3614,16 +3618,12 @@
       </c>
       <c r="H78" s="30" t="inlineStr">
         <is>
-          <t>14 20</t>
-        </is>
-      </c>
-      <c r="I78" s="36" t="inlineStr">
-        <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1">
+          <t>3 5 8 10 11 21</t>
+        </is>
+      </c>
+      <c r="I78" s="36" t="n"/>
+    </row>
+    <row r="79" ht="45" customHeight="1">
       <c r="A79" s="30" t="inlineStr">
         <is>
           <t>67</t>
@@ -3631,21 +3631,25 @@
       </c>
       <c r="B79" s="31" t="inlineStr">
         <is>
-          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
+          <t>Изоляция трубопроводов В1 трубками из вспененного полиэтилена толщиной 9 мм</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D79" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="E79" s="33" t="n"/>
+        <v>209</v>
+      </c>
+      <c r="E79" s="33" t="inlineStr">
+        <is>
+          <t>78 + 42 + 77 + 12 = 209</t>
+        </is>
+      </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
+          <t>И05.09.26-ВК, см. листы 3, 5, 8, 10, 11; И05.09.26-ВК.СО, поз. 134, 135, 136, 137</t>
         </is>
       </c>
       <c r="G79" s="35" t="inlineStr">
@@ -3655,16 +3659,12 @@
       </c>
       <c r="H79" s="30" t="inlineStr">
         <is>
-          <t>14 20</t>
-        </is>
-      </c>
-      <c r="I79" s="36" t="inlineStr">
-        <is>
-          <t>по толщине конструкции</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="30" customHeight="1">
+          <t>3 5 8 10 11 22</t>
+        </is>
+      </c>
+      <c r="I79" s="36" t="n"/>
+    </row>
+    <row r="80" ht="45" customHeight="1">
       <c r="A80" s="30" t="inlineStr">
         <is>
           <t>68</t>
@@ -3672,21 +3672,21 @@
       </c>
       <c r="B80" s="31" t="inlineStr">
         <is>
-          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
+          <t>Изоляция стояков и выпусков К2 (SML) трубками из вспененного полиэтилена толщиной 9 мм от конденсата</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="D80" s="32" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E80" s="33" t="n"/>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 135</t>
+          <t>И05.09.26-ВК, см. лист 15; И05.09.26-ВК.СО, поз. 148</t>
         </is>
       </c>
       <c r="G80" s="35" t="inlineStr">
@@ -3696,75 +3696,53 @@
       </c>
       <c r="H80" s="30" t="inlineStr">
         <is>
-          <t>14 20</t>
+          <t>15 22</t>
         </is>
       </c>
       <c r="I80" s="36" t="inlineStr">
         <is>
-          <t>п. 11.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="45" customHeight="1">
-      <c r="A81" s="30" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B81" s="31" t="inlineStr">
-        <is>
-          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
-        </is>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="33" t="n"/>
-      <c r="F81" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 136</t>
-        </is>
-      </c>
-      <c r="G81" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H81" s="30" t="inlineStr">
-        <is>
-          <t>14 20</t>
-        </is>
-      </c>
-      <c r="I81" s="36" t="n"/>
+          <t>кроме Ст.К2-8 на террасе 1.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>Проходы через строительные конструкции</t>
+        </is>
+      </c>
+      <c r="B81" s="28" t="n"/>
+      <c r="C81" s="28" t="n"/>
+      <c r="D81" s="28" t="n"/>
+      <c r="E81" s="28" t="n"/>
+      <c r="F81" s="28" t="n"/>
+      <c r="G81" s="28" t="n"/>
+      <c r="H81" s="28" t="n"/>
+      <c r="I81" s="29" t="n"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B82" s="31" t="inlineStr">
         <is>
-          <t>Заделка торцов футляров эластичным водогазонепроницаемым материалом</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø50</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D82" s="32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E82" s="33" t="n"/>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 137</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 140</t>
         </is>
       </c>
       <c r="G82" s="35" t="inlineStr">
@@ -3774,38 +3752,38 @@
       </c>
       <c r="H82" s="30" t="inlineStr">
         <is>
-          <t>14 21</t>
+          <t>14 22</t>
         </is>
       </c>
       <c r="I82" s="36" t="inlineStr">
         <is>
-          <t>футляры Ø75 и Ø160 (п. 8.8)</t>
+          <t>по толщине конструкции</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="30" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B83" s="31" t="inlineStr">
         <is>
-          <t>Заделка проёмов под пучки труб в плитах и стенах</t>
+          <t>Установка гильз из труб ПП Ø50 с заполнением зазора</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D83" s="32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E83" s="33" t="n"/>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 138</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 140</t>
         </is>
       </c>
       <c r="G83" s="35" t="inlineStr">
@@ -3815,72 +3793,98 @@
       </c>
       <c r="H83" s="30" t="inlineStr">
         <is>
-          <t>14 21</t>
+          <t>14 22</t>
         </is>
       </c>
       <c r="I83" s="36" t="inlineStr">
         <is>
-          <t>ТЗ-1, лист 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="45" customHeight="1">
+          <t>п. 11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="30" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø75</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="E84" s="33" t="n"/>
+      <c r="F84" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 141</t>
+        </is>
+      </c>
+      <c r="G84" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H84" s="30" t="inlineStr">
+        <is>
+          <t>14 22</t>
+        </is>
+      </c>
+      <c r="I84" s="36" t="inlineStr">
+        <is>
+          <t>по толщине конструкции</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="30" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B84" s="31" t="inlineStr">
-        <is>
-          <t>Утепление К1-1 под террасой 1.13 и К1-б под террасой бани б1 плитами ЭППС 50 мм</t>
-        </is>
-      </c>
-      <c r="C84" s="32" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D84" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E84" s="33" t="inlineStr">
-        <is>
-          <t>2.4 + 3.1 = 5.5</t>
-        </is>
-      </c>
-      <c r="F84" s="34" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК, см. листы 6, 9; И05.09.26-ВК.СО, поз. 139, 140</t>
-        </is>
-      </c>
-      <c r="G84" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H84" s="30" t="inlineStr">
-        <is>
-          <t>6 9 21</t>
-        </is>
-      </c>
-      <c r="I84" s="36" t="n"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="27" t="inlineStr">
-        <is>
-          <t>Испытания и пусконаладочные работы</t>
-        </is>
-      </c>
-      <c r="B85" s="28" t="n"/>
-      <c r="C85" s="28" t="n"/>
-      <c r="D85" s="28" t="n"/>
-      <c r="E85" s="28" t="n"/>
-      <c r="F85" s="28" t="n"/>
-      <c r="G85" s="28" t="n"/>
-      <c r="H85" s="28" t="n"/>
-      <c r="I85" s="29" t="n"/>
-    </row>
-    <row r="86" ht="45" customHeight="1">
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>Установка гильз из труб ПП Ø75 с заполнением зазора</t>
+        </is>
+      </c>
+      <c r="C85" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D85" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="E85" s="33" t="n"/>
+      <c r="F85" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 141</t>
+        </is>
+      </c>
+      <c r="G85" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H85" s="30" t="inlineStr">
+        <is>
+          <t>14 22</t>
+        </is>
+      </c>
+      <c r="I85" s="36" t="inlineStr">
+        <is>
+          <t>п. 11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
       <c r="A86" s="30" t="inlineStr">
         <is>
           <t>73</t>
@@ -3888,25 +3892,21 @@
       </c>
       <c r="B86" s="31" t="inlineStr">
         <is>
-          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
+          <t>Сверление отверстий в стенах и перекрытиях под гильзы Ø160</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D86" s="32" t="n">
-        <v>440</v>
-      </c>
-      <c r="E86" s="33" t="inlineStr">
-        <is>
-          <t>12 + 123 + 196 + 106 + 3 = 440</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E86" s="33" t="n"/>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 35, 36, 37, 38, 39</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 142</t>
         </is>
       </c>
       <c r="G86" s="35" t="inlineStr">
@@ -3916,16 +3916,16 @@
       </c>
       <c r="H86" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
+          <t>14 22</t>
         </is>
       </c>
       <c r="I86" s="36" t="inlineStr">
         <is>
-          <t>в т. ч. до закрытия в конструкциях</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="45" customHeight="1">
+          <t>по толщине конструкции</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
       <c r="A87" s="30" t="inlineStr">
         <is>
           <t>74</t>
@@ -3933,25 +3933,21 @@
       </c>
       <c r="B87" s="31" t="inlineStr">
         <is>
-          <t>Испытание систем канализации К1 и К2 (участок К2-1) проливом воды</t>
+          <t>Установка гильз из труб ПП Ø160 с заполнением зазора</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="D87" s="32" t="n">
-        <v>139</v>
-      </c>
-      <c r="E87" s="33" t="inlineStr">
-        <is>
-          <t>30 + 28 + 1 + 25 + 52 + 3 = 139</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E87" s="33" t="n"/>
       <c r="F87" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 40, 41, 42, 43, 44, 45</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 142</t>
         </is>
       </c>
       <c r="G87" s="35" t="inlineStr">
@@ -3961,12 +3957,16 @@
       </c>
       <c r="H87" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
-        </is>
-      </c>
-      <c r="I87" s="36" t="n"/>
-    </row>
-    <row r="88" ht="30" customHeight="1">
+          <t>14 22</t>
+        </is>
+      </c>
+      <c r="I87" s="36" t="inlineStr">
+        <is>
+          <t>п. 11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="45" customHeight="1">
       <c r="A88" s="30" t="inlineStr">
         <is>
           <t>75</t>
@@ -3974,25 +3974,21 @@
       </c>
       <c r="B88" s="31" t="inlineStr">
         <is>
-          <t>Испытание трубопроводов К1, К2 в грунте наполнением водой до засыпки</t>
+          <t>Заделка гильз негорючим гидрофобным материалом, в противопожарных конструкциях — огнезащитным герметиком</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D88" s="32" t="n">
-        <v>80</v>
-      </c>
-      <c r="E88" s="33" t="inlineStr">
-        <is>
-          <t>25 + 52 + 3 = 80</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E88" s="33" t="n"/>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 43, 44, 45</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 143</t>
         </is>
       </c>
       <c r="G88" s="35" t="inlineStr">
@@ -4002,12 +3998,12 @@
       </c>
       <c r="H88" s="30" t="inlineStr">
         <is>
-          <t>2 14 16</t>
+          <t>14 22</t>
         </is>
       </c>
       <c r="I88" s="36" t="n"/>
     </row>
-    <row r="89" ht="45" customHeight="1">
+    <row r="89" ht="30" customHeight="1">
       <c r="A89" s="30" t="inlineStr">
         <is>
           <t>76</t>
@@ -4015,25 +4011,21 @@
       </c>
       <c r="B89" s="31" t="inlineStr">
         <is>
-          <t>Промывка и дезинфекция трубопроводов систем В1, Т3, Т4</t>
+          <t>Заделка торцов футляров эластичным водогазонепроницаемым материалом</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D89" s="32" t="n">
-        <v>440</v>
-      </c>
-      <c r="E89" s="33" t="inlineStr">
-        <is>
-          <t>12 + 123 + 196 + 106 + 3 = 440</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E89" s="33" t="n"/>
       <c r="F89" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 35, 36, 37, 38, 39</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 144</t>
         </is>
       </c>
       <c r="G89" s="35" t="inlineStr">
@@ -4043,10 +4035,14 @@
       </c>
       <c r="H89" s="30" t="inlineStr">
         <is>
-          <t>1 2 16</t>
-        </is>
-      </c>
-      <c r="I89" s="36" t="n"/>
+          <t>14 22</t>
+        </is>
+      </c>
+      <c r="I89" s="36" t="inlineStr">
+        <is>
+          <t>футляры Ø75 и Ø160 (п. 8.8)</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="30" t="inlineStr">
@@ -4056,21 +4052,21 @@
       </c>
       <c r="B90" s="31" t="inlineStr">
         <is>
-          <t>Наладка циркуляции ГВС: настройка балансировочных клапанов по П4</t>
+          <t>Заделка проёмов под пучки труб в плитах и стенах</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="D90" s="32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E90" s="33" t="n"/>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 97</t>
+          <t>И05.09.26-ВК, см. лист 14; И05.09.26-ВК.СО, поз. 145</t>
         </is>
       </c>
       <c r="G90" s="35" t="inlineStr">
@@ -4080,64 +4076,371 @@
       </c>
       <c r="H90" s="30" t="inlineStr">
         <is>
-          <t>13 19</t>
+          <t>14 22</t>
         </is>
       </c>
       <c r="I90" s="36" t="inlineStr">
         <is>
+          <t>ТЗ-1, лист 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="45" customHeight="1">
+      <c r="A91" s="30" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B91" s="31" t="inlineStr">
+        <is>
+          <t>Утепление К1-1 под террасой 1.13 и К1-б под террасой бани б1 плитами ЭППС 50 мм</t>
+        </is>
+      </c>
+      <c r="C91" s="32" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D91" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E91" s="33" t="inlineStr">
+        <is>
+          <t>2.4 + 3.1 = 5.5</t>
+        </is>
+      </c>
+      <c r="F91" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 6, 9; И05.09.26-ВК.СО, поз. 146, 147</t>
+        </is>
+      </c>
+      <c r="G91" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H91" s="30" t="inlineStr">
+        <is>
+          <t>6 9 22</t>
+        </is>
+      </c>
+      <c r="I91" s="36" t="n"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>Испытания и пусконаладочные работы</t>
+        </is>
+      </c>
+      <c r="B92" s="28" t="n"/>
+      <c r="C92" s="28" t="n"/>
+      <c r="D92" s="28" t="n"/>
+      <c r="E92" s="28" t="n"/>
+      <c r="F92" s="28" t="n"/>
+      <c r="G92" s="28" t="n"/>
+      <c r="H92" s="28" t="n"/>
+      <c r="I92" s="29" t="n"/>
+    </row>
+    <row r="93" ht="45" customHeight="1">
+      <c r="A93" s="30" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B93" s="31" t="inlineStr">
+        <is>
+          <t>Гидростатическое испытание трубопроводов систем В1, Т3, Т4</t>
+        </is>
+      </c>
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D93" s="32" t="n">
+        <v>440</v>
+      </c>
+      <c r="E93" s="33" t="inlineStr">
+        <is>
+          <t>12 + 123 + 196 + 106 + 3 = 440</t>
+        </is>
+      </c>
+      <c r="F93" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 35, 36, 37, 38, 39</t>
+        </is>
+      </c>
+      <c r="G93" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H93" s="30" t="inlineStr">
+        <is>
+          <t>1 2 17</t>
+        </is>
+      </c>
+      <c r="I93" s="36" t="inlineStr">
+        <is>
+          <t>в т. ч. до закрытия в конструкциях</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="45" customHeight="1">
+      <c r="A94" s="30" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B94" s="31" t="inlineStr">
+        <is>
+          <t>Испытание систем канализации К1 и К2 (участок К2-1) проливом воды</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D94" s="32" t="n">
+        <v>139</v>
+      </c>
+      <c r="E94" s="33" t="inlineStr">
+        <is>
+          <t>30 + 28 + 1 + 25 + 52 + 3 = 139</t>
+        </is>
+      </c>
+      <c r="F94" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 40, 41, 42, 43, 44, 45</t>
+        </is>
+      </c>
+      <c r="G94" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H94" s="30" t="inlineStr">
+        <is>
+          <t>1 2 17</t>
+        </is>
+      </c>
+      <c r="I94" s="36" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="30" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B95" s="31" t="inlineStr">
+        <is>
+          <t>Испытание трубопроводов К1, К2 в грунте наполнением водой до засыпки</t>
+        </is>
+      </c>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D95" s="32" t="n">
+        <v>80</v>
+      </c>
+      <c r="E95" s="33" t="inlineStr">
+        <is>
+          <t>25 + 52 + 3 = 80</t>
+        </is>
+      </c>
+      <c r="F95" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 2, 14; И05.09.26-ВК.СО, поз. 43, 44, 45</t>
+        </is>
+      </c>
+      <c r="G95" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H95" s="30" t="inlineStr">
+        <is>
+          <t>2 14 17</t>
+        </is>
+      </c>
+      <c r="I95" s="36" t="n"/>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="30" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B96" s="31" t="inlineStr">
+        <is>
+          <t>Испытание внутренних водостоков К2 наполнением водой до уровня наивысшей воронки (не менее 10 мин) до закрытия штраб</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D96" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E96" s="33" t="n"/>
+      <c r="F96" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 2, 15; И05.09.26-ВК.СО, поз. 46</t>
+        </is>
+      </c>
+      <c r="G96" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H96" s="30" t="inlineStr">
+        <is>
+          <t>2 15 18</t>
+        </is>
+      </c>
+      <c r="I96" s="36" t="inlineStr">
+        <is>
+          <t>выпуски на время испытания заглушить</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="45" customHeight="1">
+      <c r="A97" s="30" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B97" s="31" t="inlineStr">
+        <is>
+          <t>Промывка и дезинфекция трубопроводов систем В1, Т3, Т4</t>
+        </is>
+      </c>
+      <c r="C97" s="32" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="D97" s="32" t="n">
+        <v>440</v>
+      </c>
+      <c r="E97" s="33" t="inlineStr">
+        <is>
+          <t>12 + 123 + 196 + 106 + 3 = 440</t>
+        </is>
+      </c>
+      <c r="F97" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. листы 1, 2; И05.09.26-ВК.СО, поз. 35, 36, 37, 38, 39</t>
+        </is>
+      </c>
+      <c r="G97" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H97" s="30" t="inlineStr">
+        <is>
+          <t>1 2 17</t>
+        </is>
+      </c>
+      <c r="I97" s="36" t="n"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="30" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B98" s="31" t="inlineStr">
+        <is>
+          <t>Наладка циркуляции ГВС: настройка балансировочных клапанов по П4</t>
+        </is>
+      </c>
+      <c r="C98" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D98" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E98" s="33" t="n"/>
+      <c r="F98" s="34" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК, см. лист 13; И05.09.26-ВК.СО, поз. 102</t>
+        </is>
+      </c>
+      <c r="G98" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H98" s="30" t="inlineStr">
+        <is>
+          <t>13 20</t>
+        </is>
+      </c>
+      <c r="I98" s="36" t="inlineStr">
+        <is>
           <t>П4</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="30" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B91" s="31" t="inlineStr">
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="30" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B99" s="31" t="inlineStr">
         <is>
           <t>Пусконаладочные работы циркуляционных насосов Н8, Н9</t>
         </is>
       </c>
-      <c r="C91" s="32" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D91" s="32" t="n">
+      <c r="C99" s="32" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="D99" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E91" s="33" t="inlineStr">
+      <c r="E99" s="33" t="inlineStr">
         <is>
           <t>1 + 1 = 2</t>
         </is>
       </c>
-      <c r="F91" s="34" t="inlineStr">
+      <c r="F99" s="34" t="inlineStr">
         <is>
           <t>И05.09.26-ВК, см. листы 7, 8; И05.09.26-ВК.СО, поз. 1, 2</t>
         </is>
       </c>
-      <c r="G91" s="35" t="inlineStr">
-        <is>
-          <t>И05.09.26-ВК Водопровод и канализация</t>
-        </is>
-      </c>
-      <c r="H91" s="30" t="inlineStr">
-        <is>
-          <t>7 8 15</t>
-        </is>
-      </c>
-      <c r="I91" s="36" t="n"/>
+      <c r="G99" s="35" t="inlineStr">
+        <is>
+          <t>И05.09.26-ВК Водопровод и канализация</t>
+        </is>
+      </c>
+      <c r="H99" s="30" t="inlineStr">
+        <is>
+          <t>7 8 16</t>
+        </is>
+      </c>
+      <c r="I99" s="36" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A64:I64"/>
+  <mergeCells count="11">
     <mergeCell ref="A59:I59"/>
-    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A81:I81"/>
     <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A85:I85"/>
-    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A92:I92"/>
     <mergeCell ref="A39:I39"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A4:I4"/>
@@ -4154,7 +4457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -4170,7 +4473,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="38" t="inlineStr">
         <is>
-          <t>1. Объёмы подсчитаны по 3D-модели систем ВК и листам И05.09.26-ВК (1–14); ссылки даны на позиции спецификации И05.09.26-ВК.СО. Длины труб — с запасом 10 %.</t>
+          <t>1. Объёмы подсчитаны по 3D-модели систем ВК и листам И05.09.26-ВК (1–15); ссылки даны на позиции спецификации И05.09.26-ВК.СО. Длины труб — с запасом 10 %.</t>
         </is>
       </c>
     </row>
@@ -4220,6 +4523,13 @@
       <c r="A9" s="38" t="inlineStr">
         <is>
           <t>8. Состав работ уточнён по опросному листу Заказчика: бесшумная канализация, защита от протечек в мокрых зонах, трап в парной, лоток гаража с пескоуловителем в ливневую сеть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>9. Внутренние водостоки К2 — чугунные безраструбные трубы SML DN100 в штрабах стен (решение Заказчика 30.10.2026), лист 15 и приложение П5; дождеприёмники ДК у стен и пластиковые трубы в грунте после них — раздел НВК.</t>
         </is>
       </c>
     </row>
